--- a/reports/screener_2026-08-05.xlsx
+++ b/reports/screener_2026-08-05.xlsx
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="AX5" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.41281066323299</v>
       </c>
       <c r="AY5" t="n">
         <v>-39.50409545018086</v>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="AX9" t="n">
-        <v>-16.54525760371704</v>
+        <v>-14.90715866883865</v>
       </c>
       <c r="AY9" t="n">
         <v>-54.13720844041888</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW11" t="n">
@@ -2763,7 +2763,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="AX14" t="n">
-        <v>-14.30768966674805</v>
+        <v>-12.4901748318072</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="AW15" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="AX15" t="n">
-        <v>-1.277582454837922</v>
+        <v>-2.118835116863982</v>
       </c>
       <c r="AY15" t="n">
         <v>-13.54395936495905</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-2.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.129361865388501</v>
+        <v>-1.814843745989081</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="AW26" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="AX26" t="n">
-        <v>-3.49544105988292</v>
+        <v>-3.053439393562163</v>
       </c>
       <c r="AY26" t="n">
         <v>-39.52381043207078</v>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY29" t="n">
-        <v>-39.51925229062647</v>
+        <v>-39.5192605242667</v>
       </c>
       <c r="AZ29" t="b">
         <v>1</v>
@@ -6217,7 +6217,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY33" t="n">
-        <v>-12.46353572253916</v>
+        <v>-12.46351675410393</v>
       </c>
       <c r="AZ33" t="b">
         <v>1</v>
@@ -6376,7 +6376,7 @@
       <c r="AU34" t="inlineStr"/>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW34" t="n">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="AW36" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="AX36" t="n">
-        <v>-2.285715311515235</v>
+        <v>-2.252858377438904</v>
       </c>
       <c r="AY36" t="n">
         <v>-17.59775069846685</v>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="AX37" t="n">
-        <v>-3.418800283779255</v>
+        <v>-3.004289078750577</v>
       </c>
       <c r="AY37" t="n">
         <v>-52.18694930098489</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-1.98511558212644</v>
       </c>
       <c r="AY38" t="n">
         <v>-47.92224740248528</v>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7955,7 @@
         <v>-0.5080771590812438</v>
       </c>
       <c r="AY43" t="n">
-        <v>-19.64053433208342</v>
+        <v>-19.64052806350488</v>
       </c>
       <c r="AZ43" t="b">
         <v>1</v>
@@ -8466,7 +8466,7 @@
         <v>-4.020742883737105</v>
       </c>
       <c r="AY46" t="n">
-        <v>-14.35606196730216</v>
+        <v>-14.3560541194689</v>
       </c>
       <c r="AZ46" t="b">
         <v>1</v>
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="AW49" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>-0.5291042223046771</v>
       </c>
       <c r="AY49" t="n">
         <v>-15.4147281673955</v>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>16.3700008392334</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="AX50" t="n">
-        <v>-14.84423417392992</v>
+        <v>-13.52358030617676</v>
       </c>
       <c r="AY50" t="n">
         <v>-34.85117715011583</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9506,14 +9506,14 @@
       <c r="AU52" t="inlineStr"/>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW52" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="AX52" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-0.6925190193304398</v>
       </c>
       <c r="AY52" t="n">
         <v>-27.87197279000151</v>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>sem sinal (-0.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="AW58" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="AX58" t="n">
-        <v>-3.506767262291599</v>
+        <v>-3.465848880756128</v>
       </c>
       <c r="AY58" t="n">
-        <v>-13.58724744836764</v>
+        <v>-13.55060950604702</v>
       </c>
       <c r="AZ58" t="b">
         <v>1</v>
@@ -10669,7 +10669,7 @@
       <c r="AU59" t="inlineStr"/>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW59" t="n">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
         <v>-0.9501178501326923</v>
       </c>
       <c r="AY60" t="n">
-        <v>-14.40870028403989</v>
+        <v>-14.40870883002358</v>
       </c>
       <c r="AZ60" t="b">
         <v>1</v>
@@ -13006,10 +13006,10 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="AX5" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.41281066323299</v>
       </c>
       <c r="AY5" t="n">
         <v>-39.50409545018086</v>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13694,10 +13694,10 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="AX9" t="n">
-        <v>-16.54525760371704</v>
+        <v>-14.90715866883865</v>
       </c>
       <c r="AY9" t="n">
         <v>-54.13720844041888</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW11" t="n">
@@ -14398,7 +14398,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -14579,10 +14579,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="AX14" t="n">
-        <v>-14.30768966674805</v>
+        <v>-12.4901748318072</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14752,10 +14752,10 @@
         </is>
       </c>
       <c r="AW15" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="AX15" t="n">
-        <v>-1.277582454837922</v>
+        <v>-2.118835116863982</v>
       </c>
       <c r="AY15" t="n">
         <v>-13.54395936495905</v>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-2.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -15971,10 +15971,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.129361865388501</v>
+        <v>-1.814843745989081</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -16838,10 +16838,10 @@
         </is>
       </c>
       <c r="AW27" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="AX27" t="n">
-        <v>-3.49544105988292</v>
+        <v>-3.053439393562163</v>
       </c>
       <c r="AY27" t="n">
         <v>-39.52381043207078</v>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17323,7 +17323,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY30" t="n">
-        <v>-39.51925229062647</v>
+        <v>-39.5192605242667</v>
       </c>
       <c r="AZ30" t="b">
         <v>1</v>
@@ -18019,7 +18019,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY34" t="n">
-        <v>-12.46353572253916</v>
+        <v>-12.46351675410393</v>
       </c>
       <c r="AZ34" t="b">
         <v>1</v>
@@ -18178,7 +18178,7 @@
       <c r="AU35" t="inlineStr"/>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW35" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -18528,10 +18528,10 @@
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="AX37" t="n">
-        <v>-2.285715311515235</v>
+        <v>-2.252858377438904</v>
       </c>
       <c r="AY37" t="n">
         <v>-17.59775069846685</v>
@@ -18705,10 +18705,10 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="AX38" t="n">
-        <v>-3.418800283779255</v>
+        <v>-3.004289078750577</v>
       </c>
       <c r="AY38" t="n">
         <v>-52.18694930098489</v>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -18878,10 +18878,10 @@
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-1.98511558212644</v>
       </c>
       <c r="AY39" t="n">
         <v>-47.92224740248528</v>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
         <v>-0.5080771590812438</v>
       </c>
       <c r="AY44" t="n">
-        <v>-19.64053433208342</v>
+        <v>-19.64052806350488</v>
       </c>
       <c r="AZ44" t="b">
         <v>1</v>
@@ -20268,7 +20268,7 @@
         <v>-4.020742883737105</v>
       </c>
       <c r="AY47" t="n">
-        <v>-14.35606196730216</v>
+        <v>-14.3560541194689</v>
       </c>
       <c r="AZ47" t="b">
         <v>1</v>
@@ -20781,10 +20781,10 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>-0.5291042223046771</v>
       </c>
       <c r="AY50" t="n">
         <v>-15.4147281673955</v>
@@ -20800,7 +20800,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -20958,10 +20958,10 @@
         </is>
       </c>
       <c r="AW51" t="n">
-        <v>16.3700008392334</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="AX51" t="n">
-        <v>-14.84423417392992</v>
+        <v>-13.52358030617676</v>
       </c>
       <c r="AY51" t="n">
         <v>-34.85117715011583</v>
@@ -20977,7 +20977,7 @@
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-13.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -21308,14 +21308,14 @@
       <c r="AU53" t="inlineStr"/>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW53" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="AX53" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-0.6925190193304398</v>
       </c>
       <c r="AY53" t="n">
         <v>-27.87197279000151</v>
@@ -21331,7 +21331,7 @@
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>sem sinal (-0.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -22302,13 +22302,13 @@
         </is>
       </c>
       <c r="AW59" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="AX59" t="n">
-        <v>-3.506767262291599</v>
+        <v>-3.465848880756128</v>
       </c>
       <c r="AY59" t="n">
-        <v>-13.58724744836764</v>
+        <v>-13.55060950604702</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -22471,7 +22471,7 @@
       <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW60" t="n">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -22654,7 +22654,7 @@
         <v>-0.9501178501326923</v>
       </c>
       <c r="AY61" t="n">
-        <v>-14.40870028403989</v>
+        <v>-14.40870883002358</v>
       </c>
       <c r="AZ61" t="b">
         <v>1</v>
@@ -23996,7 +23996,7 @@
         <v>-1.302573977731003</v>
       </c>
       <c r="AY69" t="n">
-        <v>-15.92981174353384</v>
+        <v>-15.92983151621281</v>
       </c>
       <c r="AZ69" t="b">
         <v>0</v>
@@ -24163,10 +24163,10 @@
         </is>
       </c>
       <c r="AW70" t="n">
-        <v>76.08999633789062</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="AX70" t="n">
-        <v>0.2891329100952689</v>
+        <v>0.03932718901014098</v>
       </c>
       <c r="AY70" t="n">
         <v>-16.71033041805866</v>
@@ -24336,10 +24336,10 @@
         </is>
       </c>
       <c r="AW71" t="n">
-        <v>30.3700008392334</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="AX71" t="n">
-        <v>-7.770828268476048</v>
+        <v>-7.679630560276429</v>
       </c>
       <c r="AY71" t="n">
         <v>-20.69199954808616</v>
@@ -24355,7 +24355,7 @@
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24497,10 +24497,10 @@
         </is>
       </c>
       <c r="AW72" t="n">
-        <v>21.27000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="AX72" t="n">
-        <v>-1.316411286410224</v>
+        <v>-1.686185498450943</v>
       </c>
       <c r="AY72" t="n">
         <v>-23.79046311986899</v>
@@ -24516,7 +24516,7 @@
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-1.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -24664,10 +24664,10 @@
         </is>
       </c>
       <c r="AW73" t="n">
-        <v>4.070000171661377</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="AX73" t="n">
-        <v>-4.422605876297203</v>
+        <v>-2.506263268008835</v>
       </c>
       <c r="AY73" t="n">
         <v>-19.0219927402037</v>
@@ -24683,7 +24683,7 @@
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>sem sinal (-4.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24817,7 +24817,7 @@
       <c r="AU74" t="inlineStr"/>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW74" t="n">
@@ -24840,7 +24840,7 @@
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>sem sinal (-5.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.3% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -25332,7 +25332,7 @@
       <c r="AU77" t="inlineStr"/>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW77" t="n">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>sem sinal (-10.4% do topo; Lateral)</t>
+          <t>sem sinal (-10.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -26194,21 +26194,17 @@
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr"/>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU82" t="inlineStr"/>
       <c r="AV82" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW82" t="n">
-        <v>3.519999980926514</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.2840906397000742</v>
+        <v>-0.8426958391001382</v>
       </c>
       <c r="AY82" t="n">
         <v>-43.96825611876666</v>
@@ -26217,14 +26213,14 @@
         <v>0</v>
       </c>
       <c r="BA82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="b">
         <v>0</v>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -26262,7 +26258,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -26363,21 +26359,17 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr"/>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW83" t="n">
-        <v>21.85000038146973</v>
+        <v>22</v>
       </c>
       <c r="AX83" t="n">
-        <v>0.09153527420819874</v>
+        <v>-0.5909052762118283</v>
       </c>
       <c r="AY83" t="n">
         <v>-14.67030216407054</v>
@@ -26386,14 +26378,14 @@
         <v>0</v>
       </c>
       <c r="BA83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB83" t="b">
         <v>0</v>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -26543,10 +26535,10 @@
         </is>
       </c>
       <c r="AW84" t="n">
-        <v>60.54000091552734</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="AX84" t="n">
-        <v>-3.452263166470892</v>
+        <v>-3.944121234780862</v>
       </c>
       <c r="AY84" t="n">
         <v>-19.90956690277227</v>
@@ -26562,7 +26554,7 @@
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Alta)</t>
+          <t>sem sinal (-3.9% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -26863,10 +26855,10 @@
         </is>
       </c>
       <c r="AW86" t="n">
-        <v>0.1599999964237213</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>-5.882356034843117</v>
       </c>
       <c r="AY86" t="n">
         <v>-99.17440658744904</v>
@@ -26882,7 +26874,7 @@
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -27867,10 +27859,10 @@
         </is>
       </c>
       <c r="AW92" t="n">
-        <v>66.26999664306641</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="AX92" t="n">
-        <v>-3.561184420100938</v>
+        <v>-3.313159874831761</v>
       </c>
       <c r="AY92" t="n">
         <v>-5.76526078591314</v>
@@ -27886,7 +27878,7 @@
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Alta)</t>
+          <t>sem sinal (-3.3% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -28553,10 +28545,10 @@
         </is>
       </c>
       <c r="AW96" t="n">
-        <v>21.07999992370605</v>
+        <v>21.17000007629395</v>
       </c>
       <c r="AX96" t="n">
-        <v>-3.889941640379546</v>
+        <v>-4.298534927409481</v>
       </c>
       <c r="AY96" t="n">
         <v>-19.35852192104358</v>
@@ -28572,7 +28564,7 @@
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>sem sinal (-3.9% do topo; Lateral)</t>
+          <t>sem sinal (-4.3% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -29207,10 +29199,10 @@
         </is>
       </c>
       <c r="AW100" t="n">
-        <v>8.710000038146973</v>
+        <v>8.659999847412109</v>
       </c>
       <c r="AX100" t="n">
-        <v>-0.5740550001823053</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
         <v>-18.43808159694287</v>
@@ -29226,7 +29218,7 @@
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
+          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -29549,10 +29541,10 @@
         </is>
       </c>
       <c r="AW102" t="n">
-        <v>32.43999862670898</v>
+        <v>32.27000045776367</v>
       </c>
       <c r="AX102" t="n">
-        <v>-7.12083712617817</v>
+        <v>-6.631550252991147</v>
       </c>
       <c r="AY102" t="n">
         <v>-22.38033148894612</v>
@@ -29568,7 +29560,7 @@
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -32111,10 +32103,10 @@
         </is>
       </c>
       <c r="AW118" t="n">
-        <v>6.940000057220459</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="AX118" t="n">
-        <v>-15.99423810320502</v>
+        <v>-14.64128859693144</v>
       </c>
       <c r="AY118" t="n">
         <v>-57.6923074261264</v>
@@ -32130,7 +32122,7 @@
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>sem sinal (-16.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -32170,7 +32162,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -32277,21 +32269,17 @@
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="inlineStr"/>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU119" t="inlineStr"/>
       <c r="AV119" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW119" t="n">
-        <v>18.23999977111816</v>
+        <v>18.25</v>
       </c>
       <c r="AX119" t="n">
-        <v>0.05482581692610733</v>
+        <v>0</v>
       </c>
       <c r="AY119" t="n">
         <v>-14.11764705882353</v>
@@ -32300,14 +32288,14 @@
         <v>0</v>
       </c>
       <c r="BA119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="b">
         <v>0</v>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -32789,10 +32777,10 @@
         </is>
       </c>
       <c r="AW122" t="n">
-        <v>14.27999973297119</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="AX122" t="n">
-        <v>-1.120447131680857</v>
+        <v>-2.21606443298612</v>
       </c>
       <c r="AY122" t="n">
         <v>-18.51651739090506</v>
@@ -32808,7 +32796,7 @@
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -33709,10 +33697,10 @@
         </is>
       </c>
       <c r="AW128" t="n">
-        <v>0.3300000131130219</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="AX128" t="n">
-        <v>-15.15151816185063</v>
+        <v>-9.677419664956521</v>
       </c>
       <c r="AY128" t="n">
         <v>-80.5555562454241</v>
@@ -33728,7 +33716,7 @@
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>sem sinal (-15.2% do topo; Em Baixa)</t>
+          <t>sem sinal (-9.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -33874,7 +33862,7 @@
       <c r="AU129" t="inlineStr"/>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW129" t="n">
@@ -33897,7 +33885,7 @@
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Lateral)</t>
+          <t>sem sinal (-1.9% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -34202,10 +34190,10 @@
         </is>
       </c>
       <c r="AW131" t="n">
-        <v>12.31999969482422</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="AX131" t="n">
-        <v>-8.441558341027754</v>
+        <v>-8.367186446266416</v>
       </c>
       <c r="AY131" t="n">
         <v>-23.05593553629934</v>
@@ -34416,7 +34404,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -34451,7 +34439,7 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>51848818688</v>
+        <v>51957202944</v>
       </c>
       <c r="W133" t="n">
         <v>40.6</v>
@@ -34519,10 +34507,14 @@
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="inlineStr"/>
-      <c r="AU133" t="inlineStr"/>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW133" t="n">
@@ -34538,14 +34530,14 @@
         <v>0</v>
       </c>
       <c r="BA133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB133" t="b">
         <v>0</v>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>sem sinal (-0.0% do topo; Em Baixa)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34677,7 @@
         <v>-35.41666472641126</v>
       </c>
       <c r="AY134" t="n">
-        <v>-89.31034509690564</v>
+        <v>-89.16083867989796</v>
       </c>
       <c r="AZ134" t="b">
         <v>0</v>

--- a/reports/screener_2026-08-05.xlsx
+++ b/reports/screener_2026-08-05.xlsx
@@ -1377,7 +1377,7 @@
         <v>-14.41281066323299</v>
       </c>
       <c r="AY5" t="n">
-        <v>-39.50409545018086</v>
+        <v>-39.50409920702425</v>
       </c>
       <c r="AZ5" t="b">
         <v>1</v>
@@ -5521,7 +5521,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY29" t="n">
-        <v>-39.5192605242667</v>
+        <v>-39.51925229062647</v>
       </c>
       <c r="AZ29" t="b">
         <v>1</v>
@@ -6217,7 +6217,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY33" t="n">
-        <v>-12.46351675410393</v>
+        <v>-12.46352623832258</v>
       </c>
       <c r="AZ33" t="b">
         <v>1</v>
@@ -7955,7 +7955,7 @@
         <v>-0.5080771590812438</v>
       </c>
       <c r="AY43" t="n">
-        <v>-19.64052806350488</v>
+        <v>-19.64053433208342</v>
       </c>
       <c r="AZ43" t="b">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY54" t="n">
-        <v>-23.4739172343906</v>
+        <v>-23.47392377028176</v>
       </c>
       <c r="AZ54" t="b">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>-3.465848880756128</v>
       </c>
       <c r="AY58" t="n">
-        <v>-13.55060950604702</v>
+        <v>-13.55060269313266</v>
       </c>
       <c r="AZ58" t="b">
         <v>1</v>
@@ -10679,7 +10679,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY59" t="n">
-        <v>-50.51140559404919</v>
+        <v>-50.51140229842947</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -11206,7 +11206,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY62" t="n">
-        <v>-9.423154175560278</v>
+        <v>-9.423147674714317</v>
       </c>
       <c r="AZ62" t="b">
         <v>1</v>
@@ -12021,7 +12021,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY67" t="n">
-        <v>-23.22975619580519</v>
+        <v>-23.22976334700939</v>
       </c>
       <c r="AZ67" t="b">
         <v>1</v>
@@ -13012,7 +13012,7 @@
         <v>-14.41281066323299</v>
       </c>
       <c r="AY5" t="n">
-        <v>-39.50409545018086</v>
+        <v>-39.50409920702425</v>
       </c>
       <c r="AZ5" t="b">
         <v>1</v>
@@ -17323,7 +17323,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY30" t="n">
-        <v>-39.5192605242667</v>
+        <v>-39.51925229062647</v>
       </c>
       <c r="AZ30" t="b">
         <v>1</v>
@@ -18019,7 +18019,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY34" t="n">
-        <v>-12.46351675410393</v>
+        <v>-12.46352623832258</v>
       </c>
       <c r="AZ34" t="b">
         <v>1</v>
@@ -19757,7 +19757,7 @@
         <v>-0.5080771590812438</v>
       </c>
       <c r="AY44" t="n">
-        <v>-19.64052806350488</v>
+        <v>-19.64053433208342</v>
       </c>
       <c r="AZ44" t="b">
         <v>1</v>
@@ -21668,7 +21668,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY55" t="n">
-        <v>-23.4739172343906</v>
+        <v>-23.47392377028176</v>
       </c>
       <c r="AZ55" t="b">
         <v>1</v>
@@ -22308,7 +22308,7 @@
         <v>-3.465848880756128</v>
       </c>
       <c r="AY59" t="n">
-        <v>-13.55060950604702</v>
+        <v>-13.55060269313266</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -22481,7 +22481,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY60" t="n">
-        <v>-50.51140559404919</v>
+        <v>-50.51140229842947</v>
       </c>
       <c r="AZ60" t="b">
         <v>1</v>
@@ -23008,7 +23008,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY63" t="n">
-        <v>-9.423154175560278</v>
+        <v>-9.423147674714317</v>
       </c>
       <c r="AZ63" t="b">
         <v>1</v>
@@ -23823,7 +23823,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY68" t="n">
-        <v>-23.22975619580519</v>
+        <v>-23.22976334700939</v>
       </c>
       <c r="AZ68" t="b">
         <v>1</v>
@@ -23996,7 +23996,7 @@
         <v>-1.302573977731003</v>
       </c>
       <c r="AY69" t="n">
-        <v>-15.92983151621281</v>
+        <v>-15.92982162987447</v>
       </c>
       <c r="AZ69" t="b">
         <v>0</v>
@@ -24163,10 +24163,10 @@
         </is>
       </c>
       <c r="AW70" t="n">
-        <v>76.27999877929688</v>
+        <v>76.08999633789062</v>
       </c>
       <c r="AX70" t="n">
-        <v>0.03932718901014098</v>
+        <v>0.2891329100952689</v>
       </c>
       <c r="AY70" t="n">
         <v>-16.71033041805866</v>
@@ -24827,7 +24827,7 @@
         <v>-5.326373076856417</v>
       </c>
       <c r="AY74" t="n">
-        <v>-15.96621334750062</v>
+        <v>-15.96620814657582</v>
       </c>
       <c r="AZ74" t="b">
         <v>0</v>
@@ -25865,7 +25865,7 @@
         <v>0.1575335373968034</v>
       </c>
       <c r="AY80" t="n">
-        <v>-33.331611084974</v>
+        <v>-33.33160558679006</v>
       </c>
       <c r="AZ80" t="b">
         <v>0</v>
@@ -28382,7 +28382,7 @@
         <v>4.274930948545386</v>
       </c>
       <c r="AY95" t="n">
-        <v>-23.65887805399658</v>
+        <v>-23.6588689925551</v>
       </c>
       <c r="AZ95" t="b">
         <v>0</v>

--- a/reports/screener_2026-08-05.xlsx
+++ b/reports/screener_2026-08-05.xlsx
@@ -1182,7 +1182,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista do papel VLID3 revela uma sólida relação de qualidade e preço, uma vez que sua rentabilidade medida</t>
+        </is>
+      </c>
       <c r="AU4" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -1371,13 +1375,13 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>5.619999885559082</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="AX5" t="n">
-        <v>-14.41281066323299</v>
+        <v>-14.71631105238386</v>
       </c>
       <c r="AY5" t="n">
-        <v>-39.50409920702425</v>
+        <v>-39.50409545018086</v>
       </c>
       <c r="AZ5" t="b">
         <v>1</v>
@@ -1390,7 +1394,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1705,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>insider selling (Yes). Criteria met: 2 of 6.
+    *   *Technical/Trend*: Pivot de</t>
+        </is>
+      </c>
       <c r="AU7" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -2059,10 +2068,10 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>18.85000038146973</v>
+        <v>19.21999931335449</v>
       </c>
       <c r="AX9" t="n">
-        <v>-14.90715866883865</v>
+        <v>-16.54525760371704</v>
       </c>
       <c r="AY9" t="n">
         <v>-54.13720844041888</v>
@@ -2078,7 +2087,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2410,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da TGMA3 revela uma empresa de alta qualidade operacional que combina forte rentabilidade com endivid</t>
+        </is>
+      </c>
       <c r="AU11" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -2409,7 +2422,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW11" t="n">
@@ -2763,7 +2776,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -2773,7 +2786,7 @@
         <v>-3.612203515041446</v>
       </c>
       <c r="AY13" t="n">
-        <v>-22.77636138240788</v>
+        <v>-22.7763666994001</v>
       </c>
       <c r="AZ13" t="b">
         <v>1</v>
@@ -2786,7 +2799,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Lateral)</t>
+          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2944,10 +2957,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>12.72999954223633</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>-12.4901748318072</v>
+        <v>-14.30768966674805</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -2963,7 +2976,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3117,10 +3130,10 @@
         </is>
       </c>
       <c r="AW15" t="n">
-        <v>43.41999816894531</v>
+        <v>43.04999923706055</v>
       </c>
       <c r="AX15" t="n">
-        <v>-2.118835116863982</v>
+        <v>-1.277582454837922</v>
       </c>
       <c r="AY15" t="n">
         <v>-13.54395936495905</v>
@@ -3136,7 +3149,7 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>sem sinal (-2.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.3% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3464,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
+        </is>
+      </c>
       <c r="AU17" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -3996,7 +4013,7 @@
         <v>-4.338697601218778</v>
       </c>
       <c r="AY20" t="n">
-        <v>-21.08023573257425</v>
+        <v>-21.08022686888683</v>
       </c>
       <c r="AZ20" t="b">
         <v>1</v>
@@ -4336,10 +4353,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>49.04000091552734</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.814843745989081</v>
+        <v>-1.129361865388501</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -4355,7 +4372,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.8% do topo; Em Alta)</t>
+          <t>sem sinal (-1.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4868,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da FESA4 revela um cenário de baixa rentabilidade e contração operacional, evidenciado pelo RO</t>
+        </is>
+      </c>
       <c r="AU25" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -5036,10 +5057,10 @@
         </is>
       </c>
       <c r="AW26" t="n">
-        <v>6.550000190734863</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="AX26" t="n">
-        <v>-3.053439393562163</v>
+        <v>-3.49544105988292</v>
       </c>
       <c r="AY26" t="n">
         <v>-39.52381043207078</v>
@@ -5055,7 +5076,7 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5226,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>Yes, Net Debt/EBITDA &lt; 3 and &lt;= sector: n/d, market cap &gt;= 300</t>
+        </is>
+      </c>
       <c r="AU27" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -5521,7 +5546,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY29" t="n">
-        <v>-39.51925229062647</v>
+        <v>-39.5192605242667</v>
       </c>
       <c r="AZ29" t="b">
         <v>1</v>
@@ -5676,7 +5701,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>4. Correlate indicators (not just list them)? Yes.
+        5. Position each indicator vs. sector average</t>
+        </is>
+      </c>
       <c r="AU30" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -6034,7 +6064,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>0m: Yes, no insider selling: No).
+    *   *Technical*: Breakout (Rompimento),</t>
+        </is>
+      </c>
       <c r="AU32" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -6217,7 +6252,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY33" t="n">
-        <v>-12.46352623832258</v>
+        <v>-12.46351675410393</v>
       </c>
       <c r="AZ33" t="b">
         <v>1</v>
@@ -6376,7 +6411,7 @@
       <c r="AU34" t="inlineStr"/>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW34" t="n">
@@ -6399,7 +6434,7 @@
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Lateral)</t>
+          <t>sem sinal (-2.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -6726,10 +6761,10 @@
         </is>
       </c>
       <c r="AW36" t="n">
-        <v>29.73999977111816</v>
+        <v>29.75</v>
       </c>
       <c r="AX36" t="n">
-        <v>-2.252858377438904</v>
+        <v>-2.285715311515235</v>
       </c>
       <c r="AY36" t="n">
         <v>-17.59775069846685</v>
@@ -6903,10 +6938,10 @@
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>2.329999923706055</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="AX37" t="n">
-        <v>-3.004289078750577</v>
+        <v>-3.418800283779255</v>
       </c>
       <c r="AY37" t="n">
         <v>-52.18694930098489</v>
@@ -6922,7 +6957,7 @@
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7076,10 +7111,10 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>4.03000020980835</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="AX38" t="n">
-        <v>-1.98511558212644</v>
+        <v>-0.7537681217588132</v>
       </c>
       <c r="AY38" t="n">
         <v>-47.92224740248528</v>
@@ -7095,7 +7130,7 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-2.0% do topo; Lateral)</t>
+          <t>sem sinal (-0.8% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8318,11 @@
           <t>próxima</t>
         </is>
       </c>
-      <c r="AT45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>setor Não, Dív.Líq/EBITDA n/d, sem venda de insiders Não).</t>
+        </is>
+      </c>
       <c r="AU45" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -8466,7 +8505,7 @@
         <v>-4.020742883737105</v>
       </c>
       <c r="AY46" t="n">
-        <v>-14.3560541194689</v>
+        <v>-14.35606196730216</v>
       </c>
       <c r="AZ46" t="b">
         <v>1</v>
@@ -8794,7 +8833,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista do papel BBSE3 revela uma empresa de altíssima rentabilidade sobre o patrimônio líquido, com</t>
+        </is>
+      </c>
       <c r="AU48" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -8979,10 +9022,10 @@
         </is>
       </c>
       <c r="AW49" t="n">
-        <v>11.34000015258789</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="AX49" t="n">
-        <v>-0.5291042223046771</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
         <v>-15.4147281673955</v>
@@ -8998,7 +9041,7 @@
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>sem sinal (-0.5% do topo; Em Alta)</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9156,10 +9199,10 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>16.1200008392334</v>
+        <v>16.3700008392334</v>
       </c>
       <c r="AX50" t="n">
-        <v>-13.52358030617676</v>
+        <v>-14.84423417392992</v>
       </c>
       <c r="AY50" t="n">
         <v>-34.85117715011583</v>
@@ -9175,7 +9218,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (-13.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9506,14 +9549,14 @@
       <c r="AU52" t="inlineStr"/>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW52" t="n">
-        <v>43.31999969482422</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="AX52" t="n">
-        <v>-0.6925190193304398</v>
+        <v>-0.1856102533401627</v>
       </c>
       <c r="AY52" t="n">
         <v>-27.87197279000151</v>
@@ -9529,7 +9572,7 @@
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>sem sinal (-0.7% do topo; Em Alta)</t>
+          <t>sem sinal (-0.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -9550,13 +9593,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>54.28</v>
+        <v>54.17</v>
       </c>
       <c r="E53" t="n">
         <v>78.66</v>
       </c>
       <c r="F53" t="n">
-        <v>22.82</v>
+        <v>22.48</v>
       </c>
       <c r="G53" t="n">
         <v>55.48</v>
@@ -9632,7 +9675,7 @@
         <v>0.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="AG53" t="n">
         <v>15.86999988555908</v>
@@ -10025,7 +10068,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>Liq/EBITDA (n/d), market cap &gt;= 300mi (Yes), no insider selling</t>
+        </is>
+      </c>
       <c r="AU55" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -10500,13 +10547,13 @@
         </is>
       </c>
       <c r="AW58" t="n">
-        <v>43.61150741577148</v>
+        <v>43.63000106811523</v>
       </c>
       <c r="AX58" t="n">
-        <v>-3.465848880756128</v>
+        <v>-3.506767262291599</v>
       </c>
       <c r="AY58" t="n">
-        <v>-13.55060269313266</v>
+        <v>-13.58724744836764</v>
       </c>
       <c r="AZ58" t="b">
         <v>1</v>
@@ -10669,7 +10716,7 @@
       <c r="AU59" t="inlineStr"/>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW59" t="n">
@@ -10679,7 +10726,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY59" t="n">
-        <v>-50.51140229842947</v>
+        <v>-50.51140559404919</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -10692,7 +10739,7 @@
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Lateral)</t>
+          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11253,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY62" t="n">
-        <v>-9.423147674714317</v>
+        <v>-9.423154175560278</v>
       </c>
       <c r="AZ62" t="b">
         <v>1</v>
@@ -11490,7 +11537,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>Selic, ROIC&gt;=sector, margin&gt;=15%, CAGR&gt;=sector).
+    *   *Technical/Trend*:</t>
+        </is>
+      </c>
       <c r="AU64" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -12021,7 +12073,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY67" t="n">
-        <v>-23.22976334700939</v>
+        <v>-23.22977049821228</v>
       </c>
       <c r="AZ67" t="b">
         <v>1</v>
@@ -12817,7 +12869,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista do papel VLID3 revela uma sólida relação de qualidade e preço, uma vez que sua rentabilidade medida</t>
+        </is>
+      </c>
       <c r="AU4" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -13006,13 +13062,13 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>5.619999885559082</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="AX5" t="n">
-        <v>-14.41281066323299</v>
+        <v>-14.71631105238386</v>
       </c>
       <c r="AY5" t="n">
-        <v>-39.50409920702425</v>
+        <v>-39.50409545018086</v>
       </c>
       <c r="AZ5" t="b">
         <v>1</v>
@@ -13025,7 +13081,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13392,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>insider selling (Yes). Criteria met: 2 of 6.
+    *   *Technical/Trend*: Pivot de</t>
+        </is>
+      </c>
       <c r="AU7" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -13694,10 +13755,10 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>18.85000038146973</v>
+        <v>19.21999931335449</v>
       </c>
       <c r="AX9" t="n">
-        <v>-14.90715866883865</v>
+        <v>-16.54525760371704</v>
       </c>
       <c r="AY9" t="n">
         <v>-54.13720844041888</v>
@@ -13713,7 +13774,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14097,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da TGMA3 revela uma empresa de alta qualidade operacional que combina forte rentabilidade com endivid</t>
+        </is>
+      </c>
       <c r="AU11" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -14044,7 +14109,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW11" t="n">
@@ -14398,7 +14463,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -14408,7 +14473,7 @@
         <v>-3.612203515041446</v>
       </c>
       <c r="AY13" t="n">
-        <v>-22.77636138240788</v>
+        <v>-22.7763666994001</v>
       </c>
       <c r="AZ13" t="b">
         <v>1</v>
@@ -14421,7 +14486,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Lateral)</t>
+          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14579,10 +14644,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>12.72999954223633</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>-12.4901748318072</v>
+        <v>-14.30768966674805</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -14598,7 +14663,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14752,10 +14817,10 @@
         </is>
       </c>
       <c r="AW15" t="n">
-        <v>43.41999816894531</v>
+        <v>43.04999923706055</v>
       </c>
       <c r="AX15" t="n">
-        <v>-2.118835116863982</v>
+        <v>-1.277582454837922</v>
       </c>
       <c r="AY15" t="n">
         <v>-13.54395936495905</v>
@@ -14771,7 +14836,7 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>sem sinal (-2.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.3% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15151,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
+        </is>
+      </c>
       <c r="AU17" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -15631,7 +15700,7 @@
         <v>-4.338697601218778</v>
       </c>
       <c r="AY20" t="n">
-        <v>-21.08023573257425</v>
+        <v>-21.08022686888683</v>
       </c>
       <c r="AZ20" t="b">
         <v>1</v>
@@ -15971,10 +16040,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>49.04000091552734</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.814843745989081</v>
+        <v>-1.129361865388501</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -15990,7 +16059,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.8% do topo; Em Alta)</t>
+          <t>sem sinal (-1.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -16653,7 +16722,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da FESA4 revela um cenário de baixa rentabilidade e contração operacional, evidenciado pelo RO</t>
+        </is>
+      </c>
       <c r="AU26" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -16838,10 +16911,10 @@
         </is>
       </c>
       <c r="AW27" t="n">
-        <v>6.550000190734863</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="AX27" t="n">
-        <v>-3.053439393562163</v>
+        <v>-3.49544105988292</v>
       </c>
       <c r="AY27" t="n">
         <v>-39.52381043207078</v>
@@ -16857,7 +16930,7 @@
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17080,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>Yes, Net Debt/EBITDA &lt; 3 and &lt;= sector: n/d, market cap &gt;= 300</t>
+        </is>
+      </c>
       <c r="AU28" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -17323,7 +17400,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY30" t="n">
-        <v>-39.51925229062647</v>
+        <v>-39.5192605242667</v>
       </c>
       <c r="AZ30" t="b">
         <v>1</v>
@@ -17478,7 +17555,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>4. Correlate indicators (not just list them)? Yes.
+        5. Position each indicator vs. sector average</t>
+        </is>
+      </c>
       <c r="AU31" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -17836,7 +17918,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>0m: Yes, no insider selling: No).
+    *   *Technical*: Breakout (Rompimento),</t>
+        </is>
+      </c>
       <c r="AU33" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -18019,7 +18106,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY34" t="n">
-        <v>-12.46352623832258</v>
+        <v>-12.46351675410393</v>
       </c>
       <c r="AZ34" t="b">
         <v>1</v>
@@ -18178,7 +18265,7 @@
       <c r="AU35" t="inlineStr"/>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW35" t="n">
@@ -18201,7 +18288,7 @@
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Lateral)</t>
+          <t>sem sinal (-2.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -18528,10 +18615,10 @@
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>29.73999977111816</v>
+        <v>29.75</v>
       </c>
       <c r="AX37" t="n">
-        <v>-2.252858377438904</v>
+        <v>-2.285715311515235</v>
       </c>
       <c r="AY37" t="n">
         <v>-17.59775069846685</v>
@@ -18705,10 +18792,10 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>2.329999923706055</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="AX38" t="n">
-        <v>-3.004289078750577</v>
+        <v>-3.418800283779255</v>
       </c>
       <c r="AY38" t="n">
         <v>-52.18694930098489</v>
@@ -18724,7 +18811,7 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -18878,10 +18965,10 @@
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>4.03000020980835</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="AX39" t="n">
-        <v>-1.98511558212644</v>
+        <v>-0.7537681217588132</v>
       </c>
       <c r="AY39" t="n">
         <v>-47.92224740248528</v>
@@ -18897,7 +18984,7 @@
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>sem sinal (-2.0% do topo; Lateral)</t>
+          <t>sem sinal (-0.8% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -20085,7 +20172,11 @@
           <t>próxima</t>
         </is>
       </c>
-      <c r="AT46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>setor Não, Dív.Líq/EBITDA n/d, sem venda de insiders Não).</t>
+        </is>
+      </c>
       <c r="AU46" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -20268,7 +20359,7 @@
         <v>-4.020742883737105</v>
       </c>
       <c r="AY47" t="n">
-        <v>-14.3560541194689</v>
+        <v>-14.35606196730216</v>
       </c>
       <c r="AZ47" t="b">
         <v>1</v>
@@ -20596,7 +20687,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista do papel BBSE3 revela uma empresa de altíssima rentabilidade sobre o patrimônio líquido, com</t>
+        </is>
+      </c>
       <c r="AU49" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -20781,10 +20876,10 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>11.34000015258789</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="AX50" t="n">
-        <v>-0.5291042223046771</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
         <v>-15.4147281673955</v>
@@ -20800,7 +20895,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (-0.5% do topo; Em Alta)</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -20958,10 +21053,10 @@
         </is>
       </c>
       <c r="AW51" t="n">
-        <v>16.1200008392334</v>
+        <v>16.3700008392334</v>
       </c>
       <c r="AX51" t="n">
-        <v>-13.52358030617676</v>
+        <v>-14.84423417392992</v>
       </c>
       <c r="AY51" t="n">
         <v>-34.85117715011583</v>
@@ -20977,7 +21072,7 @@
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>sem sinal (-13.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -21308,14 +21403,14 @@
       <c r="AU53" t="inlineStr"/>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW53" t="n">
-        <v>43.31999969482422</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="AX53" t="n">
-        <v>-0.6925190193304398</v>
+        <v>-0.1856102533401627</v>
       </c>
       <c r="AY53" t="n">
         <v>-27.87197279000151</v>
@@ -21331,7 +21426,7 @@
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>sem sinal (-0.7% do topo; Em Alta)</t>
+          <t>sem sinal (-0.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -21352,13 +21447,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>54.28</v>
+        <v>54.17</v>
       </c>
       <c r="E54" t="n">
         <v>78.66</v>
       </c>
       <c r="F54" t="n">
-        <v>22.82</v>
+        <v>22.48</v>
       </c>
       <c r="G54" t="n">
         <v>55.48</v>
@@ -21434,7 +21529,7 @@
         <v>0.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="AG54" t="n">
         <v>15.86999988555908</v>
@@ -21827,7 +21922,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>Liq/EBITDA (n/d), market cap &gt;= 300mi (Yes), no insider selling</t>
+        </is>
+      </c>
       <c r="AU56" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -22302,13 +22401,13 @@
         </is>
       </c>
       <c r="AW59" t="n">
-        <v>43.61150741577148</v>
+        <v>43.63000106811523</v>
       </c>
       <c r="AX59" t="n">
-        <v>-3.465848880756128</v>
+        <v>-3.506767262291599</v>
       </c>
       <c r="AY59" t="n">
-        <v>-13.55060269313266</v>
+        <v>-13.58724744836764</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -22471,7 +22570,7 @@
       <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW60" t="n">
@@ -22481,7 +22580,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY60" t="n">
-        <v>-50.51140229842947</v>
+        <v>-50.51140559404919</v>
       </c>
       <c r="AZ60" t="b">
         <v>1</v>
@@ -22494,7 +22593,7 @@
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Lateral)</t>
+          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -23008,7 +23107,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY63" t="n">
-        <v>-9.423147674714317</v>
+        <v>-9.423154175560278</v>
       </c>
       <c r="AZ63" t="b">
         <v>1</v>
@@ -23292,7 +23391,12 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>Selic, ROIC&gt;=sector, margin&gt;=15%, CAGR&gt;=sector).
+    *   *Technical/Trend*:</t>
+        </is>
+      </c>
       <c r="AU65" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -23823,7 +23927,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY68" t="n">
-        <v>-23.22976334700939</v>
+        <v>-23.22977049821228</v>
       </c>
       <c r="AZ68" t="b">
         <v>1</v>
@@ -23996,7 +24100,7 @@
         <v>-1.302573977731003</v>
       </c>
       <c r="AY69" t="n">
-        <v>-15.92982162987447</v>
+        <v>-15.92983151621281</v>
       </c>
       <c r="AZ69" t="b">
         <v>0</v>
@@ -24336,10 +24440,10 @@
         </is>
       </c>
       <c r="AW71" t="n">
-        <v>30.34000015258789</v>
+        <v>30.3700008392334</v>
       </c>
       <c r="AX71" t="n">
-        <v>-7.679630560276429</v>
+        <v>-7.770828268476048</v>
       </c>
       <c r="AY71" t="n">
         <v>-20.69199954808616</v>
@@ -24355,7 +24459,7 @@
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>sem sinal (-7.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24497,10 +24601,10 @@
         </is>
       </c>
       <c r="AW72" t="n">
-        <v>21.35000038146973</v>
+        <v>21.27000045776367</v>
       </c>
       <c r="AX72" t="n">
-        <v>-1.686185498450943</v>
+        <v>-1.316411286410224</v>
       </c>
       <c r="AY72" t="n">
         <v>-23.79046311986899</v>
@@ -24516,7 +24620,7 @@
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>sem sinal (-1.7% do topo; Em Alta)</t>
+          <t>sem sinal (-1.3% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -24664,10 +24768,10 @@
         </is>
       </c>
       <c r="AW73" t="n">
-        <v>3.990000009536743</v>
+        <v>4.070000171661377</v>
       </c>
       <c r="AX73" t="n">
-        <v>-2.506263268008835</v>
+        <v>-4.422605876297203</v>
       </c>
       <c r="AY73" t="n">
         <v>-19.0219927402037</v>
@@ -24683,7 +24787,7 @@
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24817,7 +24921,7 @@
       <c r="AU74" t="inlineStr"/>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW74" t="n">
@@ -24840,7 +24944,7 @@
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>sem sinal (-5.3% do topo; Lateral)</t>
+          <t>sem sinal (-5.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -25034,13 +25138,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>47.85</v>
+        <v>47.96</v>
       </c>
       <c r="E76" t="n">
         <v>36.84</v>
       </c>
       <c r="F76" t="n">
-        <v>40.76</v>
+        <v>41.11</v>
       </c>
       <c r="G76" t="n">
         <v>87.51000000000001</v>
@@ -25332,7 +25436,7 @@
       <c r="AU77" t="inlineStr"/>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW77" t="n">
@@ -25355,7 +25459,7 @@
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>sem sinal (-10.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-10.4% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25969,7 @@
         <v>0.1575335373968034</v>
       </c>
       <c r="AY80" t="n">
-        <v>-33.33160558679006</v>
+        <v>-33.331611084974</v>
       </c>
       <c r="AZ80" t="b">
         <v>0</v>
@@ -26087,7 +26191,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -26194,17 +26298,21 @@
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr"/>
-      <c r="AU82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW82" t="n">
-        <v>3.559999942779541</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="AX82" t="n">
-        <v>-0.8426958391001382</v>
+        <v>0.2840906397000742</v>
       </c>
       <c r="AY82" t="n">
         <v>-43.96825611876666</v>
@@ -26213,14 +26321,14 @@
         <v>0</v>
       </c>
       <c r="BA82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB82" t="b">
         <v>0</v>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Em Alta)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -26258,7 +26366,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -26359,17 +26467,21 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr"/>
-      <c r="AU83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW83" t="n">
-        <v>22</v>
+        <v>21.85000038146973</v>
       </c>
       <c r="AX83" t="n">
-        <v>-0.5909052762118283</v>
+        <v>0.09153527420819874</v>
       </c>
       <c r="AY83" t="n">
         <v>-14.67030216407054</v>
@@ -26378,14 +26490,14 @@
         <v>0</v>
       </c>
       <c r="BA83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB83" t="b">
         <v>0</v>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -26535,10 +26647,10 @@
         </is>
       </c>
       <c r="AW84" t="n">
-        <v>60.84999847412109</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="AX84" t="n">
-        <v>-3.944121234780862</v>
+        <v>-3.452263166470892</v>
       </c>
       <c r="AY84" t="n">
         <v>-19.90956690277227</v>
@@ -26554,7 +26666,7 @@
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>sem sinal (-3.9% do topo; Em Alta)</t>
+          <t>sem sinal (-3.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -26855,10 +26967,10 @@
         </is>
       </c>
       <c r="AW86" t="n">
-        <v>0.1700000017881393</v>
+        <v>0.1599999964237213</v>
       </c>
       <c r="AX86" t="n">
-        <v>-5.882356034843117</v>
+        <v>0</v>
       </c>
       <c r="AY86" t="n">
         <v>-99.17440658744904</v>
@@ -26874,7 +26986,7 @@
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>sem sinal (-5.9% do topo; Em Baixa)</t>
+          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -27859,10 +27971,10 @@
         </is>
       </c>
       <c r="AW92" t="n">
-        <v>66.09999847412109</v>
+        <v>66.26999664306641</v>
       </c>
       <c r="AX92" t="n">
-        <v>-3.313159874831761</v>
+        <v>-3.561184420100938</v>
       </c>
       <c r="AY92" t="n">
         <v>-5.76526078591314</v>
@@ -27878,7 +27990,7 @@
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>sem sinal (-3.3% do topo; Em Alta)</t>
+          <t>sem sinal (-3.6% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -28382,7 +28494,7 @@
         <v>4.274930948545386</v>
       </c>
       <c r="AY95" t="n">
-        <v>-23.6588689925551</v>
+        <v>-23.65887805399658</v>
       </c>
       <c r="AZ95" t="b">
         <v>0</v>
@@ -28545,10 +28657,10 @@
         </is>
       </c>
       <c r="AW96" t="n">
-        <v>21.17000007629395</v>
+        <v>21.07999992370605</v>
       </c>
       <c r="AX96" t="n">
-        <v>-4.298534927409481</v>
+        <v>-3.889941640379546</v>
       </c>
       <c r="AY96" t="n">
         <v>-19.35852192104358</v>
@@ -28564,7 +28676,7 @@
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>sem sinal (-4.3% do topo; Lateral)</t>
+          <t>sem sinal (-3.9% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -29199,10 +29311,10 @@
         </is>
       </c>
       <c r="AW100" t="n">
-        <v>8.659999847412109</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>-0.5740550001823053</v>
       </c>
       <c r="AY100" t="n">
         <v>-18.43808159694287</v>
@@ -29218,7 +29330,7 @@
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -29541,10 +29653,10 @@
         </is>
       </c>
       <c r="AW102" t="n">
-        <v>32.27000045776367</v>
+        <v>32.43999862670898</v>
       </c>
       <c r="AX102" t="n">
-        <v>-6.631550252991147</v>
+        <v>-7.12083712617817</v>
       </c>
       <c r="AY102" t="n">
         <v>-22.38033148894612</v>
@@ -29560,7 +29672,7 @@
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>sem sinal (-6.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -32103,10 +32215,10 @@
         </is>
       </c>
       <c r="AW118" t="n">
-        <v>6.829999923706055</v>
+        <v>6.940000057220459</v>
       </c>
       <c r="AX118" t="n">
-        <v>-14.64128859693144</v>
+        <v>-15.99423810320502</v>
       </c>
       <c r="AY118" t="n">
         <v>-57.6923074261264</v>
@@ -32122,7 +32234,7 @@
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>sem sinal (-14.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-16.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -32162,7 +32274,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -32269,17 +32381,21 @@
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="inlineStr"/>
-      <c r="AU119" t="inlineStr"/>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AV119" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW119" t="n">
-        <v>18.25</v>
+        <v>18.23999977111816</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>0.05482581692610733</v>
       </c>
       <c r="AY119" t="n">
         <v>-14.11764705882353</v>
@@ -32288,14 +32404,14 @@
         <v>0</v>
       </c>
       <c r="BA119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB119" t="b">
         <v>0</v>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Alta)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -32777,10 +32893,10 @@
         </is>
       </c>
       <c r="AW122" t="n">
-        <v>14.4399995803833</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="AX122" t="n">
-        <v>-2.21606443298612</v>
+        <v>-1.120447131680857</v>
       </c>
       <c r="AY122" t="n">
         <v>-18.51651739090506</v>
@@ -32796,7 +32912,7 @@
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Em Alta)</t>
+          <t>sem sinal (-1.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -33697,10 +33813,10 @@
         </is>
       </c>
       <c r="AW128" t="n">
-        <v>0.3100000023841858</v>
+        <v>0.3300000131130219</v>
       </c>
       <c r="AX128" t="n">
-        <v>-9.677419664956521</v>
+        <v>-15.15151816185063</v>
       </c>
       <c r="AY128" t="n">
         <v>-80.5555562454241</v>
@@ -33716,7 +33832,7 @@
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>sem sinal (-9.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-15.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -33862,7 +33978,7 @@
       <c r="AU129" t="inlineStr"/>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW129" t="n">
@@ -33885,7 +34001,7 @@
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Em Alta)</t>
+          <t>sem sinal (-1.9% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -34190,10 +34306,10 @@
         </is>
       </c>
       <c r="AW131" t="n">
-        <v>12.3100004196167</v>
+        <v>12.31999969482422</v>
       </c>
       <c r="AX131" t="n">
-        <v>-8.367186446266416</v>
+        <v>-8.441558341027754</v>
       </c>
       <c r="AY131" t="n">
         <v>-23.05593553629934</v>
@@ -34404,7 +34520,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -34439,7 +34555,7 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>51957202944</v>
+        <v>51848818688</v>
       </c>
       <c r="W133" t="n">
         <v>40.6</v>
@@ -34507,14 +34623,10 @@
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="inlineStr"/>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="AU133" t="inlineStr"/>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW133" t="n">
@@ -34530,14 +34642,14 @@
         <v>0</v>
       </c>
       <c r="BA133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB133" t="b">
         <v>0</v>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (-0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -34677,7 +34789,7 @@
         <v>-35.41666472641126</v>
       </c>
       <c r="AY134" t="n">
-        <v>-89.16083867989796</v>
+        <v>-89.31034509690564</v>
       </c>
       <c r="AZ134" t="b">
         <v>0</v>

--- a/reports/screener_2026-08-05.xlsx
+++ b/reports/screener_2026-08-05.xlsx
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.48999999999999</v>
+        <v>72.45</v>
       </c>
       <c r="E5" t="n">
         <v>81.05</v>
       </c>
       <c r="F5" t="n">
-        <v>58.25</v>
+        <v>58.1</v>
       </c>
       <c r="G5" t="n">
         <v>61.1</v>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69.66</v>
+        <v>69.61</v>
       </c>
       <c r="E11" t="n">
         <v>79.12</v>
       </c>
       <c r="F11" t="n">
-        <v>38.97</v>
+        <v>38.8</v>
       </c>
       <c r="G11" t="n">
         <v>84.34</v>
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69.23999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="E12" t="n">
         <v>90.51000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>35.51</v>
+        <v>35.34</v>
       </c>
       <c r="G12" t="n">
         <v>65.79000000000001</v>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68.70999999999999</v>
+        <v>68.64</v>
       </c>
       <c r="E13" t="n">
         <v>83.66</v>
       </c>
       <c r="F13" t="n">
-        <v>57.75</v>
+        <v>57.52</v>
       </c>
       <c r="G13" t="n">
         <v>63.93</v>
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.5</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>54.93</v>
       </c>
       <c r="F14" t="n">
-        <v>56.87</v>
+        <v>56.73</v>
       </c>
       <c r="G14" t="n">
         <v>92.98999999999999</v>
@@ -3321,44 +3321,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INTB3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66.77</v>
+        <v>66.72</v>
       </c>
       <c r="E17" t="n">
-        <v>72.69</v>
+        <v>61.42</v>
       </c>
       <c r="F17" t="n">
-        <v>40.83</v>
+        <v>53.27</v>
       </c>
       <c r="G17" t="n">
-        <v>88</v>
+        <v>80.89</v>
       </c>
       <c r="H17" t="n">
-        <v>76.52</v>
+        <v>87.12</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -3373,10 +3373,10 @@
         <v>1</v>
       </c>
       <c r="P17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -3386,77 +3386,73 @@
         <v>1</v>
       </c>
       <c r="U17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4914711040</v>
+        <v>7821505536</v>
       </c>
       <c r="W17" t="n">
-        <v>8.25</v>
+        <v>4.9</v>
       </c>
       <c r="X17" t="n">
-        <v>1.49</v>
+        <v>0.91</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>10.83</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.07</v>
+        <v>18.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>17.52</v>
+        <v>6.91</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.1</v>
+        <v>20.76</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
-        <v>2.64</v>
+        <v>3.78</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.58</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>15.02000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="AH17" t="n">
-        <v>20.03</v>
+        <v>38.54</v>
       </c>
       <c r="AI17" t="n">
-        <v>15.44</v>
+        <v>23.46</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23.39</v>
+        <v>44.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>40.6</v>
-      </c>
+        <v>47.96</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
-        <v>23.96</v>
+        <v>38.54</v>
       </c>
       <c r="AN17" t="n">
-        <v>20.32</v>
+        <v>41.37</v>
       </c>
       <c r="AO17" t="n">
-        <v>35.29</v>
+        <v>93.78</v>
       </c>
       <c r="AP17" t="n">
-        <v>59.49</v>
+        <v>80.52</v>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3464,86 +3460,78 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW17" t="n">
-        <v>14.38436412811279</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.418939370483477</v>
+        <v>-7.012189752619536</v>
       </c>
       <c r="AY17" t="n">
-        <v>-4.081037600189341</v>
+        <v>-40.71938764311017</v>
       </c>
       <c r="AZ17" t="b">
         <v>1</v>
       </c>
       <c r="BA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-7.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>INTB3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66.72</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>61.42</v>
+        <v>72.69</v>
       </c>
       <c r="F18" t="n">
-        <v>53.27</v>
+        <v>40.62</v>
       </c>
       <c r="G18" t="n">
-        <v>80.89</v>
+        <v>88</v>
       </c>
       <c r="H18" t="n">
-        <v>87.12</v>
+        <v>76.52</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -3558,10 +3546,10 @@
         <v>1</v>
       </c>
       <c r="P18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -3571,73 +3559,77 @@
         <v>1</v>
       </c>
       <c r="U18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>7821505536</v>
+        <v>4914711040</v>
       </c>
       <c r="W18" t="n">
-        <v>4.9</v>
+        <v>8.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0.91</v>
+        <v>1.49</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.83</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.6</v>
+        <v>18.07</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.91</v>
+        <v>17.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>20.76</v>
+        <v>13.1</v>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>3.78</v>
+        <v>2.64</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>0.26</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.58</v>
+      </c>
       <c r="AG18" t="n">
-        <v>21.35000038146973</v>
+        <v>15.02000045776367</v>
       </c>
       <c r="AH18" t="n">
-        <v>38.54</v>
+        <v>20.03</v>
       </c>
       <c r="AI18" t="n">
-        <v>23.46</v>
+        <v>15.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>44.21</v>
+        <v>23.39</v>
       </c>
       <c r="AK18" t="n">
-        <v>47.96</v>
-      </c>
-      <c r="AL18" t="inlineStr"/>
+        <v>20.32</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40.6</v>
+      </c>
       <c r="AM18" t="n">
-        <v>38.54</v>
+        <v>23.96</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.37</v>
+        <v>20.32</v>
       </c>
       <c r="AO18" t="n">
-        <v>93.78</v>
+        <v>35.29</v>
       </c>
       <c r="AP18" t="n">
-        <v>80.52</v>
+        <v>59.49</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3645,34 +3637,42 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW18" t="n">
-        <v>22.95999908447266</v>
+        <v>14.38436412811279</v>
       </c>
       <c r="AX18" t="n">
-        <v>-7.012189752619536</v>
+        <v>4.418939370483477</v>
       </c>
       <c r="AY18" t="n">
-        <v>-40.71938764311017</v>
+        <v>-4.081037600189341</v>
       </c>
       <c r="AZ18" t="b">
         <v>1</v>
       </c>
       <c r="BA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>sem sinal (-7.0% do topo; Em Baixa)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66.47</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E19" t="n">
         <v>74.34</v>
       </c>
       <c r="F19" t="n">
-        <v>44.07</v>
+        <v>43.92</v>
       </c>
       <c r="G19" t="n">
         <v>66.84999999999999</v>
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66.34</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E20" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>58.13</v>
+        <v>57.95</v>
       </c>
       <c r="G20" t="n">
         <v>72.40000000000001</v>
@@ -4013,7 +4013,7 @@
         <v>-4.338697601218778</v>
       </c>
       <c r="AY20" t="n">
-        <v>-21.08022686888683</v>
+        <v>-21.08023573257425</v>
       </c>
       <c r="AZ20" t="b">
         <v>1</v>
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.24</v>
+        <v>62.22</v>
       </c>
       <c r="E24" t="n">
         <v>78.76000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>54.74</v>
+        <v>54.67</v>
       </c>
       <c r="G24" t="n">
         <v>56.89</v>
@@ -5097,13 +5097,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>61.58</v>
+        <v>61.54</v>
       </c>
       <c r="E27" t="n">
         <v>85.53</v>
       </c>
       <c r="F27" t="n">
-        <v>46.19</v>
+        <v>46.05</v>
       </c>
       <c r="G27" t="n">
         <v>28.72</v>
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>60.99</v>
+        <v>60.95</v>
       </c>
       <c r="E29" t="n">
         <v>40.81</v>
       </c>
       <c r="F29" t="n">
-        <v>65.41</v>
+        <v>65.28</v>
       </c>
       <c r="G29" t="n">
         <v>89.40000000000001</v>
@@ -5546,7 +5546,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY29" t="n">
-        <v>-39.5192605242667</v>
+        <v>-39.51924817380552</v>
       </c>
       <c r="AZ29" t="b">
         <v>1</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60.59</v>
+        <v>60.53</v>
       </c>
       <c r="E30" t="n">
         <v>54.88</v>
       </c>
       <c r="F30" t="n">
-        <v>59.67</v>
+        <v>59.51</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60.5</v>
+        <v>60.43</v>
       </c>
       <c r="E31" t="n">
         <v>62.88</v>
       </c>
       <c r="F31" t="n">
-        <v>27.96</v>
+        <v>27.71</v>
       </c>
       <c r="G31" t="n">
         <v>88.03</v>
@@ -5935,13 +5935,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>60.32</v>
+        <v>60.29</v>
       </c>
       <c r="E32" t="n">
         <v>69.06</v>
       </c>
       <c r="F32" t="n">
-        <v>70.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>40.55</v>
@@ -6252,7 +6252,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY33" t="n">
-        <v>-12.46351675410393</v>
+        <v>-12.46352623832258</v>
       </c>
       <c r="AZ33" t="b">
         <v>1</v>
@@ -6286,13 +6286,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>59.72</v>
+        <v>59.64</v>
       </c>
       <c r="E34" t="n">
         <v>78.31</v>
       </c>
       <c r="F34" t="n">
-        <v>39.1</v>
+        <v>38.89</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
@@ -6455,13 +6455,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>59.58</v>
+        <v>59.49</v>
       </c>
       <c r="E35" t="n">
         <v>91.86</v>
       </c>
       <c r="F35" t="n">
-        <v>25.58</v>
+        <v>25.34</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
@@ -6624,13 +6624,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>58.81</v>
+        <v>58.77</v>
       </c>
       <c r="E36" t="n">
         <v>87.29000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>36.28</v>
+        <v>36.15</v>
       </c>
       <c r="G36" t="n">
         <v>53.36</v>
@@ -6787,33 +6787,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>58.75</v>
+        <v>58.73</v>
       </c>
       <c r="E37" t="n">
-        <v>44.99</v>
+        <v>54.62</v>
       </c>
       <c r="F37" t="n">
-        <v>75.16</v>
+        <v>72.33</v>
       </c>
       <c r="G37" t="n">
-        <v>60.83</v>
+        <v>61.72</v>
       </c>
       <c r="H37" t="n">
-        <v>55.3</v>
+        <v>37.12</v>
       </c>
       <c r="I37" t="n">
         <v>37</v>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
         <v>7</v>
@@ -6833,10 +6833,10 @@
         <v>0</v>
       </c>
       <c r="N37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="b">
@@ -6855,74 +6855,70 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>4522778112</v>
+        <v>9096800256</v>
       </c>
       <c r="W37" t="n">
-        <v>6.94</v>
+        <v>5.26</v>
       </c>
       <c r="X37" t="n">
-        <v>0.34</v>
+        <v>0.83</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.25</v>
+        <v>3.02</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.94</v>
+        <v>15.83</v>
       </c>
       <c r="AA37" t="n">
-        <v>10.12</v>
+        <v>10.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.92</v>
+        <v>4.49</v>
       </c>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="n">
-        <v>2.259999990463257</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AJ37" t="n">
-        <v>4.18</v>
+        <v>7.62</v>
       </c>
       <c r="AK37" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>9.77</v>
-      </c>
+        <v>8.970000000000001</v>
+      </c>
+      <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="AN37" t="n">
-        <v>4.18</v>
+        <v>4.8</v>
       </c>
       <c r="AO37" t="n">
-        <v>85.14</v>
+        <v>21.61</v>
       </c>
       <c r="AP37" t="n">
-        <v>116.23</v>
+        <v>25.22</v>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6934,17 +6930,17 @@
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>2.339999914169312</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="AX37" t="n">
-        <v>-3.418800283779255</v>
+        <v>-0.7537681217588132</v>
       </c>
       <c r="AY37" t="n">
-        <v>-52.18694930098489</v>
+        <v>-47.92224740248528</v>
       </c>
       <c r="AZ37" t="b">
         <v>1</v>
@@ -6957,40 +6953,40 @@
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-0.8% do topo; Lateral)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>58.73</v>
+        <v>58.72</v>
       </c>
       <c r="E38" t="n">
-        <v>54.62</v>
+        <v>44.99</v>
       </c>
       <c r="F38" t="n">
-        <v>72.33</v>
+        <v>75.05</v>
       </c>
       <c r="G38" t="n">
-        <v>61.72</v>
+        <v>60.83</v>
       </c>
       <c r="H38" t="n">
-        <v>37.12</v>
+        <v>55.3</v>
       </c>
       <c r="I38" t="n">
         <v>38</v>
@@ -7001,7 +6997,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>7</v>
@@ -7010,10 +7006,10 @@
         <v>0</v>
       </c>
       <c r="N38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
@@ -7022,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="b">
@@ -7032,70 +7028,74 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>9096800256</v>
+        <v>4522778112</v>
       </c>
       <c r="W38" t="n">
-        <v>5.26</v>
+        <v>6.94</v>
       </c>
       <c r="X38" t="n">
-        <v>0.83</v>
+        <v>0.34</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.02</v>
+        <v>5.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>15.83</v>
+        <v>4.94</v>
       </c>
       <c r="AA38" t="n">
-        <v>10.88</v>
+        <v>10.12</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.49</v>
+        <v>8.92</v>
       </c>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>0.49</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.13</v>
+      </c>
       <c r="AG38" t="n">
-        <v>3.950000047683716</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AJ38" t="n">
-        <v>7.62</v>
+        <v>4.18</v>
       </c>
       <c r="AK38" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="AL38" t="inlineStr"/>
+        <v>6.98</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>9.77</v>
+      </c>
       <c r="AM38" t="n">
-        <v>4.95</v>
+        <v>4.89</v>
       </c>
       <c r="AN38" t="n">
-        <v>4.8</v>
+        <v>4.18</v>
       </c>
       <c r="AO38" t="n">
-        <v>21.61</v>
+        <v>85.14</v>
       </c>
       <c r="AP38" t="n">
-        <v>25.22</v>
+        <v>116.23</v>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -7107,17 +7107,17 @@
       <c r="AU38" t="inlineStr"/>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>3.980000019073486</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-3.418800283779255</v>
       </c>
       <c r="AY38" t="n">
-        <v>-47.92224740248528</v>
+        <v>-52.18694930098489</v>
       </c>
       <c r="AZ38" t="b">
         <v>1</v>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7151,13 +7151,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>58.69</v>
+        <v>58.67</v>
       </c>
       <c r="E39" t="n">
         <v>45.88</v>
       </c>
       <c r="F39" t="n">
-        <v>75.98999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="G39" t="n">
         <v>50.02</v>
@@ -7501,13 +7501,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>58.28</v>
+        <v>58.31</v>
       </c>
       <c r="E41" t="n">
         <v>54.95</v>
       </c>
       <c r="F41" t="n">
-        <v>48.88</v>
+        <v>48.95</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.2</v>
+        <v>58.16</v>
       </c>
       <c r="E42" t="n">
         <v>54.53</v>
       </c>
       <c r="F42" t="n">
-        <v>55.9</v>
+        <v>55.79</v>
       </c>
       <c r="G42" t="n">
         <v>37.84</v>
@@ -7833,7 +7833,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7843,23 +7843,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>58.08</v>
+        <v>58.07</v>
       </c>
       <c r="E43" t="n">
-        <v>62.28</v>
+        <v>75.37</v>
       </c>
       <c r="F43" t="n">
-        <v>49.47</v>
+        <v>30.97</v>
       </c>
       <c r="G43" t="n">
-        <v>68.58</v>
+        <v>53.48</v>
       </c>
       <c r="H43" t="n">
-        <v>51.52</v>
+        <v>78.03</v>
       </c>
       <c r="I43" t="n">
         <v>43</v>
@@ -7870,105 +7870,101 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L43" t="n">
         <v>7</v>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="b">
         <v>1</v>
       </c>
       <c r="P43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="b">
         <v>1</v>
       </c>
       <c r="R43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="b">
         <v>1</v>
       </c>
       <c r="U43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>15163994112</v>
+        <v>41226313728</v>
       </c>
       <c r="W43" t="n">
-        <v>9.01</v>
+        <v>8.76</v>
       </c>
       <c r="X43" t="n">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="Y43" t="n">
-        <v>4.89</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>11.91</v>
+        <v>19.7</v>
       </c>
       <c r="AA43" t="n">
-        <v>10.63</v>
+        <v>10.69</v>
       </c>
       <c r="AB43" t="n">
-        <v>19.49</v>
+        <v>33.52</v>
       </c>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.1</v>
-      </c>
+        <v>1.49</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="n">
-        <v>21.54000091552734</v>
+        <v>39.88999938964844</v>
       </c>
       <c r="AH43" t="n">
-        <v>17.56</v>
+        <v>54.58</v>
       </c>
       <c r="AI43" t="n">
-        <v>13.53</v>
+        <v>33.23</v>
       </c>
       <c r="AJ43" t="n">
-        <v>30.72</v>
+        <v>46.2</v>
       </c>
       <c r="AK43" t="n">
-        <v>32.91</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>71.72</v>
-      </c>
+        <v>48.6</v>
+      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="n">
-        <v>33.29</v>
+        <v>45.65</v>
       </c>
       <c r="AN43" t="n">
-        <v>30.72</v>
+        <v>47.4</v>
       </c>
       <c r="AO43" t="n">
-        <v>42.6</v>
+        <v>18.84</v>
       </c>
       <c r="AP43" t="n">
-        <v>54.53</v>
+        <v>14.45</v>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7980,17 +7976,17 @@
       <c r="AU43" t="inlineStr"/>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW43" t="n">
-        <v>21.64999961853027</v>
+        <v>41.59000015258789</v>
       </c>
       <c r="AX43" t="n">
-        <v>-0.5080771590812438</v>
+        <v>-4.087522858144721</v>
       </c>
       <c r="AY43" t="n">
-        <v>-19.64053433208342</v>
+        <v>-10.39229508845479</v>
       </c>
       <c r="AZ43" t="b">
         <v>1</v>
@@ -8003,14 +7999,14 @@
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>sem sinal (-0.5% do topo; Lateral)</t>
+          <t>sem sinal (-4.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8020,23 +8016,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>58.07</v>
+        <v>58.05</v>
       </c>
       <c r="E44" t="n">
-        <v>75.37</v>
+        <v>62.28</v>
       </c>
       <c r="F44" t="n">
-        <v>30.97</v>
+        <v>49.37</v>
       </c>
       <c r="G44" t="n">
-        <v>53.48</v>
+        <v>68.58</v>
       </c>
       <c r="H44" t="n">
-        <v>78.03</v>
+        <v>51.52</v>
       </c>
       <c r="I44" t="n">
         <v>44</v>
@@ -8047,101 +8043,105 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>7</v>
       </c>
       <c r="M44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="b">
         <v>1</v>
       </c>
       <c r="P44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="b">
         <v>1</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="b">
         <v>1</v>
       </c>
       <c r="U44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>41226313728</v>
+        <v>15163994112</v>
       </c>
       <c r="W44" t="n">
-        <v>8.76</v>
+        <v>9.01</v>
       </c>
       <c r="X44" t="n">
-        <v>1.73</v>
+        <v>1.07</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.210000000000001</v>
+        <v>4.89</v>
       </c>
       <c r="Z44" t="n">
-        <v>19.7</v>
+        <v>11.91</v>
       </c>
       <c r="AA44" t="n">
-        <v>10.69</v>
+        <v>10.63</v>
       </c>
       <c r="AB44" t="n">
-        <v>33.52</v>
+        <v>19.49</v>
       </c>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AG44" t="n">
-        <v>39.88999938964844</v>
+        <v>21.54000091552734</v>
       </c>
       <c r="AH44" t="n">
-        <v>54.58</v>
+        <v>17.56</v>
       </c>
       <c r="AI44" t="n">
-        <v>33.23</v>
+        <v>13.53</v>
       </c>
       <c r="AJ44" t="n">
-        <v>46.2</v>
+        <v>30.72</v>
       </c>
       <c r="AK44" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="AL44" t="inlineStr"/>
+        <v>32.91</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>71.72</v>
+      </c>
       <c r="AM44" t="n">
-        <v>45.65</v>
+        <v>33.29</v>
       </c>
       <c r="AN44" t="n">
-        <v>47.4</v>
+        <v>30.72</v>
       </c>
       <c r="AO44" t="n">
-        <v>18.84</v>
+        <v>42.6</v>
       </c>
       <c r="AP44" t="n">
-        <v>14.45</v>
+        <v>54.53</v>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -8153,17 +8153,17 @@
       <c r="AU44" t="inlineStr"/>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW44" t="n">
-        <v>41.59000015258789</v>
+        <v>21.64999961853027</v>
       </c>
       <c r="AX44" t="n">
-        <v>-4.087522858144721</v>
+        <v>-0.5080771590812438</v>
       </c>
       <c r="AY44" t="n">
-        <v>-10.39229508845479</v>
+        <v>-19.64053433208342</v>
       </c>
       <c r="AZ44" t="b">
         <v>1</v>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>sem sinal (-4.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-0.5% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>57.97</v>
+        <v>57.86</v>
       </c>
       <c r="E45" t="n">
         <v>52.6</v>
       </c>
       <c r="F45" t="n">
-        <v>57.63</v>
+        <v>57.32</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
@@ -8505,7 +8505,7 @@
         <v>-4.020742883737105</v>
       </c>
       <c r="AY46" t="n">
-        <v>-14.35606196730216</v>
+        <v>-14.3560541194689</v>
       </c>
       <c r="AZ46" t="b">
         <v>1</v>
@@ -8539,13 +8539,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>56.5</v>
+        <v>56.47</v>
       </c>
       <c r="E47" t="n">
         <v>72.91</v>
       </c>
       <c r="F47" t="n">
-        <v>40.23</v>
+        <v>40.13</v>
       </c>
       <c r="G47" t="n">
         <v>75.81</v>
@@ -8712,13 +8712,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>55.95</v>
+        <v>56.18</v>
       </c>
       <c r="E48" t="n">
         <v>69.17</v>
       </c>
       <c r="F48" t="n">
-        <v>24.56</v>
+        <v>25.19</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
@@ -8780,14 +8780,12 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>87.75</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="n">
         <v>42.06999969482422</v>
       </c>
@@ -8795,28 +8793,26 @@
         <v>77.83</v>
       </c>
       <c r="AI48" t="n">
-        <v>60</v>
+        <v>47.38</v>
       </c>
       <c r="AJ48" t="n">
-        <v>60.8</v>
+        <v>48.02</v>
       </c>
       <c r="AK48" t="n">
         <v>24.44</v>
       </c>
-      <c r="AL48" t="n">
-        <v>94.65000000000001</v>
-      </c>
+      <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="n">
-        <v>63.54</v>
+        <v>49.42</v>
       </c>
       <c r="AN48" t="n">
-        <v>60.8</v>
+        <v>47.7</v>
       </c>
       <c r="AO48" t="n">
-        <v>44.53</v>
+        <v>13.38</v>
       </c>
       <c r="AP48" t="n">
-        <v>51.04</v>
+        <v>17.46</v>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
@@ -9062,13 +9058,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>55.09</v>
+        <v>55.07</v>
       </c>
       <c r="E50" t="n">
         <v>47.37</v>
       </c>
       <c r="F50" t="n">
-        <v>78.25</v>
+        <v>78.17</v>
       </c>
       <c r="G50" t="n">
         <v>55.3</v>
@@ -9225,7 +9221,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9235,34 +9231,34 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>54.74</v>
+        <v>54.73</v>
       </c>
       <c r="E51" t="n">
-        <v>75.95999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="F51" t="n">
-        <v>37.59</v>
+        <v>57.67</v>
       </c>
       <c r="G51" t="n">
-        <v>26.44</v>
+        <v>56.6</v>
       </c>
       <c r="H51" t="n">
-        <v>77.27</v>
+        <v>19.7</v>
       </c>
       <c r="I51" t="n">
         <v>51</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L51" t="n">
         <v>7</v>
@@ -9277,13 +9273,13 @@
         <v>1</v>
       </c>
       <c r="P51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="b">
@@ -9293,69 +9289,65 @@
         <v>1</v>
       </c>
       <c r="V51" t="n">
-        <v>53406994432</v>
+        <v>53107621888</v>
       </c>
       <c r="W51" t="n">
-        <v>9.27</v>
+        <v>4.78</v>
       </c>
       <c r="X51" t="n">
-        <v>2.2</v>
+        <v>1.13</v>
       </c>
       <c r="Y51" t="n">
-        <v>8.050000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="Z51" t="n">
-        <v>23.72</v>
+        <v>23.68</v>
       </c>
       <c r="AA51" t="n">
-        <v>15.33</v>
+        <v>6.83</v>
       </c>
       <c r="AB51" t="n">
-        <v>12.79</v>
+        <v>22.96</v>
       </c>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="n">
-        <v>1.15</v>
+        <v>3.52</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0.52</v>
-      </c>
+        <v>2.02</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="n">
-        <v>46.34999847412109</v>
+        <v>43.02000045776367</v>
       </c>
       <c r="AH51" t="n">
-        <v>62.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI51" t="n">
-        <v>47.94</v>
+        <v>0.04</v>
       </c>
       <c r="AJ51" t="n">
-        <v>64.23999999999999</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="AK51" t="n">
-        <v>48.68</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>130.25</v>
-      </c>
+        <v>87.8</v>
+      </c>
+      <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="n">
-        <v>70.66</v>
+        <v>44.81</v>
       </c>
       <c r="AN51" t="n">
-        <v>62.19</v>
+        <v>43.94</v>
       </c>
       <c r="AO51" t="n">
-        <v>34.17</v>
+        <v>2.13</v>
       </c>
       <c r="AP51" t="n">
-        <v>52.45</v>
+        <v>4.16</v>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
@@ -9369,44 +9361,40 @@
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="AU51" t="inlineStr"/>
       <c r="AV51" t="inlineStr">
         <is>
           <t>Lateral</t>
         </is>
       </c>
       <c r="AW51" t="n">
-        <v>47.20000076293945</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="AX51" t="n">
-        <v>-1.80085227770963</v>
+        <v>-0.1856102533401627</v>
       </c>
       <c r="AY51" t="n">
-        <v>-12.53370020185791</v>
+        <v>-27.87197279000151</v>
       </c>
       <c r="AZ51" t="b">
         <v>1</v>
       </c>
       <c r="BA51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (-0.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9416,34 +9404,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>54.73</v>
+        <v>54.68</v>
       </c>
       <c r="E52" t="n">
-        <v>66.16</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>57.67</v>
+        <v>37.39</v>
       </c>
       <c r="G52" t="n">
-        <v>56.6</v>
+        <v>26.44</v>
       </c>
       <c r="H52" t="n">
-        <v>19.7</v>
+        <v>77.27</v>
       </c>
       <c r="I52" t="n">
         <v>52</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
         <v>7</v>
@@ -9458,13 +9446,13 @@
         <v>1</v>
       </c>
       <c r="P52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="b">
@@ -9474,65 +9462,69 @@
         <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>53107621888</v>
+        <v>53406994432</v>
       </c>
       <c r="W52" t="n">
-        <v>4.78</v>
+        <v>9.27</v>
       </c>
       <c r="X52" t="n">
-        <v>1.13</v>
+        <v>2.2</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.01</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Z52" t="n">
-        <v>23.68</v>
+        <v>23.72</v>
       </c>
       <c r="AA52" t="n">
-        <v>6.83</v>
+        <v>15.33</v>
       </c>
       <c r="AB52" t="n">
-        <v>22.96</v>
+        <v>12.79</v>
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="n">
-        <v>3.52</v>
+        <v>1.15</v>
       </c>
       <c r="AE52" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
+        <v>1.43</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.52</v>
+      </c>
       <c r="AG52" t="n">
-        <v>43.02000045776367</v>
+        <v>46.34999847412109</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.07000000000000001</v>
+        <v>62.19</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.04</v>
+        <v>47.94</v>
       </c>
       <c r="AJ52" t="n">
-        <v>91.31999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AK52" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="AL52" t="inlineStr"/>
+        <v>48.68</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>130.25</v>
+      </c>
       <c r="AM52" t="n">
-        <v>44.81</v>
+        <v>70.66</v>
       </c>
       <c r="AN52" t="n">
-        <v>43.94</v>
+        <v>62.19</v>
       </c>
       <c r="AO52" t="n">
-        <v>2.13</v>
+        <v>34.17</v>
       </c>
       <c r="AP52" t="n">
-        <v>4.16</v>
+        <v>52.45</v>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
@@ -9545,34 +9537,42 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AU52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>A CPFL Energia (CPFE3) apresenta-se como um ativo de alta qualidade operacional no setor de utilidade pública, com um retorno sobre o patrimônio líquido de 23,7% e um retorno sobre o capital investido de 15,3% que se posicionam significativamente acima das médias setoriais de 11,6% e 9,5%, respectivamente. Essa sólida rentabilidade convive com múltiplos de preço que sugerem um valuation misto, pois, embora o preço sobre valor patrimonial de 2,2 esteja acima dos pares, o preço sobre lucro de 9,27 e o indicador de crescimento PEG de 0,52 mostram-se atraentes frente à forte capacidade de geração de resultados da companhia. O robusto crescimento da empresa é evidenciado pela taxa de crescimento anual composta da receita nos últimos cinco anos de 18,0%, superando com folga a média negativa do setor de 10,1%, o que valida o cumprimento de seis dos sete critérios do checklist de investimento. No âmbito financeiro, a relação de dívida sobre o patrimônio de 1,43 reflete uma alavancagem que exige atenção, mas que é mitigada por uma liquidez corrente de 1,15 e pela alta eficiência operacional, sustentando um rendimento de dividendos de 8,05% que se mostra coerente com a forte geração de caixa e com o histórico de distribuição da empresa. Sob a ótica do valuation por múltiplos métodos de preço-teto, observa-se uma dispersão relevante entre as metodologias, variando desde os mais conservadores 47,94 reais pelo modelo de Gordon e 48,68 reais por Graham, passando por 62,19 reais por Bazin, até os mais otimistas 130,25 reais por Lynch. Essa disparidade resulta em uma média de 70,66 reais e uma mediana de 62,19 reais, o que confere ao papel um potencial de valorização de 34,2% em relação à mediana frente ao preço atual de 46,35 reais. Como principais prós, destacam-se a rentabilidade muito acima da média setorial, o forte crescimento histórico de receita e o atraente retorno em dividendos amparado por ótimos indicadores de qualidade. Em contrapartida, figuram como contras o nível de endividamento patrimonial relativamente elevado, uma margem líquida de 12,79% que não atinge o patamar ideal de 15% do checklist e a tendência gráfica lateralizada que reflete a atual indefinição do mercado no curto prazo.</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>Lateral</t>
         </is>
       </c>
       <c r="AW52" t="n">
-        <v>43.09999847412109</v>
+        <v>47.20000076293945</v>
       </c>
       <c r="AX52" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-1.80085227770963</v>
       </c>
       <c r="AY52" t="n">
-        <v>-27.87197279000151</v>
+        <v>-12.53370020185791</v>
       </c>
       <c r="AZ52" t="b">
         <v>1</v>
       </c>
       <c r="BA52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -9593,13 +9593,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>54.17</v>
+        <v>54.11</v>
       </c>
       <c r="E53" t="n">
         <v>78.66</v>
       </c>
       <c r="F53" t="n">
-        <v>22.48</v>
+        <v>22.25</v>
       </c>
       <c r="G53" t="n">
         <v>55.48</v>
@@ -9909,7 +9909,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY54" t="n">
-        <v>-23.47392377028176</v>
+        <v>-23.4739172343906</v>
       </c>
       <c r="AZ54" t="b">
         <v>1</v>
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>51.93</v>
+        <v>51.8</v>
       </c>
       <c r="E58" t="n">
         <v>59.96</v>
       </c>
       <c r="F58" t="n">
-        <v>29.13</v>
+        <v>28.79</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
@@ -10726,7 +10726,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY59" t="n">
-        <v>-50.51140559404919</v>
+        <v>-50.51140229842947</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -10899,7 +10899,7 @@
         <v>-0.9501178501326923</v>
       </c>
       <c r="AY60" t="n">
-        <v>-14.40870883002358</v>
+        <v>-14.40870028403989</v>
       </c>
       <c r="AZ60" t="b">
         <v>1</v>
@@ -10933,13 +10933,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>51.68</v>
+        <v>51.62</v>
       </c>
       <c r="E61" t="n">
         <v>46.49</v>
       </c>
       <c r="F61" t="n">
-        <v>70.33</v>
+        <v>70.13</v>
       </c>
       <c r="G61" t="n">
         <v>39.18</v>
@@ -11235,7 +11235,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>A WEG (WEGE3) se consolida como uma empresa de altíssima eficiência operacional, apresentando um ROE de 33,2% e um ROIC de 24,3% que se posicionam muito acima dos pares do setor de bens industriais, os quais registram médias de 7,0% e 10,1%, respectivamente. Essa qualidade excepcional, contudo, convive com múltiplos de preço bastante esticados, evidenciados pelo P/L de 33,0 e pelo P/VP de 10,94, indicando que o mercado cobra um prêmio elevado por essa rentabilidade diferenciada. No balanço entre rentabilidade e endividamento, a companhia demonstra extrema solidez financeira ao associar sua forte margem líquida de 15,58% a uma baixa relação de dívida sobre o patrimônio de 0,29 e a uma confortável liquidez corrente de 1,59. O retorno em dividendos de 4,08% mostra-se coerente e sustentável diante da robusta geração de lucro e da estrutura de capital desalavancada, embora o crescimento de longo prazo acenda um sinal de alerta, visto que o CAGR de receita de cinco anos contraiu 2,1%, situando-se abaixo da média setorial de expansão de 14,9%. No checklist de critérios fundamentalistas, a empresa atende a 5 de 7 requisitos, falhando justamente na expansão de receita frente aos pares e na ocorrência de vendas por parte de insiders, o que se reflete em uma nota de qualidade de 86,0 contra um score de valor de apenas 4,0. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão acentuada, variando desde os R$ 33,44 pelo modelo de Bazin até os R$ 12,28 pela fórmula de Graham, resultando em uma média de R$ 20,30 e uma mediana de R$ 17,74. Frente ao preço atual de R$ 49,17, a mediana projeta um upside negativo de 63,9%, sugerindo que a cotação de mercado atual embutiu expectativas excessivamente otimistas que descolam o papel de suas referências teóricas de valor. Em suma, os principais prós do investimento residem na rentabilidade formidável, na saúde financeira impecável e na resiliência operacional, enquanto os contras concentram-se no valuation severamente esticado, no crescimento recente de receita abaixo do setor e na expressiva distância para os preços-teto calculados.</t>
+        </is>
+      </c>
       <c r="AU62" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -11253,7 +11257,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY62" t="n">
-        <v>-9.423154175560278</v>
+        <v>-9.423147674714317</v>
       </c>
       <c r="AZ62" t="b">
         <v>1</v>
@@ -11408,13 +11412,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>50.82</v>
+        <v>50.84</v>
       </c>
       <c r="E64" t="n">
         <v>57.31</v>
       </c>
       <c r="F64" t="n">
-        <v>29.72</v>
+        <v>29.79</v>
       </c>
       <c r="G64" t="n">
         <v>61.5</v>
@@ -11594,13 +11598,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>50.25</v>
+        <v>50.19</v>
       </c>
       <c r="E65" t="n">
         <v>39.71</v>
       </c>
       <c r="F65" t="n">
-        <v>63.02</v>
+        <v>62.84</v>
       </c>
       <c r="G65" t="n">
         <v>43.18</v>
@@ -11771,13 +11775,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>49.62</v>
+        <v>49.61</v>
       </c>
       <c r="E66" t="n">
         <v>11.21</v>
       </c>
       <c r="F66" t="n">
-        <v>85.59999999999999</v>
+        <v>85.55</v>
       </c>
       <c r="G66" t="n">
         <v>93.01000000000001</v>
@@ -11930,13 +11934,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>49.47</v>
+        <v>49.4</v>
       </c>
       <c r="E67" t="n">
         <v>47.58</v>
       </c>
       <c r="F67" t="n">
-        <v>39.02</v>
+        <v>38.77</v>
       </c>
       <c r="G67" t="n">
         <v>49.88</v>
@@ -12073,7 +12077,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY67" t="n">
-        <v>-23.22977049821228</v>
+        <v>-23.22975619580519</v>
       </c>
       <c r="AZ67" t="b">
         <v>1</v>
@@ -12925,13 +12929,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.48999999999999</v>
+        <v>72.45</v>
       </c>
       <c r="E5" t="n">
         <v>81.05</v>
       </c>
       <c r="F5" t="n">
-        <v>58.25</v>
+        <v>58.1</v>
       </c>
       <c r="G5" t="n">
         <v>61.1</v>
@@ -13968,13 +13972,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69.66</v>
+        <v>69.61</v>
       </c>
       <c r="E11" t="n">
         <v>79.12</v>
       </c>
       <c r="F11" t="n">
-        <v>38.97</v>
+        <v>38.8</v>
       </c>
       <c r="G11" t="n">
         <v>84.34</v>
@@ -14153,13 +14157,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69.23999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="E12" t="n">
         <v>90.51000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>35.51</v>
+        <v>35.34</v>
       </c>
       <c r="G12" t="n">
         <v>65.79000000000001</v>
@@ -14330,13 +14334,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68.70999999999999</v>
+        <v>68.64</v>
       </c>
       <c r="E13" t="n">
         <v>83.66</v>
       </c>
       <c r="F13" t="n">
-        <v>57.75</v>
+        <v>57.52</v>
       </c>
       <c r="G13" t="n">
         <v>63.93</v>
@@ -14507,13 +14511,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.5</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>54.93</v>
       </c>
       <c r="F14" t="n">
-        <v>56.87</v>
+        <v>56.73</v>
       </c>
       <c r="G14" t="n">
         <v>92.98999999999999</v>
@@ -15008,44 +15012,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INTB3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66.77</v>
+        <v>66.72</v>
       </c>
       <c r="E17" t="n">
-        <v>72.69</v>
+        <v>61.42</v>
       </c>
       <c r="F17" t="n">
-        <v>40.83</v>
+        <v>53.27</v>
       </c>
       <c r="G17" t="n">
-        <v>88</v>
+        <v>80.89</v>
       </c>
       <c r="H17" t="n">
-        <v>76.52</v>
+        <v>87.12</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -15060,10 +15064,10 @@
         <v>1</v>
       </c>
       <c r="P17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -15073,77 +15077,73 @@
         <v>1</v>
       </c>
       <c r="U17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4914711040</v>
+        <v>7821505536</v>
       </c>
       <c r="W17" t="n">
-        <v>8.25</v>
+        <v>4.9</v>
       </c>
       <c r="X17" t="n">
-        <v>1.49</v>
+        <v>0.91</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>10.83</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.07</v>
+        <v>18.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>17.52</v>
+        <v>6.91</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.1</v>
+        <v>20.76</v>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
-        <v>2.64</v>
+        <v>3.78</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.58</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>15.02000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="AH17" t="n">
-        <v>20.03</v>
+        <v>38.54</v>
       </c>
       <c r="AI17" t="n">
-        <v>15.44</v>
+        <v>23.46</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23.39</v>
+        <v>44.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>40.6</v>
-      </c>
+        <v>47.96</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
-        <v>23.96</v>
+        <v>38.54</v>
       </c>
       <c r="AN17" t="n">
-        <v>20.32</v>
+        <v>41.37</v>
       </c>
       <c r="AO17" t="n">
-        <v>35.29</v>
+        <v>93.78</v>
       </c>
       <c r="AP17" t="n">
-        <v>59.49</v>
+        <v>80.52</v>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -15151,86 +15151,78 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW17" t="n">
-        <v>14.38436412811279</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.418939370483477</v>
+        <v>-7.012189752619536</v>
       </c>
       <c r="AY17" t="n">
-        <v>-4.081037600189341</v>
+        <v>-40.71938764311017</v>
       </c>
       <c r="AZ17" t="b">
         <v>1</v>
       </c>
       <c r="BA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-7.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>INTB3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66.72</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>61.42</v>
+        <v>72.69</v>
       </c>
       <c r="F18" t="n">
-        <v>53.27</v>
+        <v>40.62</v>
       </c>
       <c r="G18" t="n">
-        <v>80.89</v>
+        <v>88</v>
       </c>
       <c r="H18" t="n">
-        <v>87.12</v>
+        <v>76.52</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -15245,10 +15237,10 @@
         <v>1</v>
       </c>
       <c r="P18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -15258,73 +15250,77 @@
         <v>1</v>
       </c>
       <c r="U18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>7821505536</v>
+        <v>4914711040</v>
       </c>
       <c r="W18" t="n">
-        <v>4.9</v>
+        <v>8.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0.91</v>
+        <v>1.49</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.83</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.6</v>
+        <v>18.07</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.91</v>
+        <v>17.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>20.76</v>
+        <v>13.1</v>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>3.78</v>
+        <v>2.64</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>0.26</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.58</v>
+      </c>
       <c r="AG18" t="n">
-        <v>21.35000038146973</v>
+        <v>15.02000045776367</v>
       </c>
       <c r="AH18" t="n">
-        <v>38.54</v>
+        <v>20.03</v>
       </c>
       <c r="AI18" t="n">
-        <v>23.46</v>
+        <v>15.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>44.21</v>
+        <v>23.39</v>
       </c>
       <c r="AK18" t="n">
-        <v>47.96</v>
-      </c>
-      <c r="AL18" t="inlineStr"/>
+        <v>20.32</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40.6</v>
+      </c>
       <c r="AM18" t="n">
-        <v>38.54</v>
+        <v>23.96</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.37</v>
+        <v>20.32</v>
       </c>
       <c r="AO18" t="n">
-        <v>93.78</v>
+        <v>35.29</v>
       </c>
       <c r="AP18" t="n">
-        <v>80.52</v>
+        <v>59.49</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -15332,34 +15328,42 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW18" t="n">
-        <v>22.95999908447266</v>
+        <v>14.38436412811279</v>
       </c>
       <c r="AX18" t="n">
-        <v>-7.012189752619536</v>
+        <v>4.418939370483477</v>
       </c>
       <c r="AY18" t="n">
-        <v>-40.71938764311017</v>
+        <v>-4.081037600189341</v>
       </c>
       <c r="AZ18" t="b">
         <v>1</v>
       </c>
       <c r="BA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>sem sinal (-7.0% do topo; Em Baixa)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -15380,13 +15384,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66.47</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E19" t="n">
         <v>74.34</v>
       </c>
       <c r="F19" t="n">
-        <v>44.07</v>
+        <v>43.92</v>
       </c>
       <c r="G19" t="n">
         <v>66.84999999999999</v>
@@ -15557,13 +15561,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66.34</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E20" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>58.13</v>
+        <v>57.95</v>
       </c>
       <c r="G20" t="n">
         <v>72.40000000000001</v>
@@ -15700,7 +15704,7 @@
         <v>-4.338697601218778</v>
       </c>
       <c r="AY20" t="n">
-        <v>-21.08022686888683</v>
+        <v>-21.08023573257425</v>
       </c>
       <c r="AZ20" t="b">
         <v>1</v>
@@ -16080,13 +16084,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63.19</v>
+        <v>63.18</v>
       </c>
       <c r="E23" t="n">
         <v>6.72</v>
       </c>
       <c r="F23" t="n">
-        <v>93.68000000000001</v>
+        <v>93.66</v>
       </c>
       <c r="G23" t="n">
         <v>90.36</v>
@@ -16420,13 +16424,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62.24</v>
+        <v>62.22</v>
       </c>
       <c r="E25" t="n">
         <v>78.76000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>54.74</v>
+        <v>54.67</v>
       </c>
       <c r="G25" t="n">
         <v>56.89</v>
@@ -16951,13 +16955,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>61.58</v>
+        <v>61.54</v>
       </c>
       <c r="E28" t="n">
         <v>85.53</v>
       </c>
       <c r="F28" t="n">
-        <v>46.19</v>
+        <v>46.05</v>
       </c>
       <c r="G28" t="n">
         <v>28.72</v>
@@ -17257,13 +17261,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60.99</v>
+        <v>60.95</v>
       </c>
       <c r="E30" t="n">
         <v>40.81</v>
       </c>
       <c r="F30" t="n">
-        <v>65.41</v>
+        <v>65.28</v>
       </c>
       <c r="G30" t="n">
         <v>89.40000000000001</v>
@@ -17400,7 +17404,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY30" t="n">
-        <v>-39.5192605242667</v>
+        <v>-39.51924817380552</v>
       </c>
       <c r="AZ30" t="b">
         <v>1</v>
@@ -17434,13 +17438,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60.59</v>
+        <v>60.53</v>
       </c>
       <c r="E31" t="n">
         <v>54.88</v>
       </c>
       <c r="F31" t="n">
-        <v>59.67</v>
+        <v>59.51</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
@@ -17612,13 +17616,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>60.5</v>
+        <v>60.43</v>
       </c>
       <c r="E32" t="n">
         <v>62.88</v>
       </c>
       <c r="F32" t="n">
-        <v>27.96</v>
+        <v>27.71</v>
       </c>
       <c r="G32" t="n">
         <v>88.03</v>
@@ -17789,13 +17793,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>60.32</v>
+        <v>60.29</v>
       </c>
       <c r="E33" t="n">
         <v>69.06</v>
       </c>
       <c r="F33" t="n">
-        <v>70.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>40.55</v>
@@ -18106,7 +18110,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY34" t="n">
-        <v>-12.46351675410393</v>
+        <v>-12.46352623832258</v>
       </c>
       <c r="AZ34" t="b">
         <v>1</v>
@@ -18140,13 +18144,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>59.72</v>
+        <v>59.64</v>
       </c>
       <c r="E35" t="n">
         <v>78.31</v>
       </c>
       <c r="F35" t="n">
-        <v>39.1</v>
+        <v>38.89</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
@@ -18309,13 +18313,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>59.58</v>
+        <v>59.49</v>
       </c>
       <c r="E36" t="n">
         <v>91.86</v>
       </c>
       <c r="F36" t="n">
-        <v>25.58</v>
+        <v>25.34</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
@@ -18478,13 +18482,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>58.81</v>
+        <v>58.77</v>
       </c>
       <c r="E37" t="n">
         <v>87.29000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>36.28</v>
+        <v>36.15</v>
       </c>
       <c r="G37" t="n">
         <v>53.36</v>
@@ -18641,33 +18645,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>58.75</v>
+        <v>58.73</v>
       </c>
       <c r="E38" t="n">
-        <v>44.99</v>
+        <v>54.62</v>
       </c>
       <c r="F38" t="n">
-        <v>75.16</v>
+        <v>72.33</v>
       </c>
       <c r="G38" t="n">
-        <v>60.83</v>
+        <v>61.72</v>
       </c>
       <c r="H38" t="n">
-        <v>55.3</v>
+        <v>37.12</v>
       </c>
       <c r="I38" t="n">
         <v>37</v>
@@ -18678,7 +18682,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
         <v>7</v>
@@ -18687,10 +18691,10 @@
         <v>0</v>
       </c>
       <c r="N38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
@@ -18699,7 +18703,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="b">
@@ -18709,74 +18713,70 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4522778112</v>
+        <v>9096800256</v>
       </c>
       <c r="W38" t="n">
-        <v>6.94</v>
+        <v>5.26</v>
       </c>
       <c r="X38" t="n">
-        <v>0.34</v>
+        <v>0.83</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.25</v>
+        <v>3.02</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.94</v>
+        <v>15.83</v>
       </c>
       <c r="AA38" t="n">
-        <v>10.12</v>
+        <v>10.88</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.92</v>
+        <v>4.49</v>
       </c>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="n">
-        <v>2.259999990463257</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AJ38" t="n">
-        <v>4.18</v>
+        <v>7.62</v>
       </c>
       <c r="AK38" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>9.77</v>
-      </c>
+        <v>8.970000000000001</v>
+      </c>
+      <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="AN38" t="n">
-        <v>4.18</v>
+        <v>4.8</v>
       </c>
       <c r="AO38" t="n">
-        <v>85.14</v>
+        <v>21.61</v>
       </c>
       <c r="AP38" t="n">
-        <v>116.23</v>
+        <v>25.22</v>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -18788,17 +18788,17 @@
       <c r="AU38" t="inlineStr"/>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>2.339999914169312</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="AX38" t="n">
-        <v>-3.418800283779255</v>
+        <v>-0.7537681217588132</v>
       </c>
       <c r="AY38" t="n">
-        <v>-52.18694930098489</v>
+        <v>-47.92224740248528</v>
       </c>
       <c r="AZ38" t="b">
         <v>1</v>
@@ -18811,40 +18811,40 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-0.8% do topo; Lateral)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>58.73</v>
+        <v>58.72</v>
       </c>
       <c r="E39" t="n">
-        <v>54.62</v>
+        <v>44.99</v>
       </c>
       <c r="F39" t="n">
-        <v>72.33</v>
+        <v>75.05</v>
       </c>
       <c r="G39" t="n">
-        <v>61.72</v>
+        <v>60.83</v>
       </c>
       <c r="H39" t="n">
-        <v>37.12</v>
+        <v>55.3</v>
       </c>
       <c r="I39" t="n">
         <v>38</v>
@@ -18855,7 +18855,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>7</v>
@@ -18864,10 +18864,10 @@
         <v>0</v>
       </c>
       <c r="N39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="b">
         <v>0</v>
@@ -18876,7 +18876,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="b">
@@ -18886,70 +18886,74 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>9096800256</v>
+        <v>4522778112</v>
       </c>
       <c r="W39" t="n">
-        <v>5.26</v>
+        <v>6.94</v>
       </c>
       <c r="X39" t="n">
-        <v>0.83</v>
+        <v>0.34</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.02</v>
+        <v>5.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>15.83</v>
+        <v>4.94</v>
       </c>
       <c r="AA39" t="n">
-        <v>10.88</v>
+        <v>10.12</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.49</v>
+        <v>8.92</v>
       </c>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
+        <v>0.49</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.13</v>
+      </c>
       <c r="AG39" t="n">
-        <v>3.950000047683716</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AJ39" t="n">
-        <v>7.62</v>
+        <v>4.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="AL39" t="inlineStr"/>
+        <v>6.98</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>9.77</v>
+      </c>
       <c r="AM39" t="n">
-        <v>4.95</v>
+        <v>4.89</v>
       </c>
       <c r="AN39" t="n">
-        <v>4.8</v>
+        <v>4.18</v>
       </c>
       <c r="AO39" t="n">
-        <v>21.61</v>
+        <v>85.14</v>
       </c>
       <c r="AP39" t="n">
-        <v>25.22</v>
+        <v>116.23</v>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -18961,17 +18965,17 @@
       <c r="AU39" t="inlineStr"/>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>3.980000019073486</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-3.418800283779255</v>
       </c>
       <c r="AY39" t="n">
-        <v>-47.92224740248528</v>
+        <v>-52.18694930098489</v>
       </c>
       <c r="AZ39" t="b">
         <v>1</v>
@@ -18984,7 +18988,7 @@
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -19005,13 +19009,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>58.69</v>
+        <v>58.67</v>
       </c>
       <c r="E40" t="n">
         <v>45.88</v>
       </c>
       <c r="F40" t="n">
-        <v>75.98999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="G40" t="n">
         <v>50.02</v>
@@ -19355,13 +19359,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.28</v>
+        <v>58.31</v>
       </c>
       <c r="E42" t="n">
         <v>54.95</v>
       </c>
       <c r="F42" t="n">
-        <v>48.88</v>
+        <v>48.95</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
@@ -19524,13 +19528,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>58.2</v>
+        <v>58.16</v>
       </c>
       <c r="E43" t="n">
         <v>54.53</v>
       </c>
       <c r="F43" t="n">
-        <v>55.9</v>
+        <v>55.79</v>
       </c>
       <c r="G43" t="n">
         <v>37.84</v>
@@ -19687,7 +19691,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19697,23 +19701,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>58.08</v>
+        <v>58.07</v>
       </c>
       <c r="E44" t="n">
-        <v>62.28</v>
+        <v>75.37</v>
       </c>
       <c r="F44" t="n">
-        <v>49.47</v>
+        <v>30.97</v>
       </c>
       <c r="G44" t="n">
-        <v>68.58</v>
+        <v>53.48</v>
       </c>
       <c r="H44" t="n">
-        <v>51.52</v>
+        <v>78.03</v>
       </c>
       <c r="I44" t="n">
         <v>43</v>
@@ -19724,105 +19728,101 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L44" t="n">
         <v>7</v>
       </c>
       <c r="M44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="b">
         <v>1</v>
       </c>
       <c r="P44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="b">
         <v>1</v>
       </c>
       <c r="R44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="b">
         <v>1</v>
       </c>
       <c r="U44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>15163994112</v>
+        <v>41226313728</v>
       </c>
       <c r="W44" t="n">
-        <v>9.01</v>
+        <v>8.76</v>
       </c>
       <c r="X44" t="n">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="Y44" t="n">
-        <v>4.89</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Z44" t="n">
-        <v>11.91</v>
+        <v>19.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>10.63</v>
+        <v>10.69</v>
       </c>
       <c r="AB44" t="n">
-        <v>19.49</v>
+        <v>33.52</v>
       </c>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.1</v>
-      </c>
+        <v>1.49</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="n">
-        <v>21.54000091552734</v>
+        <v>39.88999938964844</v>
       </c>
       <c r="AH44" t="n">
-        <v>17.56</v>
+        <v>54.58</v>
       </c>
       <c r="AI44" t="n">
-        <v>13.53</v>
+        <v>33.23</v>
       </c>
       <c r="AJ44" t="n">
-        <v>30.72</v>
+        <v>46.2</v>
       </c>
       <c r="AK44" t="n">
-        <v>32.91</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>71.72</v>
-      </c>
+        <v>48.6</v>
+      </c>
+      <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="n">
-        <v>33.29</v>
+        <v>45.65</v>
       </c>
       <c r="AN44" t="n">
-        <v>30.72</v>
+        <v>47.4</v>
       </c>
       <c r="AO44" t="n">
-        <v>42.6</v>
+        <v>18.84</v>
       </c>
       <c r="AP44" t="n">
-        <v>54.53</v>
+        <v>14.45</v>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -19834,17 +19834,17 @@
       <c r="AU44" t="inlineStr"/>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW44" t="n">
-        <v>21.64999961853027</v>
+        <v>41.59000015258789</v>
       </c>
       <c r="AX44" t="n">
-        <v>-0.5080771590812438</v>
+        <v>-4.087522858144721</v>
       </c>
       <c r="AY44" t="n">
-        <v>-19.64053433208342</v>
+        <v>-10.39229508845479</v>
       </c>
       <c r="AZ44" t="b">
         <v>1</v>
@@ -19857,14 +19857,14 @@
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>sem sinal (-0.5% do topo; Lateral)</t>
+          <t>sem sinal (-4.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19874,23 +19874,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>58.07</v>
+        <v>58.05</v>
       </c>
       <c r="E45" t="n">
-        <v>75.37</v>
+        <v>62.28</v>
       </c>
       <c r="F45" t="n">
-        <v>30.97</v>
+        <v>49.37</v>
       </c>
       <c r="G45" t="n">
-        <v>53.48</v>
+        <v>68.58</v>
       </c>
       <c r="H45" t="n">
-        <v>78.03</v>
+        <v>51.52</v>
       </c>
       <c r="I45" t="n">
         <v>44</v>
@@ -19901,101 +19901,105 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L45" t="n">
         <v>7</v>
       </c>
       <c r="M45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="b">
         <v>1</v>
       </c>
       <c r="P45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="b">
         <v>1</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="b">
         <v>1</v>
       </c>
       <c r="U45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>41226313728</v>
+        <v>15163994112</v>
       </c>
       <c r="W45" t="n">
-        <v>8.76</v>
+        <v>9.01</v>
       </c>
       <c r="X45" t="n">
-        <v>1.73</v>
+        <v>1.07</v>
       </c>
       <c r="Y45" t="n">
-        <v>8.210000000000001</v>
+        <v>4.89</v>
       </c>
       <c r="Z45" t="n">
-        <v>19.7</v>
+        <v>11.91</v>
       </c>
       <c r="AA45" t="n">
-        <v>10.69</v>
+        <v>10.63</v>
       </c>
       <c r="AB45" t="n">
-        <v>33.52</v>
+        <v>19.49</v>
       </c>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AG45" t="n">
-        <v>39.88999938964844</v>
+        <v>21.54000091552734</v>
       </c>
       <c r="AH45" t="n">
-        <v>54.58</v>
+        <v>17.56</v>
       </c>
       <c r="AI45" t="n">
-        <v>33.23</v>
+        <v>13.53</v>
       </c>
       <c r="AJ45" t="n">
-        <v>46.2</v>
+        <v>30.72</v>
       </c>
       <c r="AK45" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="AL45" t="inlineStr"/>
+        <v>32.91</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>71.72</v>
+      </c>
       <c r="AM45" t="n">
-        <v>45.65</v>
+        <v>33.29</v>
       </c>
       <c r="AN45" t="n">
-        <v>47.4</v>
+        <v>30.72</v>
       </c>
       <c r="AO45" t="n">
-        <v>18.84</v>
+        <v>42.6</v>
       </c>
       <c r="AP45" t="n">
-        <v>14.45</v>
+        <v>54.53</v>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -20007,17 +20011,17 @@
       <c r="AU45" t="inlineStr"/>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW45" t="n">
-        <v>41.59000015258789</v>
+        <v>21.64999961853027</v>
       </c>
       <c r="AX45" t="n">
-        <v>-4.087522858144721</v>
+        <v>-0.5080771590812438</v>
       </c>
       <c r="AY45" t="n">
-        <v>-10.39229508845479</v>
+        <v>-19.64053433208342</v>
       </c>
       <c r="AZ45" t="b">
         <v>1</v>
@@ -20030,7 +20034,7 @@
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>sem sinal (-4.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-0.5% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -20051,13 +20055,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>57.97</v>
+        <v>57.86</v>
       </c>
       <c r="E46" t="n">
         <v>52.6</v>
       </c>
       <c r="F46" t="n">
-        <v>57.63</v>
+        <v>57.32</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
@@ -20359,7 +20363,7 @@
         <v>-4.020742883737105</v>
       </c>
       <c r="AY47" t="n">
-        <v>-14.35606196730216</v>
+        <v>-14.3560541194689</v>
       </c>
       <c r="AZ47" t="b">
         <v>1</v>
@@ -20393,13 +20397,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>56.5</v>
+        <v>56.47</v>
       </c>
       <c r="E48" t="n">
         <v>72.91</v>
       </c>
       <c r="F48" t="n">
-        <v>40.23</v>
+        <v>40.13</v>
       </c>
       <c r="G48" t="n">
         <v>75.81</v>
@@ -20566,13 +20570,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>55.95</v>
+        <v>56.18</v>
       </c>
       <c r="E49" t="n">
         <v>69.17</v>
       </c>
       <c r="F49" t="n">
-        <v>24.56</v>
+        <v>25.19</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
@@ -20634,14 +20638,12 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>87.75</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="n">
         <v>42.06999969482422</v>
       </c>
@@ -20649,28 +20651,26 @@
         <v>77.83</v>
       </c>
       <c r="AI49" t="n">
-        <v>60</v>
+        <v>47.38</v>
       </c>
       <c r="AJ49" t="n">
-        <v>60.8</v>
+        <v>48.02</v>
       </c>
       <c r="AK49" t="n">
         <v>24.44</v>
       </c>
-      <c r="AL49" t="n">
-        <v>94.65000000000001</v>
-      </c>
+      <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="n">
-        <v>63.54</v>
+        <v>49.42</v>
       </c>
       <c r="AN49" t="n">
-        <v>60.8</v>
+        <v>47.7</v>
       </c>
       <c r="AO49" t="n">
-        <v>44.53</v>
+        <v>13.38</v>
       </c>
       <c r="AP49" t="n">
-        <v>51.04</v>
+        <v>17.46</v>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
@@ -20916,13 +20916,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>55.09</v>
+        <v>55.07</v>
       </c>
       <c r="E51" t="n">
         <v>47.37</v>
       </c>
       <c r="F51" t="n">
-        <v>78.25</v>
+        <v>78.17</v>
       </c>
       <c r="G51" t="n">
         <v>55.3</v>
@@ -21079,7 +21079,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -21089,34 +21089,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>54.74</v>
+        <v>54.73</v>
       </c>
       <c r="E52" t="n">
-        <v>75.95999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="F52" t="n">
-        <v>37.59</v>
+        <v>57.67</v>
       </c>
       <c r="G52" t="n">
-        <v>26.44</v>
+        <v>56.6</v>
       </c>
       <c r="H52" t="n">
-        <v>77.27</v>
+        <v>19.7</v>
       </c>
       <c r="I52" t="n">
         <v>51</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L52" t="n">
         <v>7</v>
@@ -21131,13 +21131,13 @@
         <v>1</v>
       </c>
       <c r="P52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="b">
@@ -21147,69 +21147,65 @@
         <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>53406994432</v>
+        <v>53107621888</v>
       </c>
       <c r="W52" t="n">
-        <v>9.27</v>
+        <v>4.78</v>
       </c>
       <c r="X52" t="n">
-        <v>2.2</v>
+        <v>1.13</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.050000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="Z52" t="n">
-        <v>23.72</v>
+        <v>23.68</v>
       </c>
       <c r="AA52" t="n">
-        <v>15.33</v>
+        <v>6.83</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.79</v>
+        <v>22.96</v>
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="n">
-        <v>1.15</v>
+        <v>3.52</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0.52</v>
-      </c>
+        <v>2.02</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="n">
-        <v>46.34999847412109</v>
+        <v>43.02000045776367</v>
       </c>
       <c r="AH52" t="n">
-        <v>62.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI52" t="n">
-        <v>47.94</v>
+        <v>0.04</v>
       </c>
       <c r="AJ52" t="n">
-        <v>64.23999999999999</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="AK52" t="n">
-        <v>48.68</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>130.25</v>
-      </c>
+        <v>87.8</v>
+      </c>
+      <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="n">
-        <v>70.66</v>
+        <v>44.81</v>
       </c>
       <c r="AN52" t="n">
-        <v>62.19</v>
+        <v>43.94</v>
       </c>
       <c r="AO52" t="n">
-        <v>34.17</v>
+        <v>2.13</v>
       </c>
       <c r="AP52" t="n">
-        <v>52.45</v>
+        <v>4.16</v>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
@@ -21223,44 +21219,40 @@
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="AU52" t="inlineStr"/>
       <c r="AV52" t="inlineStr">
         <is>
           <t>Lateral</t>
         </is>
       </c>
       <c r="AW52" t="n">
-        <v>47.20000076293945</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="AX52" t="n">
-        <v>-1.80085227770963</v>
+        <v>-0.1856102533401627</v>
       </c>
       <c r="AY52" t="n">
-        <v>-12.53370020185791</v>
+        <v>-27.87197279000151</v>
       </c>
       <c r="AZ52" t="b">
         <v>1</v>
       </c>
       <c r="BA52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (-0.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -21270,34 +21262,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>54.73</v>
+        <v>54.68</v>
       </c>
       <c r="E53" t="n">
-        <v>66.16</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>57.67</v>
+        <v>37.39</v>
       </c>
       <c r="G53" t="n">
-        <v>56.6</v>
+        <v>26.44</v>
       </c>
       <c r="H53" t="n">
-        <v>19.7</v>
+        <v>77.27</v>
       </c>
       <c r="I53" t="n">
         <v>52</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L53" t="n">
         <v>7</v>
@@ -21312,13 +21304,13 @@
         <v>1</v>
       </c>
       <c r="P53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="b">
@@ -21328,65 +21320,69 @@
         <v>1</v>
       </c>
       <c r="V53" t="n">
-        <v>53107621888</v>
+        <v>53406994432</v>
       </c>
       <c r="W53" t="n">
-        <v>4.78</v>
+        <v>9.27</v>
       </c>
       <c r="X53" t="n">
-        <v>1.13</v>
+        <v>2.2</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.01</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Z53" t="n">
-        <v>23.68</v>
+        <v>23.72</v>
       </c>
       <c r="AA53" t="n">
-        <v>6.83</v>
+        <v>15.33</v>
       </c>
       <c r="AB53" t="n">
-        <v>22.96</v>
+        <v>12.79</v>
       </c>
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="n">
-        <v>3.52</v>
+        <v>1.15</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
+        <v>1.43</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.52</v>
+      </c>
       <c r="AG53" t="n">
-        <v>43.02000045776367</v>
+        <v>46.34999847412109</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.07000000000000001</v>
+        <v>62.19</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.04</v>
+        <v>47.94</v>
       </c>
       <c r="AJ53" t="n">
-        <v>91.31999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AK53" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="AL53" t="inlineStr"/>
+        <v>48.68</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>130.25</v>
+      </c>
       <c r="AM53" t="n">
-        <v>44.81</v>
+        <v>70.66</v>
       </c>
       <c r="AN53" t="n">
-        <v>43.94</v>
+        <v>62.19</v>
       </c>
       <c r="AO53" t="n">
-        <v>2.13</v>
+        <v>34.17</v>
       </c>
       <c r="AP53" t="n">
-        <v>4.16</v>
+        <v>52.45</v>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
@@ -21399,34 +21395,42 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>A CPFL Energia (CPFE3) apresenta-se como um ativo de alta qualidade operacional no setor de utilidade pública, com um retorno sobre o patrimônio líquido de 23,7% e um retorno sobre o capital investido de 15,3% que se posicionam significativamente acima das médias setoriais de 11,6% e 9,5%, respectivamente. Essa sólida rentabilidade convive com múltiplos de preço que sugerem um valuation misto, pois, embora o preço sobre valor patrimonial de 2,2 esteja acima dos pares, o preço sobre lucro de 9,27 e o indicador de crescimento PEG de 0,52 mostram-se atraentes frente à forte capacidade de geração de resultados da companhia. O robusto crescimento da empresa é evidenciado pela taxa de crescimento anual composta da receita nos últimos cinco anos de 18,0%, superando com folga a média negativa do setor de 10,1%, o que valida o cumprimento de seis dos sete critérios do checklist de investimento. No âmbito financeiro, a relação de dívida sobre o patrimônio de 1,43 reflete uma alavancagem que exige atenção, mas que é mitigada por uma liquidez corrente de 1,15 e pela alta eficiência operacional, sustentando um rendimento de dividendos de 8,05% que se mostra coerente com a forte geração de caixa e com o histórico de distribuição da empresa. Sob a ótica do valuation por múltiplos métodos de preço-teto, observa-se uma dispersão relevante entre as metodologias, variando desde os mais conservadores 47,94 reais pelo modelo de Gordon e 48,68 reais por Graham, passando por 62,19 reais por Bazin, até os mais otimistas 130,25 reais por Lynch. Essa disparidade resulta em uma média de 70,66 reais e uma mediana de 62,19 reais, o que confere ao papel um potencial de valorização de 34,2% em relação à mediana frente ao preço atual de 46,35 reais. Como principais prós, destacam-se a rentabilidade muito acima da média setorial, o forte crescimento histórico de receita e o atraente retorno em dividendos amparado por ótimos indicadores de qualidade. Em contrapartida, figuram como contras o nível de endividamento patrimonial relativamente elevado, uma margem líquida de 12,79% que não atinge o patamar ideal de 15% do checklist e a tendência gráfica lateralizada que reflete a atual indefinição do mercado no curto prazo.</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>Lateral</t>
         </is>
       </c>
       <c r="AW53" t="n">
-        <v>43.09999847412109</v>
+        <v>47.20000076293945</v>
       </c>
       <c r="AX53" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-1.80085227770963</v>
       </c>
       <c r="AY53" t="n">
-        <v>-27.87197279000151</v>
+        <v>-12.53370020185791</v>
       </c>
       <c r="AZ53" t="b">
         <v>1</v>
       </c>
       <c r="BA53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -21447,13 +21451,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>54.17</v>
+        <v>54.11</v>
       </c>
       <c r="E54" t="n">
         <v>78.66</v>
       </c>
       <c r="F54" t="n">
-        <v>22.48</v>
+        <v>22.25</v>
       </c>
       <c r="G54" t="n">
         <v>55.48</v>
@@ -21763,7 +21767,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY55" t="n">
-        <v>-23.47392377028176</v>
+        <v>-23.4739172343906</v>
       </c>
       <c r="AZ55" t="b">
         <v>1</v>
@@ -22272,13 +22276,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>51.93</v>
+        <v>51.8</v>
       </c>
       <c r="E59" t="n">
         <v>59.96</v>
       </c>
       <c r="F59" t="n">
-        <v>29.13</v>
+        <v>28.79</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
@@ -22580,7 +22584,7 @@
         <v>-2.68817586779716</v>
       </c>
       <c r="AY60" t="n">
-        <v>-50.51140559404919</v>
+        <v>-50.51140229842947</v>
       </c>
       <c r="AZ60" t="b">
         <v>1</v>
@@ -22753,7 +22757,7 @@
         <v>-0.9501178501326923</v>
       </c>
       <c r="AY61" t="n">
-        <v>-14.40870883002358</v>
+        <v>-14.40870028403989</v>
       </c>
       <c r="AZ61" t="b">
         <v>1</v>
@@ -22787,13 +22791,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>51.68</v>
+        <v>51.62</v>
       </c>
       <c r="E62" t="n">
         <v>46.49</v>
       </c>
       <c r="F62" t="n">
-        <v>70.33</v>
+        <v>70.13</v>
       </c>
       <c r="G62" t="n">
         <v>39.18</v>
@@ -23089,7 +23093,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr">
+        <is>
+          <t>A WEG (WEGE3) se consolida como uma empresa de altíssima eficiência operacional, apresentando um ROE de 33,2% e um ROIC de 24,3% que se posicionam muito acima dos pares do setor de bens industriais, os quais registram médias de 7,0% e 10,1%, respectivamente. Essa qualidade excepcional, contudo, convive com múltiplos de preço bastante esticados, evidenciados pelo P/L de 33,0 e pelo P/VP de 10,94, indicando que o mercado cobra um prêmio elevado por essa rentabilidade diferenciada. No balanço entre rentabilidade e endividamento, a companhia demonstra extrema solidez financeira ao associar sua forte margem líquida de 15,58% a uma baixa relação de dívida sobre o patrimônio de 0,29 e a uma confortável liquidez corrente de 1,59. O retorno em dividendos de 4,08% mostra-se coerente e sustentável diante da robusta geração de lucro e da estrutura de capital desalavancada, embora o crescimento de longo prazo acenda um sinal de alerta, visto que o CAGR de receita de cinco anos contraiu 2,1%, situando-se abaixo da média setorial de expansão de 14,9%. No checklist de critérios fundamentalistas, a empresa atende a 5 de 7 requisitos, falhando justamente na expansão de receita frente aos pares e na ocorrência de vendas por parte de insiders, o que se reflete em uma nota de qualidade de 86,0 contra um score de valor de apenas 4,0. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão acentuada, variando desde os R$ 33,44 pelo modelo de Bazin até os R$ 12,28 pela fórmula de Graham, resultando em uma média de R$ 20,30 e uma mediana de R$ 17,74. Frente ao preço atual de R$ 49,17, a mediana projeta um upside negativo de 63,9%, sugerindo que a cotação de mercado atual embutiu expectativas excessivamente otimistas que descolam o papel de suas referências teóricas de valor. Em suma, os principais prós do investimento residem na rentabilidade formidável, na saúde financeira impecável e na resiliência operacional, enquanto os contras concentram-se no valuation severamente esticado, no crescimento recente de receita abaixo do setor e na expressiva distância para os preços-teto calculados.</t>
+        </is>
+      </c>
       <c r="AU63" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -23107,7 +23115,7 @@
         <v>2.012442719195318</v>
       </c>
       <c r="AY63" t="n">
-        <v>-9.423154175560278</v>
+        <v>-9.423147674714317</v>
       </c>
       <c r="AZ63" t="b">
         <v>1</v>
@@ -23262,13 +23270,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>50.82</v>
+        <v>50.84</v>
       </c>
       <c r="E65" t="n">
         <v>57.31</v>
       </c>
       <c r="F65" t="n">
-        <v>29.72</v>
+        <v>29.79</v>
       </c>
       <c r="G65" t="n">
         <v>61.5</v>
@@ -23448,13 +23456,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>50.25</v>
+        <v>50.19</v>
       </c>
       <c r="E66" t="n">
         <v>39.71</v>
       </c>
       <c r="F66" t="n">
-        <v>63.02</v>
+        <v>62.84</v>
       </c>
       <c r="G66" t="n">
         <v>43.18</v>
@@ -23625,13 +23633,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>49.62</v>
+        <v>49.61</v>
       </c>
       <c r="E67" t="n">
         <v>11.21</v>
       </c>
       <c r="F67" t="n">
-        <v>85.59999999999999</v>
+        <v>85.55</v>
       </c>
       <c r="G67" t="n">
         <v>93.01000000000001</v>
@@ -23784,13 +23792,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>49.47</v>
+        <v>49.4</v>
       </c>
       <c r="E68" t="n">
         <v>47.58</v>
       </c>
       <c r="F68" t="n">
-        <v>39.02</v>
+        <v>38.77</v>
       </c>
       <c r="G68" t="n">
         <v>49.88</v>
@@ -23927,7 +23935,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY68" t="n">
-        <v>-23.22977049821228</v>
+        <v>-23.22975619580519</v>
       </c>
       <c r="AZ68" t="b">
         <v>1</v>
@@ -23961,13 +23969,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>49.14</v>
+        <v>49.15</v>
       </c>
       <c r="E69" t="n">
         <v>49.81</v>
       </c>
       <c r="F69" t="n">
-        <v>33.05</v>
+        <v>33.07</v>
       </c>
       <c r="G69" t="n">
         <v>44.78</v>
@@ -24100,7 +24108,7 @@
         <v>-1.302573977731003</v>
       </c>
       <c r="AY69" t="n">
-        <v>-15.92983151621281</v>
+        <v>-15.92982162987447</v>
       </c>
       <c r="AZ69" t="b">
         <v>0</v>
@@ -24293,7 +24301,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -24303,23 +24311,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>49.04</v>
+        <v>49</v>
       </c>
       <c r="E71" t="n">
-        <v>76.98</v>
+        <v>40.57</v>
       </c>
       <c r="F71" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="G71" t="n">
-        <v>45.81</v>
-      </c>
+        <v>66.67</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>32.58</v>
+        <v>33.33</v>
       </c>
       <c r="I71" t="n">
         <v>70</v>
@@ -24330,28 +24336,26 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q71" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="b">
@@ -24361,65 +24365,57 @@
         <v>1</v>
       </c>
       <c r="V71" t="n">
-        <v>98502926336</v>
+        <v>119829250048</v>
       </c>
       <c r="W71" t="n">
-        <v>11.31</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="X71" t="n">
-        <v>2.26</v>
+        <v>0.64</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="Z71" t="n">
-        <v>19.97</v>
+        <v>7.71</v>
       </c>
       <c r="AA71" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>22.03</v>
+        <v>20.42</v>
       </c>
       <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>0.73</v>
-      </c>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="n">
-        <v>28.01000022888184</v>
+        <v>20.98999977111816</v>
       </c>
       <c r="AH71" t="n">
-        <v>11.3</v>
+        <v>9.17</v>
       </c>
       <c r="AI71" t="n">
-        <v>8.710000000000001</v>
+        <v>5.58</v>
       </c>
       <c r="AJ71" t="n">
-        <v>31.82</v>
+        <v>25.48</v>
       </c>
       <c r="AK71" t="n">
-        <v>26.28</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>44.13</v>
-      </c>
+        <v>43.04</v>
+      </c>
+      <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="n">
-        <v>24.45</v>
+        <v>20.82</v>
       </c>
       <c r="AN71" t="n">
-        <v>26.28</v>
+        <v>17.32</v>
       </c>
       <c r="AO71" t="n">
-        <v>-6.18</v>
+        <v>-17.48</v>
       </c>
       <c r="AP71" t="n">
-        <v>-12.72</v>
+        <v>-0.83</v>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
@@ -24436,17 +24432,17 @@
       <c r="AU71" t="inlineStr"/>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW71" t="n">
-        <v>30.3700008392334</v>
+        <v>21.27000045776367</v>
       </c>
       <c r="AX71" t="n">
-        <v>-7.770828268476048</v>
+        <v>-1.316411286410224</v>
       </c>
       <c r="AY71" t="n">
-        <v>-20.69199954808616</v>
+        <v>-23.79046311986899</v>
       </c>
       <c r="AZ71" t="b">
         <v>0</v>
@@ -24459,14 +24455,14 @@
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.3% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -24476,21 +24472,23 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>49</v>
+        <v>48.97</v>
       </c>
       <c r="E72" t="n">
-        <v>40.57</v>
+        <v>76.98</v>
       </c>
       <c r="F72" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
+        <v>26.61</v>
+      </c>
+      <c r="G72" t="n">
+        <v>45.81</v>
+      </c>
       <c r="H72" t="n">
-        <v>33.33</v>
+        <v>32.58</v>
       </c>
       <c r="I72" t="n">
         <v>71</v>
@@ -24501,26 +24499,28 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>1</v>
+      </c>
       <c r="R72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="b">
@@ -24530,57 +24530,65 @@
         <v>1</v>
       </c>
       <c r="V72" t="n">
-        <v>119829250048</v>
+        <v>98502926336</v>
       </c>
       <c r="W72" t="n">
-        <v>8.359999999999999</v>
+        <v>11.31</v>
       </c>
       <c r="X72" t="n">
-        <v>0.64</v>
+        <v>2.26</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="Z72" t="n">
-        <v>7.71</v>
+        <v>19.97</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="AB72" t="n">
-        <v>20.42</v>
+        <v>22.03</v>
       </c>
       <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr"/>
-      <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr"/>
+      <c r="AD72" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0.73</v>
+      </c>
       <c r="AG72" t="n">
-        <v>20.98999977111816</v>
+        <v>28.01000022888184</v>
       </c>
       <c r="AH72" t="n">
-        <v>9.17</v>
+        <v>11.3</v>
       </c>
       <c r="AI72" t="n">
-        <v>5.58</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AJ72" t="n">
-        <v>25.48</v>
+        <v>31.82</v>
       </c>
       <c r="AK72" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="AL72" t="inlineStr"/>
+        <v>26.28</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>44.13</v>
+      </c>
       <c r="AM72" t="n">
-        <v>20.82</v>
+        <v>24.45</v>
       </c>
       <c r="AN72" t="n">
-        <v>17.32</v>
+        <v>26.28</v>
       </c>
       <c r="AO72" t="n">
-        <v>-17.48</v>
+        <v>-6.18</v>
       </c>
       <c r="AP72" t="n">
-        <v>-0.83</v>
+        <v>-12.72</v>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
@@ -24597,17 +24605,17 @@
       <c r="AU72" t="inlineStr"/>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW72" t="n">
-        <v>21.27000045776367</v>
+        <v>30.3700008392334</v>
       </c>
       <c r="AX72" t="n">
-        <v>-1.316411286410224</v>
+        <v>-7.770828268476048</v>
       </c>
       <c r="AY72" t="n">
-        <v>-23.79046311986899</v>
+        <v>-20.69199954808616</v>
       </c>
       <c r="AZ72" t="b">
         <v>0</v>
@@ -24620,7 +24628,7 @@
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24641,13 +24649,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>48.81</v>
+        <v>48.8</v>
       </c>
       <c r="E73" t="n">
         <v>11.15</v>
       </c>
       <c r="F73" t="n">
-        <v>72.75</v>
+        <v>72.72</v>
       </c>
       <c r="G73" t="n">
         <v>59.16</v>
@@ -24965,13 +24973,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>48.35</v>
+        <v>48.33</v>
       </c>
       <c r="E75" t="n">
         <v>57.76</v>
       </c>
       <c r="F75" t="n">
-        <v>40.97</v>
+        <v>40.89</v>
       </c>
       <c r="G75" t="n">
         <v>44</v>
@@ -25138,13 +25146,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>47.96</v>
+        <v>47.89</v>
       </c>
       <c r="E76" t="n">
         <v>36.84</v>
       </c>
       <c r="F76" t="n">
-        <v>41.11</v>
+        <v>40.89</v>
       </c>
       <c r="G76" t="n">
         <v>87.51000000000001</v>
@@ -25315,13 +25323,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>47.66</v>
+        <v>47.7</v>
       </c>
       <c r="E77" t="n">
         <v>64.36</v>
       </c>
       <c r="F77" t="n">
-        <v>18.31</v>
+        <v>18.39</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
@@ -25480,13 +25488,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>47.12</v>
+        <v>47.13</v>
       </c>
       <c r="E78" t="n">
         <v>28.1</v>
       </c>
       <c r="F78" t="n">
-        <v>47.14</v>
+        <v>47.18</v>
       </c>
       <c r="G78" t="n">
         <v>88.44</v>
@@ -25826,13 +25834,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>45.98</v>
+        <v>46</v>
       </c>
       <c r="E80" t="n">
         <v>77.04000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>15.76</v>
+        <v>15.83</v>
       </c>
       <c r="G80" t="n">
         <v>48.7</v>
@@ -26178,7 +26186,7 @@
         <v>35.72</v>
       </c>
       <c r="F82" t="n">
-        <v>35.34</v>
+        <v>35.36</v>
       </c>
       <c r="G82" t="n">
         <v>41.4</v>
@@ -26349,13 +26357,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>45.25</v>
+        <v>45.19</v>
       </c>
       <c r="E83" t="n">
         <v>20.96</v>
       </c>
       <c r="F83" t="n">
-        <v>53.03</v>
+        <v>52.86</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
@@ -26518,13 +26526,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>45.13</v>
+        <v>45.06</v>
       </c>
       <c r="E84" t="n">
         <v>62.01</v>
       </c>
       <c r="F84" t="n">
-        <v>35.71</v>
+        <v>35.47</v>
       </c>
       <c r="G84" t="n">
         <v>56.46</v>
@@ -26687,13 +26695,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>44.91</v>
+        <v>44.82</v>
       </c>
       <c r="E85" t="n">
         <v>61.26</v>
       </c>
       <c r="F85" t="n">
-        <v>32.76</v>
+        <v>32.53</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
@@ -26852,13 +26860,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>44.65</v>
+        <v>44.63</v>
       </c>
       <c r="E86" t="n">
         <v>21.43</v>
       </c>
       <c r="F86" t="n">
-        <v>88.47</v>
+        <v>88.42</v>
       </c>
       <c r="G86" t="n">
         <v>45.93</v>
@@ -27007,13 +27015,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>44.51</v>
+        <v>44.5</v>
       </c>
       <c r="E87" t="n">
         <v>14.87</v>
       </c>
       <c r="F87" t="n">
-        <v>96.61</v>
+        <v>96.59</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
@@ -27323,13 +27331,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>44.19</v>
+        <v>44.16</v>
       </c>
       <c r="E89" t="n">
         <v>45.6</v>
       </c>
       <c r="F89" t="n">
-        <v>35.39</v>
+        <v>35.31</v>
       </c>
       <c r="G89" t="n">
         <v>49.98</v>
@@ -27496,13 +27504,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>44.11</v>
+        <v>44.12</v>
       </c>
       <c r="E90" t="n">
         <v>54.18</v>
       </c>
       <c r="F90" t="n">
-        <v>42.27</v>
+        <v>42.32</v>
       </c>
       <c r="G90" t="n">
         <v>24.81</v>
@@ -27669,13 +27677,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>43.64</v>
+        <v>43.58</v>
       </c>
       <c r="E91" t="n">
         <v>53.08</v>
       </c>
       <c r="F91" t="n">
-        <v>38.32</v>
+        <v>38.13</v>
       </c>
       <c r="G91" t="n">
         <v>28.07</v>
@@ -28017,7 +28025,7 @@
         <v>30.54</v>
       </c>
       <c r="F93" t="n">
-        <v>81.84999999999999</v>
+        <v>81.84</v>
       </c>
       <c r="G93" t="n">
         <v>13.79</v>
@@ -28351,13 +28359,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>42.03</v>
+        <v>41.97</v>
       </c>
       <c r="E95" t="n">
         <v>41.63</v>
       </c>
       <c r="F95" t="n">
-        <v>39.01</v>
+        <v>38.81</v>
       </c>
       <c r="G95" t="n">
         <v>53.22</v>
@@ -28697,13 +28705,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>41.51</v>
+        <v>41.45</v>
       </c>
       <c r="E97" t="n">
         <v>49.62</v>
       </c>
       <c r="F97" t="n">
-        <v>36.54</v>
+        <v>36.34</v>
       </c>
       <c r="G97" t="n">
         <v>25.02</v>
@@ -29023,13 +29031,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>40.9</v>
+        <v>40.89</v>
       </c>
       <c r="E99" t="n">
         <v>15.04</v>
       </c>
       <c r="F99" t="n">
-        <v>80.52</v>
+        <v>80.48</v>
       </c>
       <c r="G99" t="n">
         <v>50.3</v>
@@ -29178,13 +29186,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>40.72</v>
+        <v>40.69</v>
       </c>
       <c r="E100" t="n">
         <v>54.38</v>
       </c>
       <c r="F100" t="n">
-        <v>51.72</v>
+        <v>51.62</v>
       </c>
       <c r="G100" t="n">
         <v>11.54</v>
@@ -29351,13 +29359,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>40.6</v>
+        <v>40.52</v>
       </c>
       <c r="E101" t="n">
         <v>45.31</v>
       </c>
       <c r="F101" t="n">
-        <v>55.92</v>
+        <v>55.66</v>
       </c>
       <c r="G101" t="n">
         <v>22.79</v>
@@ -29693,13 +29701,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>40.21</v>
+        <v>40.22</v>
       </c>
       <c r="E103" t="n">
         <v>23.38</v>
       </c>
       <c r="F103" t="n">
-        <v>44.93</v>
+        <v>44.95</v>
       </c>
       <c r="G103" t="n">
         <v>52.39</v>
@@ -31172,13 +31180,13 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>36.46</v>
+        <v>36.47</v>
       </c>
       <c r="E112" t="n">
         <v>34.6</v>
       </c>
       <c r="F112" t="n">
-        <v>28.75</v>
+        <v>28.76</v>
       </c>
       <c r="G112" t="n">
         <v>62.44</v>
@@ -31470,13 +31478,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>36.22</v>
+        <v>36.21</v>
       </c>
       <c r="E114" t="n">
         <v>17.95</v>
       </c>
       <c r="F114" t="n">
-        <v>60.21</v>
+        <v>60.17</v>
       </c>
       <c r="G114" t="n">
         <v>52.28</v>
@@ -31947,13 +31955,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>34.9</v>
+        <v>34.89</v>
       </c>
       <c r="E117" t="n">
         <v>19.77</v>
       </c>
       <c r="F117" t="n">
-        <v>85.16</v>
+        <v>85.13</v>
       </c>
       <c r="G117" t="n">
         <v>5.05</v>
@@ -32102,13 +32110,13 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>34.4</v>
+        <v>34.39</v>
       </c>
       <c r="E118" t="n">
         <v>33.89</v>
       </c>
       <c r="F118" t="n">
-        <v>67.34999999999999</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="G118" t="n">
         <v>4.59</v>
@@ -32261,7 +32269,7 @@
         <v>31.52</v>
       </c>
       <c r="F119" t="n">
-        <v>17.06</v>
+        <v>17.07</v>
       </c>
       <c r="G119" t="n">
         <v>33.61</v>
@@ -32760,13 +32768,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>33.2</v>
+        <v>33.22</v>
       </c>
       <c r="E122" t="n">
         <v>49.6</v>
       </c>
       <c r="F122" t="n">
-        <v>25.14</v>
+        <v>25.19</v>
       </c>
       <c r="G122" t="n">
         <v>23.34</v>
@@ -33408,13 +33416,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>30.59</v>
+        <v>30.6</v>
       </c>
       <c r="E126" t="n">
         <v>28.44</v>
       </c>
       <c r="F126" t="n">
-        <v>42.52</v>
+        <v>42.56</v>
       </c>
       <c r="G126" t="n">
         <v>21.79</v>
@@ -33859,7 +33867,7 @@
         <v>18.19</v>
       </c>
       <c r="F129" t="n">
-        <v>34.98</v>
+        <v>34.99</v>
       </c>
       <c r="G129" t="n">
         <v>52.42</v>
@@ -34022,13 +34030,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="E130" t="n">
         <v>41.92</v>
       </c>
       <c r="F130" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="G130" t="n">
         <v>53.49</v>
@@ -34197,7 +34205,7 @@
         <v>10.46</v>
       </c>
       <c r="F131" t="n">
-        <v>64.34999999999999</v>
+        <v>64.33</v>
       </c>
       <c r="G131" t="n">
         <v>19.93</v>
@@ -34346,13 +34354,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>25.69</v>
+        <v>25.67</v>
       </c>
       <c r="E132" t="n">
         <v>3.28</v>
       </c>
       <c r="F132" t="n">
-        <v>70.55</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="G132" t="n">
         <v>9.789999999999999</v>
@@ -34501,13 +34509,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>24.97</v>
+        <v>25</v>
       </c>
       <c r="E133" t="n">
         <v>34.52</v>
       </c>
       <c r="F133" t="n">
-        <v>12.58</v>
+        <v>12.65</v>
       </c>
       <c r="G133" t="n">
         <v>38.48</v>

--- a/reports/screener_2026-08-05.xlsx
+++ b/reports/screener_2026-08-05.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -1182,26 +1182,18 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>A análise fundamentalista do papel VLID3 revela uma sólida relação de qualidade e preço, uma vez que sua rentabilidade medida</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>18.40999984741211</v>
+        <v>18.65999984741211</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.357957642977081</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
         <v>-19.14564002354198</v>
@@ -1210,14 +1202,14 @@
         <v>1</v>
       </c>
       <c r="BA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -1375,10 +1367,10 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="AX5" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.41281066323299</v>
       </c>
       <c r="AY5" t="n">
         <v>-39.50409545018086</v>
@@ -1394,7 +1386,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>5791078400</v>
+        <v>5815617024</v>
       </c>
       <c r="W7" t="n">
         <v>3.66</v>
@@ -1663,26 +1655,26 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>14.15999984741211</v>
+        <v>14.22000026702881</v>
       </c>
       <c r="AH7" t="n">
-        <v>26.46</v>
+        <v>26.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>16.11</v>
+        <v>16.17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>39.25</v>
+        <v>39.42</v>
       </c>
       <c r="AK7" t="n">
-        <v>49.16</v>
+        <v>49.37</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
-        <v>32.74</v>
+        <v>32.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>32.86</v>
+        <v>32.99</v>
       </c>
       <c r="AO7" t="n">
         <v>132.03</v>
@@ -1707,8 +1699,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>insider selling (Yes). Criteria met: 2 of 6.
-    *   *Technical/Trend*: Pivot de</t>
+          <t>A análise fundamentalista do Banrisul (BRSR6) revela um ativo que transita entre uma clara compressão de múltiplos de preço e desafios operacionais de rentabilidade e crescimento. O papel é negociado a um P/L de 3,66 e um P/VP de 0,51, patamares historicamente baixos que convivem com um ROE de 14,0% e um ROIC de 0,0%, ambos situando-se abaixo dos pares do setor de serviços financeiros, que registram médias de 20,1% e 7,9%, respectivamente. Essa relação de qualidade versus preço sugere que, embora a rentabilidade da instituição esteja abaixo da média setorial, o mercado precifica o ativo com um desconto severo, criando uma assimetria favorável em termos de valor. No âmbito do crescimento, a receita da companhia encolheu a uma taxa composta anual (CAGR) de -8,3% nos últimos cinco anos, desempenho significativamente abaixo da média de expansão de 8,9% observada em seus pares, o que justifica o fato de o banco ter atendido a apenas 2 de 6 critérios no checklist de qualidade e crescimento. Por outro lado, a sustentabilidade do expressivo dividendo distribuído, com um dividend yield de 11,21%, encontra forte suporte na robusta margem líquida de 22,75%, indicando que a geração de lucro atual é plenamente capaz de manter o fluxo de proventos mesmo diante de uma receita em retração. Sob a ótica do valuation, as projeções de preço-teto apresentam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 16,17 pelo modelo de Gordon e R$ 26,57 pelo método de Bazin, até estimativas mais agressivas de R$ 39,42 via fluxo de caixa descontado e R$ 49,37 pela fórmula de Graham. Essa disparidade resulta em uma média de R$ 32,88 e uma mediana de R$ 32,99, valores que, quando comparados à cotação atual de R$ 14,22, sinalizam um potencial de valorização teórico de 132,0% em relação à mediana. Em suma, o investimento em BRSR6 coloca em balanço, como pontos positivos, o elevado retorno em dividendos, o desconto patrimonial extremo e a tendência gráfica de alta com pivô armado; em contrapartida, pesam negativamente a perda de eficiência frente aos concorrentes, a retração histórica de receita e o fraco desempenho no checklist de fundamentos.</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1722,13 +1713,13 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>14.47000026702881</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="AX7" t="n">
-        <v>-2.142366371084758</v>
+        <v>-1.591692354825192</v>
       </c>
       <c r="AY7" t="n">
-        <v>-23.9689549748106</v>
+        <v>-23.64678727321692</v>
       </c>
       <c r="AZ7" t="b">
         <v>1</v>
@@ -2068,10 +2059,10 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="AX9" t="n">
-        <v>-16.54525760371704</v>
+        <v>-14.90715866883865</v>
       </c>
       <c r="AY9" t="n">
         <v>-54.13720844041888</v>
@@ -2087,7 +2078,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -2281,13 +2272,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69.61</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>79.12</v>
       </c>
       <c r="F11" t="n">
-        <v>38.8</v>
+        <v>39.02</v>
       </c>
       <c r="G11" t="n">
         <v>84.34</v>
@@ -2412,7 +2403,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>A análise fundamentalista da TGMA3 revela uma empresa de alta qualidade operacional que combina forte rentabilidade com endivid</t>
+          <t>A Tegma (TGMA3) apresenta-se como uma operação de alta eficiência no setor de bens industriais, destacando-se por uma rentabilidade excepcional, com ROE de 25,6% e ROIC de 27,0%, ambos amplamente acima das médias setoriais de 7,0% e 10,1%, respectivamente. Essa expressiva qualidade operacional convive com múltiplos de preço que sugerem atratividade, visto que o P/L de 8,89 situa-se em patamar razoável e o P/VP de 2,27 reflete o forte prêmio sobre o valor patrimonial que o mercado concede a empresas de alto retorno. A sólida saúde financeira da companhia é evidenciada pela relação dívida/patrimônio de apenas 0,23, indicando que a alta rentabilidade é conquistada com baixo endividamento, enquanto a liquidez corrente de 2,22 garante robustez para honrar compromissos de curto prazo. Esse balanço desalavancado confere extrema sustentabilidade ao expressivo dividend yield de 11,23%, o qual se mostra plenamente coerente com a forte geração de lucro e com a capacidade de distribuição da empresa. No quesito expansão, a companhia supera seus pares com um crescimento composto anual (CAGR) de receita nos últimos cinco anos de 23,5%, contra a média setorial de 14,9%, o que é corroborado pelo PEG ratio de 0,38, sinalizando que o crescimento não está precificado de forma cara. O checklist de critérios fundamentalistas reforça essa consistência ao aprovar 6 dos 7 requisitos analisados, falhando apenas na margem líquida de 10,14%, que ficou abaixo do sarrafo de 15%. Sob a ótica de valuation, as estimativas de preço-teto revelam uma dispersão relevante entre os métodos, variando desde os mais conservadores R$ 36,11 por Graham até os R$ 115,41 por Lynch, estabelecendo uma mediana de R$ 49,43 que projeta um upside potencial de 44,5% frente ao preço atual de R$ 34,20. Em suma, os principais prós da tese residem no crescimento robusto acima do setor, no endividamento sob controle, no retorno sobre o capital elevado e nos proventos fartos, ao passo que os contras limitam-se à margem líquida abaixo do patamar ideal de 15% e à tendência gráfica lateralizada do papel no curto prazo.</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -2422,7 +2413,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW11" t="n">
@@ -2776,7 +2767,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -2799,7 +2790,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -2820,10 +2811,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.45999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>54.93</v>
+        <v>55.18</v>
       </c>
       <c r="F14" t="n">
         <v>56.73</v>
@@ -2957,10 +2948,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="AX14" t="n">
-        <v>-14.30768966674805</v>
+        <v>-12.4901748318072</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -2976,7 +2967,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -3130,10 +3121,10 @@
         </is>
       </c>
       <c r="AW15" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="AX15" t="n">
-        <v>-1.277582454837922</v>
+        <v>-2.118835116863982</v>
       </c>
       <c r="AY15" t="n">
         <v>-13.54395936495905</v>
@@ -3149,7 +3140,7 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-2.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1311239680</v>
+        <v>1316036864</v>
       </c>
       <c r="W16" t="n">
         <v>6.75</v>
@@ -3245,26 +3236,26 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
-        <v>8.199999809265137</v>
+        <v>8.229999542236328</v>
       </c>
       <c r="AH16" t="n">
-        <v>10.48</v>
+        <v>10.52</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12.33</v>
+        <v>12.37</v>
       </c>
       <c r="AK16" t="n">
-        <v>10.83</v>
+        <v>10.87</v>
       </c>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN16" t="n">
-        <v>10.66</v>
+        <v>10.7</v>
       </c>
       <c r="AO16" t="n">
         <v>29.97</v>
@@ -3295,13 +3286,13 @@
         </is>
       </c>
       <c r="AW16" t="n">
-        <v>8.520000457763672</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="AX16" t="n">
-        <v>-3.7558759542899</v>
+        <v>-2.372488205209888</v>
       </c>
       <c r="AY16" t="n">
-        <v>-18.10280183820145</v>
+        <v>-17.80318060245866</v>
       </c>
       <c r="AZ16" t="b">
         <v>1</v>
@@ -3314,7 +3305,7 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>sem sinal (-3.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.4% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>4914711040</v>
+        <v>4934343168</v>
       </c>
       <c r="W18" t="n">
         <v>8.25</v>
@@ -3593,28 +3584,28 @@
         <v>0.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>15.02000045776367</v>
+        <v>15.07999992370605</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.03</v>
+        <v>20.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>15.44</v>
+        <v>15.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23.39</v>
+        <v>23.49</v>
       </c>
       <c r="AK18" t="n">
-        <v>20.32</v>
+        <v>20.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>40.6</v>
+        <v>40.76</v>
       </c>
       <c r="AM18" t="n">
-        <v>23.96</v>
+        <v>24.05</v>
       </c>
       <c r="AN18" t="n">
-        <v>20.32</v>
+        <v>20.4</v>
       </c>
       <c r="AO18" t="n">
         <v>35.29</v>
@@ -3639,7 +3630,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
+          <t>A Intelbras (INTB3) apresenta-se como uma alternativa robusta no setor industrial, destacando-se por uma notável eficiência operacional, uma vez que seu ROE de 18,1% e seu ROIC de 17,5% situam-se significativamente acima dos pares setoriais, que registram 7,0% e 10,1%, respectivamente. Essa elevada qualidade de rentabilidade convive com múltiplos de preço bastante atrativos, evidenciados por um P/L de 8,25 e um P/VP de 1,49, o que sugere uma clara assimetria favorável entre o valor entregue pela companhia e o preço cobrado pelo mercado. A saúde financeira da empresa é outro ponto forte, pois a alta rentabilidade é sustentada por um endividamento extremamente controlado, com uma relação Dívida/Patrimônio de apenas 0,26 e uma sólida liquidez corrente de 2,64. Esse balanço desalavancado confere total sustentabilidade ao expressivo dividend yield de 8,0%, o qual se mostra plenamente coerente com a geração de lucro e a capacidade de distribuição da empresa. No quesito expansão, embora o crescimento de receita nos últimos cinco anos tenha sido expressivo, a taxa de 14,3% ficou ligeiramente abaixo da média do setor de 14,9%, um fator que, somado à margem líquida de 13,1%, fez com que a companhia atendesse a 5 dos 7 critérios do checklist fundamentalista. Sob a ótica de valuation, as estimativas de preço-teto revelam uma dispersão relevante entre os métodos, variando desde os conservadores R$ 15,50 pelo modelo de Gordon até os otimistas R$ 40,76 pelo critério de Lynch, estabelecendo uma mediana de R$ 20,40 que projeta um upside potencial de 35,3% frente à cotação atual de R$ 15,08. Em suma, o papel contrapõe, como prós, uma excelente rentabilidade sobre o capital, baixo endividamento, dividendos robustos e valuation descontado, tendo como contras um crescimento de receita ligeiramente inferior ao de seus pares e uma margem líquida que ainda não atinge o patamar ideal de 15%.</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -3653,13 +3644,13 @@
         </is>
       </c>
       <c r="AW18" t="n">
-        <v>14.38436412811279</v>
+        <v>15.02000045776367</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.418939370483477</v>
+        <v>0.3994638090131897</v>
       </c>
       <c r="AY18" t="n">
-        <v>-4.081037600189341</v>
+        <v>-3.697876059421112</v>
       </c>
       <c r="AZ18" t="b">
         <v>1</v>
@@ -4353,10 +4344,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.129361865388501</v>
+        <v>-1.814843745989081</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -4372,7 +4363,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -4393,13 +4384,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62.86</v>
+        <v>62.94</v>
       </c>
       <c r="E23" t="n">
         <v>78.42</v>
       </c>
       <c r="F23" t="n">
-        <v>38.18</v>
+        <v>38.47</v>
       </c>
       <c r="G23" t="n">
         <v>90.23</v>
@@ -4797,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2087424256</v>
+        <v>2084035712</v>
       </c>
       <c r="W25" t="n">
         <v>13.46</v>
@@ -4870,7 +4861,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>A análise fundamentalista da FESA4 revela um cenário de baixa rentabilidade e contração operacional, evidenciado pelo RO</t>
+          <t>A Ferbasa (FESA4) apresenta-se atualmente como um caso de estudo intrigante, onde a baixa valorização de mercado contrasta com desafios operacionais recentes no setor de materiais básicos. A qualidade atual da companhia, refletida em um ROE de 4,9% e um ROIC de 4,4% — ambos situando-se abaixo dos pares do setor, que registram 10,6% e 7,5% respectivamente —, convive com múltiplos de preço descontados, visto que o P/L de 13,46 e o P/VP de 0,66 sugerem que o mercado já precifica essa rentabilidade mais tímida. Essa compressão de margens e retornos é acompanhada por uma estrutura de capital extremamente robusta, evidenciada pela relação dívida/patrimônio de apenas 0,12 e uma folgada liquidez corrente de 3,27, indicando que a saúde financeira da empresa permanece blindada contra intempéries. O generoso dividend yield de 11,4% mostra-se surpreendentemente elevado frente ao lucro e à rentabilidade atuais, mas encontra sustentabilidade na ausência de alavancagem financeira sufocante, embora o investidor deva monitorar a perenidade desse fluxo caso a contração operacional persista. No quesito expansão, o crescimento da empresa passa por um momento de forte pressão, com o CAGR de receita de cinco anos negativo em 7,9%, bem abaixo da média setorial de 17,4%, o que justifica o fato de a companhia ter atendido a apenas um dos sete critérios do checklist fundamentalista aplicado. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 4,64 pelo fluxo de caixa descontado até os otimistas R$ 11,7 pelo método de Bazin, estabelecendo uma mediana de R$ 8,46 que projeta um upside de 37,4% sobre a cotação atual de R$ 6,16. Em um balanço final, os principais pontos positivos residem na sólida segurança financeira, no robusto retorno via proventos e no desconto patrimonial atrativo, enquanto os pontos negativos concentram-se na perda de eficiência operacional frente aos concorrentes, no encolhimento histórico das receitas e no fraco desempenho no checklist de qualidade.</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -4924,13 +4915,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62.02</v>
+        <v>62.11</v>
       </c>
       <c r="E26" t="n">
         <v>67.77</v>
       </c>
       <c r="F26" t="n">
-        <v>45.2</v>
+        <v>45.49</v>
       </c>
       <c r="G26" t="n">
         <v>73.7</v>
@@ -5057,10 +5048,10 @@
         </is>
       </c>
       <c r="AW26" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="AX26" t="n">
-        <v>-3.49544105988292</v>
+        <v>-3.053439393562163</v>
       </c>
       <c r="AY26" t="n">
         <v>-39.52381043207078</v>
@@ -5076,7 +5067,7 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5107,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -5226,26 +5217,18 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>Yes, Net Debt/EBITDA &lt; 3 and &lt;= sector: n/d, market cap &gt;= 300</t>
-        </is>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW27" t="n">
-        <v>32.34000015258789</v>
+        <v>32.47999954223633</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.4328985435618105</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
         <v>-10.30102081343549</v>
@@ -5254,14 +5237,14 @@
         <v>1</v>
       </c>
       <c r="BA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5529,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY29" t="n">
-        <v>-39.51924817380552</v>
+        <v>-39.51925640744687</v>
       </c>
       <c r="AZ29" t="b">
         <v>1</v>
@@ -5701,12 +5684,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>4. Correlate indicators (not just list them)? Yes.
-        5. Position each indicator vs. sector average</t>
-        </is>
-      </c>
+      <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -5724,7 +5702,7 @@
         <v>0.5876255599746028</v>
       </c>
       <c r="AY30" t="n">
-        <v>-20.18449126434217</v>
+        <v>-20.18448271439143</v>
       </c>
       <c r="AZ30" t="b">
         <v>1</v>
@@ -5954,7 +5932,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -6064,27 +6042,18 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>0m: Yes, no insider selling: No).
-    *   *Technical*: Breakout (Rompimento),</t>
-        </is>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
       <c r="AV32" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW32" t="n">
-        <v>12.21000003814697</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.146603954835057</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
         <v>-12.59730869465475</v>
@@ -6093,14 +6062,14 @@
         <v>1</v>
       </c>
       <c r="BA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6221,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY33" t="n">
-        <v>-12.46352623832258</v>
+        <v>-12.46350726988326</v>
       </c>
       <c r="AZ33" t="b">
         <v>1</v>
@@ -6411,7 +6380,7 @@
       <c r="AU34" t="inlineStr"/>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW34" t="n">
@@ -6434,7 +6403,7 @@
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -6761,10 +6730,10 @@
         </is>
       </c>
       <c r="AW36" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="AX36" t="n">
-        <v>-2.285715311515235</v>
+        <v>-2.252858377438904</v>
       </c>
       <c r="AY36" t="n">
         <v>-17.59775069846685</v>
@@ -6934,10 +6903,10 @@
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="AX37" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-1.98511558212644</v>
       </c>
       <c r="AY37" t="n">
         <v>-47.92224740248528</v>
@@ -6953,7 +6922,7 @@
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -7111,10 +7080,10 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="AX38" t="n">
-        <v>-3.418800283779255</v>
+        <v>-3.004289078750577</v>
       </c>
       <c r="AY38" t="n">
         <v>-52.18694930098489</v>
@@ -7130,7 +7099,7 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7139,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -7205,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2549322752</v>
+        <v>2570927104</v>
       </c>
       <c r="W39" t="n">
         <v>7.8</v>
@@ -7236,28 +7205,28 @@
         <v>0.01</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.539999961853027</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="AH39" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AJ39" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="AK39" t="n">
-        <v>6.94</v>
+        <v>7</v>
       </c>
       <c r="AL39" t="n">
-        <v>13.62</v>
+        <v>13.73</v>
       </c>
       <c r="AM39" t="n">
-        <v>6.67</v>
+        <v>6.73</v>
       </c>
       <c r="AN39" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="AO39" t="n">
         <v>64.72</v>
@@ -7281,33 +7250,37 @@
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>3.630000114440918</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="AX39" t="n">
-        <v>-2.479342968333542</v>
+        <v>0.847456828052251</v>
       </c>
       <c r="AY39" t="n">
-        <v>-53.54330688952109</v>
+        <v>-53.14960647166905</v>
       </c>
       <c r="AZ39" t="b">
         <v>1</v>
       </c>
       <c r="BA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>6174486528</v>
+        <v>6182217728</v>
       </c>
       <c r="W41" t="n">
         <v>6.2</v>
@@ -7578,28 +7551,28 @@
         <v>2.95</v>
       </c>
       <c r="AG41" t="n">
-        <v>23.95999908447266</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="AH41" t="n">
-        <v>42.25</v>
+        <v>42.3</v>
       </c>
       <c r="AI41" t="n">
-        <v>21.3</v>
+        <v>21.33</v>
       </c>
       <c r="AJ41" t="n">
-        <v>32.47</v>
+        <v>32.52</v>
       </c>
       <c r="AK41" t="n">
-        <v>48.94</v>
+        <v>49</v>
       </c>
       <c r="AL41" t="n">
-        <v>49</v>
+        <v>49.06</v>
       </c>
       <c r="AM41" t="n">
-        <v>38.79</v>
+        <v>38.84</v>
       </c>
       <c r="AN41" t="n">
-        <v>42.25</v>
+        <v>42.3</v>
       </c>
       <c r="AO41" t="n">
         <v>76.33</v>
@@ -7633,10 +7606,10 @@
         <v>24.09000015258789</v>
       </c>
       <c r="AX41" t="n">
-        <v>-0.5396474358314585</v>
+        <v>-0.4151115850407505</v>
       </c>
       <c r="AY41" t="n">
-        <v>-12.32560412402255</v>
+        <v>-12.21582565248605</v>
       </c>
       <c r="AZ41" t="b">
         <v>1</v>
@@ -7649,7 +7622,7 @@
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>sem sinal (-0.5% do topo; Lateral)</t>
+          <t>sem sinal (-0.4% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2260919552</v>
+        <v>2290645504</v>
       </c>
       <c r="W42" t="n">
         <v>5.65</v>
@@ -8320,7 +8293,7 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>setor Não, Dív.Líq/EBITDA n/d, sem venda de insiders Não).</t>
+          <t>A análise do Banco BMG (BMGB4) sob a ótica fundamentalista revela um ativo que transita em uma tendência lateral de preços, com sinal gráfico de rompimento e uma clara assimetria entre múltiplos descontados e indicadores de eficiência. O retorno sobre o patrimônio líquido (ROE) de 14,0% e o retorno sobre o capital investido (ROIC) de 0,0% situam-se abaixo dos pares do setor de serviços financeiros, que registram médias de 20,1% e 7,9%, respectivamente, sugerindo que a instituição enfrenta desafios para rentabilizar seus recursos no mesmo patamar de seus concorrentes. Essa menor rentabilidade relativa, contudo, convive com múltiplos de preço bastante depreciados, visto que o preço sobre o lucro (P/L) de 5,97 e o preço sobre o valor patrimonial (P/VP) de 0,83 indicam um papel negociado com desconto em relação ao seu valor de livro. O dividend yield de 7,41% mostra-se atrativo e coerente com a forte margem líquida de 28,17%, sugerindo que a distribuição de proventos possui sustentabilidade lastreada na conversão de receitas em lucro líquido, mesmo diante de um crescimento histórico de receita nos últimos cinco anos de 8,6%, ligeiramente abaixo da média setorial de 8,9%. No que tange ao checklist de critérios de qualidade e segurança, o ativo atendeu a apenas um dos seis requisitos aplicáveis, penalizado principalmente pelo ROE inferior à taxa Selic e à média do setor, pelo ROIC abaixo dos pares e pela presença de vendas por parte de insiders, embora preserve a segurança de um valor de mercado robusto de aproximadamente 3,52 bilhões de reais. Sob a perspectiva de valuation, as projeções de preço-teto apresentam uma dispersão acentuada entre as metodologias, variando desde os conservadores 5,20 reais pelo modelo de Gordon e 6,74 reais por Bazin, até estimativas mais otimistas de 11,63 reais por Graham, 11,75 reais por fluxo de caixa descontado e 14,64 reais pelo modelo de Lynch. Essa disparidade resulta em uma média de 9,99 reais e uma mediana de 11,63 reais, o que projeta um expressivo potencial de valorização de 113,1% frente ao preço atual de 5,46 reais. Em balanço, os principais prós residem no valuation descontado, no carrego atraente de dividendos e no elevado potencial de valorização implícito nas métricas de preço-teto, enquanto os contras concentram-se na rentabilidade inferior à média do setor, no crescimento de receita abaixo dos pares e no fraco desempenho no checklist de critérios fundamentais.</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
@@ -8829,11 +8802,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT48" t="inlineStr">
-        <is>
-          <t>A análise fundamentalista do papel BBSE3 revela uma empresa de altíssima rentabilidade sobre o patrimônio líquido, com</t>
-        </is>
-      </c>
+      <c r="AT48" t="inlineStr"/>
       <c r="AU48" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -9018,10 +8987,10 @@
         </is>
       </c>
       <c r="AW49" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>-0.5291042223046771</v>
       </c>
       <c r="AY49" t="n">
         <v>-15.4147281673955</v>
@@ -9037,7 +9006,7 @@
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9081,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>4499459584</v>
+        <v>4531737088</v>
       </c>
       <c r="W50" t="n">
         <v>5.54</v>
@@ -9143,28 +9112,28 @@
         <v>0.08</v>
       </c>
       <c r="AG50" t="n">
-        <v>13.9399995803833</v>
+        <v>14.03999996185303</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AJ50" t="n">
-        <v>32.33</v>
+        <v>32.56</v>
       </c>
       <c r="AK50" t="n">
-        <v>35.39</v>
+        <v>35.65</v>
       </c>
       <c r="AL50" t="n">
-        <v>75.48999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="AM50" t="n">
-        <v>29.92</v>
+        <v>30.13</v>
       </c>
       <c r="AN50" t="n">
-        <v>32.33</v>
+        <v>32.56</v>
       </c>
       <c r="AO50" t="n">
         <v>131.92</v>
@@ -9195,13 +9164,13 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>16.3700008392334</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="AX50" t="n">
-        <v>-14.84423417392992</v>
+        <v>-12.52336056544037</v>
       </c>
       <c r="AY50" t="n">
-        <v>-34.85117715011583</v>
+        <v>-34.38382368287039</v>
       </c>
       <c r="AZ50" t="b">
         <v>1</v>
@@ -9214,7 +9183,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -9364,14 +9333,14 @@
       <c r="AU51" t="inlineStr"/>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW51" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="AX51" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-0.6925190193304398</v>
       </c>
       <c r="AY51" t="n">
         <v>-27.87197279000151</v>
@@ -9387,7 +9356,7 @@
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>sem sinal (-0.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9537,11 +9506,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT52" t="inlineStr">
-        <is>
-          <t>A CPFL Energia (CPFE3) apresenta-se como um ativo de alta qualidade operacional no setor de utilidade pública, com um retorno sobre o patrimônio líquido de 23,7% e um retorno sobre o capital investido de 15,3% que se posicionam significativamente acima das médias setoriais de 11,6% e 9,5%, respectivamente. Essa sólida rentabilidade convive com múltiplos de preço que sugerem um valuation misto, pois, embora o preço sobre valor patrimonial de 2,2 esteja acima dos pares, o preço sobre lucro de 9,27 e o indicador de crescimento PEG de 0,52 mostram-se atraentes frente à forte capacidade de geração de resultados da companhia. O robusto crescimento da empresa é evidenciado pela taxa de crescimento anual composta da receita nos últimos cinco anos de 18,0%, superando com folga a média negativa do setor de 10,1%, o que valida o cumprimento de seis dos sete critérios do checklist de investimento. No âmbito financeiro, a relação de dívida sobre o patrimônio de 1,43 reflete uma alavancagem que exige atenção, mas que é mitigada por uma liquidez corrente de 1,15 e pela alta eficiência operacional, sustentando um rendimento de dividendos de 8,05% que se mostra coerente com a forte geração de caixa e com o histórico de distribuição da empresa. Sob a ótica do valuation por múltiplos métodos de preço-teto, observa-se uma dispersão relevante entre as metodologias, variando desde os mais conservadores 47,94 reais pelo modelo de Gordon e 48,68 reais por Graham, passando por 62,19 reais por Bazin, até os mais otimistas 130,25 reais por Lynch. Essa disparidade resulta em uma média de 70,66 reais e uma mediana de 62,19 reais, o que confere ao papel um potencial de valorização de 34,2% em relação à mediana frente ao preço atual de 46,35 reais. Como principais prós, destacam-se a rentabilidade muito acima da média setorial, o forte crescimento histórico de receita e o atraente retorno em dividendos amparado por ótimos indicadores de qualidade. Em contrapartida, figuram como contras o nível de endividamento patrimonial relativamente elevado, uma margem líquida de 12,79% que não atinge o patamar ideal de 15% do checklist e a tendência gráfica lateralizada que reflete a atual indefinição do mercado no curto prazo.</t>
-        </is>
-      </c>
+      <c r="AT52" t="inlineStr"/>
       <c r="AU52" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -9909,7 +9874,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY54" t="n">
-        <v>-23.4739172343906</v>
+        <v>-23.47392377028176</v>
       </c>
       <c r="AZ54" t="b">
         <v>1</v>
@@ -9997,7 +9962,7 @@
         <v>1</v>
       </c>
       <c r="V55" t="n">
-        <v>15677621248</v>
+        <v>15691892736</v>
       </c>
       <c r="W55" t="n">
         <v>9.75</v>
@@ -10026,26 +9991,26 @@
       </c>
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="n">
-        <v>32.95999908447266</v>
+        <v>32.9900016784668</v>
       </c>
       <c r="AH55" t="n">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="AI55" t="n">
-        <v>10.97</v>
+        <v>10.98</v>
       </c>
       <c r="AJ55" t="n">
-        <v>34.3</v>
+        <v>34.33</v>
       </c>
       <c r="AK55" t="n">
-        <v>46.29</v>
+        <v>46.33</v>
       </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="n">
-        <v>27.39</v>
+        <v>27.42</v>
       </c>
       <c r="AN55" t="n">
-        <v>26.16</v>
+        <v>26.18</v>
       </c>
       <c r="AO55" t="n">
         <v>-20.63</v>
@@ -10068,11 +10033,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT55" t="inlineStr">
-        <is>
-          <t>Liq/EBITDA (n/d), market cap &gt;= 300mi (Yes), no insider selling</t>
-        </is>
-      </c>
+      <c r="AT55" t="inlineStr"/>
       <c r="AU55" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -10084,13 +10045,13 @@
         </is>
       </c>
       <c r="AW55" t="n">
-        <v>34.11000061035156</v>
+        <v>33.75</v>
       </c>
       <c r="AX55" t="n">
-        <v>-3.371449737030807</v>
+        <v>-2.251846878616903</v>
       </c>
       <c r="AY55" t="n">
-        <v>-10.60545926870959</v>
+        <v>-10.52408584075593</v>
       </c>
       <c r="AZ55" t="b">
         <v>1</v>
@@ -10547,13 +10508,13 @@
         </is>
       </c>
       <c r="AW58" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="AX58" t="n">
-        <v>-3.506767262291599</v>
+        <v>-3.465848880756128</v>
       </c>
       <c r="AY58" t="n">
-        <v>-13.58724744836764</v>
+        <v>-13.55060950604702</v>
       </c>
       <c r="AZ58" t="b">
         <v>1</v>
@@ -10716,7 +10677,7 @@
       <c r="AU59" t="inlineStr"/>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW59" t="n">
@@ -10739,7 +10700,7 @@
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -11110,13 +11071,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>51.4</v>
+        <v>51.48</v>
       </c>
       <c r="E62" t="n">
         <v>85.64</v>
       </c>
       <c r="F62" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="G62" t="n">
         <v>64.13</v>
@@ -11235,11 +11196,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT62" t="inlineStr">
-        <is>
-          <t>A WEG (WEGE3) se consolida como uma empresa de altíssima eficiência operacional, apresentando um ROE de 33,2% e um ROIC de 24,3% que se posicionam muito acima dos pares do setor de bens industriais, os quais registram médias de 7,0% e 10,1%, respectivamente. Essa qualidade excepcional, contudo, convive com múltiplos de preço bastante esticados, evidenciados pelo P/L de 33,0 e pelo P/VP de 10,94, indicando que o mercado cobra um prêmio elevado por essa rentabilidade diferenciada. No balanço entre rentabilidade e endividamento, a companhia demonstra extrema solidez financeira ao associar sua forte margem líquida de 15,58% a uma baixa relação de dívida sobre o patrimônio de 0,29 e a uma confortável liquidez corrente de 1,59. O retorno em dividendos de 4,08% mostra-se coerente e sustentável diante da robusta geração de lucro e da estrutura de capital desalavancada, embora o crescimento de longo prazo acenda um sinal de alerta, visto que o CAGR de receita de cinco anos contraiu 2,1%, situando-se abaixo da média setorial de expansão de 14,9%. No checklist de critérios fundamentalistas, a empresa atende a 5 de 7 requisitos, falhando justamente na expansão de receita frente aos pares e na ocorrência de vendas por parte de insiders, o que se reflete em uma nota de qualidade de 86,0 contra um score de valor de apenas 4,0. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão acentuada, variando desde os R$ 33,44 pelo modelo de Bazin até os R$ 12,28 pela fórmula de Graham, resultando em uma média de R$ 20,30 e uma mediana de R$ 17,74. Frente ao preço atual de R$ 49,17, a mediana projeta um upside negativo de 63,9%, sugerindo que a cotação de mercado atual embutiu expectativas excessivamente otimistas que descolam o papel de suas referências teóricas de valor. Em suma, os principais prós do investimento residem na rentabilidade formidável, na saúde financeira impecável e na resiliência operacional, enquanto os contras concentram-se no valuation severamente esticado, no crescimento recente de receita abaixo do setor e na expressiva distância para os preços-teto calculados.</t>
-        </is>
-      </c>
+      <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -11541,12 +11498,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT64" t="inlineStr">
-        <is>
-          <t>Selic, ROIC&gt;=sector, margin&gt;=15%, CAGR&gt;=sector).
-    *   *Technical/Trend*:</t>
-        </is>
-      </c>
+      <c r="AT64" t="inlineStr"/>
       <c r="AU64" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -12077,7 +12029,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY67" t="n">
-        <v>-23.22975619580519</v>
+        <v>-23.22976334700939</v>
       </c>
       <c r="AZ67" t="b">
         <v>1</v>
@@ -12767,7 +12719,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -12873,26 +12825,18 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>A análise fundamentalista do papel VLID3 revela uma sólida relação de qualidade e preço, uma vez que sua rentabilidade medida</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>18.40999984741211</v>
+        <v>18.65999984741211</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.357957642977081</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
         <v>-19.14564002354198</v>
@@ -12901,14 +12845,14 @@
         <v>1</v>
       </c>
       <c r="BA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -13066,10 +13010,10 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>5.639999866485596</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="AX5" t="n">
-        <v>-14.71631105238386</v>
+        <v>-14.41281066323299</v>
       </c>
       <c r="AY5" t="n">
         <v>-39.50409545018086</v>
@@ -13085,7 +13029,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>sem sinal (-14.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13273,7 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>5791078400</v>
+        <v>5815617024</v>
       </c>
       <c r="W7" t="n">
         <v>3.66</v>
@@ -13354,26 +13298,26 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>14.15999984741211</v>
+        <v>14.22000026702881</v>
       </c>
       <c r="AH7" t="n">
-        <v>26.46</v>
+        <v>26.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>16.11</v>
+        <v>16.17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>39.25</v>
+        <v>39.42</v>
       </c>
       <c r="AK7" t="n">
-        <v>49.16</v>
+        <v>49.37</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
-        <v>32.74</v>
+        <v>32.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>32.86</v>
+        <v>32.99</v>
       </c>
       <c r="AO7" t="n">
         <v>132.03</v>
@@ -13398,8 +13342,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>insider selling (Yes). Criteria met: 2 of 6.
-    *   *Technical/Trend*: Pivot de</t>
+          <t>A análise fundamentalista do Banrisul (BRSR6) revela um ativo que transita entre uma clara compressão de múltiplos de preço e desafios operacionais de rentabilidade e crescimento. O papel é negociado a um P/L de 3,66 e um P/VP de 0,51, patamares historicamente baixos que convivem com um ROE de 14,0% e um ROIC de 0,0%, ambos situando-se abaixo dos pares do setor de serviços financeiros, que registram médias de 20,1% e 7,9%, respectivamente. Essa relação de qualidade versus preço sugere que, embora a rentabilidade da instituição esteja abaixo da média setorial, o mercado precifica o ativo com um desconto severo, criando uma assimetria favorável em termos de valor. No âmbito do crescimento, a receita da companhia encolheu a uma taxa composta anual (CAGR) de -8,3% nos últimos cinco anos, desempenho significativamente abaixo da média de expansão de 8,9% observada em seus pares, o que justifica o fato de o banco ter atendido a apenas 2 de 6 critérios no checklist de qualidade e crescimento. Por outro lado, a sustentabilidade do expressivo dividendo distribuído, com um dividend yield de 11,21%, encontra forte suporte na robusta margem líquida de 22,75%, indicando que a geração de lucro atual é plenamente capaz de manter o fluxo de proventos mesmo diante de uma receita em retração. Sob a ótica do valuation, as projeções de preço-teto apresentam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 16,17 pelo modelo de Gordon e R$ 26,57 pelo método de Bazin, até estimativas mais agressivas de R$ 39,42 via fluxo de caixa descontado e R$ 49,37 pela fórmula de Graham. Essa disparidade resulta em uma média de R$ 32,88 e uma mediana de R$ 32,99, valores que, quando comparados à cotação atual de R$ 14,22, sinalizam um potencial de valorização teórico de 132,0% em relação à mediana. Em suma, o investimento em BRSR6 coloca em balanço, como pontos positivos, o elevado retorno em dividendos, o desconto patrimonial extremo e a tendência gráfica de alta com pivô armado; em contrapartida, pesam negativamente a perda de eficiência frente aos concorrentes, a retração histórica de receita e o fraco desempenho no checklist de fundamentos.</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -13413,13 +13356,13 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>14.47000026702881</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="AX7" t="n">
-        <v>-2.142366371084758</v>
+        <v>-1.591692354825192</v>
       </c>
       <c r="AY7" t="n">
-        <v>-23.9689549748106</v>
+        <v>-23.64678727321692</v>
       </c>
       <c r="AZ7" t="b">
         <v>1</v>
@@ -13759,10 +13702,10 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>19.21999931335449</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="AX9" t="n">
-        <v>-16.54525760371704</v>
+        <v>-14.90715866883865</v>
       </c>
       <c r="AY9" t="n">
         <v>-54.13720844041888</v>
@@ -13778,7 +13721,7 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>sem sinal (-16.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -13972,13 +13915,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69.61</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>79.12</v>
       </c>
       <c r="F11" t="n">
-        <v>38.8</v>
+        <v>39.02</v>
       </c>
       <c r="G11" t="n">
         <v>84.34</v>
@@ -14103,7 +14046,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>A análise fundamentalista da TGMA3 revela uma empresa de alta qualidade operacional que combina forte rentabilidade com endivid</t>
+          <t>A Tegma (TGMA3) apresenta-se como uma operação de alta eficiência no setor de bens industriais, destacando-se por uma rentabilidade excepcional, com ROE de 25,6% e ROIC de 27,0%, ambos amplamente acima das médias setoriais de 7,0% e 10,1%, respectivamente. Essa expressiva qualidade operacional convive com múltiplos de preço que sugerem atratividade, visto que o P/L de 8,89 situa-se em patamar razoável e o P/VP de 2,27 reflete o forte prêmio sobre o valor patrimonial que o mercado concede a empresas de alto retorno. A sólida saúde financeira da companhia é evidenciada pela relação dívida/patrimônio de apenas 0,23, indicando que a alta rentabilidade é conquistada com baixo endividamento, enquanto a liquidez corrente de 2,22 garante robustez para honrar compromissos de curto prazo. Esse balanço desalavancado confere extrema sustentabilidade ao expressivo dividend yield de 11,23%, o qual se mostra plenamente coerente com a forte geração de lucro e com a capacidade de distribuição da empresa. No quesito expansão, a companhia supera seus pares com um crescimento composto anual (CAGR) de receita nos últimos cinco anos de 23,5%, contra a média setorial de 14,9%, o que é corroborado pelo PEG ratio de 0,38, sinalizando que o crescimento não está precificado de forma cara. O checklist de critérios fundamentalistas reforça essa consistência ao aprovar 6 dos 7 requisitos analisados, falhando apenas na margem líquida de 10,14%, que ficou abaixo do sarrafo de 15%. Sob a ótica de valuation, as estimativas de preço-teto revelam uma dispersão relevante entre os métodos, variando desde os mais conservadores R$ 36,11 por Graham até os R$ 115,41 por Lynch, estabelecendo uma mediana de R$ 49,43 que projeta um upside potencial de 44,5% frente ao preço atual de R$ 34,20. Em suma, os principais prós da tese residem no crescimento robusto acima do setor, no endividamento sob controle, no retorno sobre o capital elevado e nos proventos fartos, ao passo que os contras limitam-se à margem líquida abaixo do patamar ideal de 15% e à tendência gráfica lateralizada do papel no curto prazo.</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -14113,7 +14056,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW11" t="n">
@@ -14467,7 +14410,7 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW13" t="n">
@@ -14490,7 +14433,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.6% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -14511,10 +14454,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.45999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>54.93</v>
+        <v>55.18</v>
       </c>
       <c r="F14" t="n">
         <v>56.73</v>
@@ -14648,10 +14591,10 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="AX14" t="n">
-        <v>-14.30768966674805</v>
+        <v>-12.4901748318072</v>
       </c>
       <c r="AY14" t="n">
         <v>-32.85678377733036</v>
@@ -14667,7 +14610,7 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>sem sinal (-14.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -14821,10 +14764,10 @@
         </is>
       </c>
       <c r="AW15" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="AX15" t="n">
-        <v>-1.277582454837922</v>
+        <v>-2.118835116863982</v>
       </c>
       <c r="AY15" t="n">
         <v>-13.54395936495905</v>
@@ -14840,7 +14783,7 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-2.1% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1311239680</v>
+        <v>1316036864</v>
       </c>
       <c r="W16" t="n">
         <v>6.75</v>
@@ -14936,26 +14879,26 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
-        <v>8.199999809265137</v>
+        <v>8.229999542236328</v>
       </c>
       <c r="AH16" t="n">
-        <v>10.48</v>
+        <v>10.52</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12.33</v>
+        <v>12.37</v>
       </c>
       <c r="AK16" t="n">
-        <v>10.83</v>
+        <v>10.87</v>
       </c>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN16" t="n">
-        <v>10.66</v>
+        <v>10.7</v>
       </c>
       <c r="AO16" t="n">
         <v>29.97</v>
@@ -14986,13 +14929,13 @@
         </is>
       </c>
       <c r="AW16" t="n">
-        <v>8.520000457763672</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="AX16" t="n">
-        <v>-3.7558759542899</v>
+        <v>-2.372488205209888</v>
       </c>
       <c r="AY16" t="n">
-        <v>-18.10280183820145</v>
+        <v>-17.80318060245866</v>
       </c>
       <c r="AZ16" t="b">
         <v>1</v>
@@ -15005,7 +14948,7 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>sem sinal (-3.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.4% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -15253,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>4914711040</v>
+        <v>4934343168</v>
       </c>
       <c r="W18" t="n">
         <v>8.25</v>
@@ -15284,28 +15227,28 @@
         <v>0.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>15.02000045776367</v>
+        <v>15.07999992370605</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.03</v>
+        <v>20.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>15.44</v>
+        <v>15.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23.39</v>
+        <v>23.49</v>
       </c>
       <c r="AK18" t="n">
-        <v>20.32</v>
+        <v>20.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>40.6</v>
+        <v>40.76</v>
       </c>
       <c r="AM18" t="n">
-        <v>23.96</v>
+        <v>24.05</v>
       </c>
       <c r="AN18" t="n">
-        <v>20.32</v>
+        <v>20.4</v>
       </c>
       <c r="AO18" t="n">
         <v>35.29</v>
@@ -15330,7 +15273,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>A análise fundamentalista da INTB3 revela uma empresa com forte eficiência operacional, evidenciada por um ROE de 18,</t>
+          <t>A Intelbras (INTB3) apresenta-se como uma alternativa robusta no setor industrial, destacando-se por uma notável eficiência operacional, uma vez que seu ROE de 18,1% e seu ROIC de 17,5% situam-se significativamente acima dos pares setoriais, que registram 7,0% e 10,1%, respectivamente. Essa elevada qualidade de rentabilidade convive com múltiplos de preço bastante atrativos, evidenciados por um P/L de 8,25 e um P/VP de 1,49, o que sugere uma clara assimetria favorável entre o valor entregue pela companhia e o preço cobrado pelo mercado. A saúde financeira da empresa é outro ponto forte, pois a alta rentabilidade é sustentada por um endividamento extremamente controlado, com uma relação Dívida/Patrimônio de apenas 0,26 e uma sólida liquidez corrente de 2,64. Esse balanço desalavancado confere total sustentabilidade ao expressivo dividend yield de 8,0%, o qual se mostra plenamente coerente com a geração de lucro e a capacidade de distribuição da empresa. No quesito expansão, embora o crescimento de receita nos últimos cinco anos tenha sido expressivo, a taxa de 14,3% ficou ligeiramente abaixo da média do setor de 14,9%, um fator que, somado à margem líquida de 13,1%, fez com que a companhia atendesse a 5 dos 7 critérios do checklist fundamentalista. Sob a ótica de valuation, as estimativas de preço-teto revelam uma dispersão relevante entre os métodos, variando desde os conservadores R$ 15,50 pelo modelo de Gordon até os otimistas R$ 40,76 pelo critério de Lynch, estabelecendo uma mediana de R$ 20,40 que projeta um upside potencial de 35,3% frente à cotação atual de R$ 15,08. Em suma, o papel contrapõe, como prós, uma excelente rentabilidade sobre o capital, baixo endividamento, dividendos robustos e valuation descontado, tendo como contras um crescimento de receita ligeiramente inferior ao de seus pares e uma margem líquida que ainda não atinge o patamar ideal de 15%.</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -15344,13 +15287,13 @@
         </is>
       </c>
       <c r="AW18" t="n">
-        <v>14.38436412811279</v>
+        <v>15.02000045776367</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.418939370483477</v>
+        <v>0.3994638090131897</v>
       </c>
       <c r="AY18" t="n">
-        <v>-4.081037600189341</v>
+        <v>-3.697876059421112</v>
       </c>
       <c r="AZ18" t="b">
         <v>1</v>
@@ -16044,10 +15987,10 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="AX22" t="n">
-        <v>-1.129361865388501</v>
+        <v>-1.814843745989081</v>
       </c>
       <c r="AY22" t="n">
         <v>-11.83384458058885</v>
@@ -16063,7 +16006,7 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-1.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16081,7 @@
         <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>159914016</v>
+        <v>157863840</v>
       </c>
       <c r="W23" t="n">
         <v>-9.09</v>
@@ -16169,22 +16112,22 @@
         <v>-2.93</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.7799999713897705</v>
+        <v>0.7699999809265137</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AO23" t="n">
         <v>234.93</v>
@@ -16214,10 +16157,10 @@
         <v>0.9900000095367432</v>
       </c>
       <c r="AX23" t="n">
-        <v>-21.2121248610128</v>
+        <v>-22.22222489807606</v>
       </c>
       <c r="AY23" t="n">
-        <v>-27.087428180438</v>
+        <v>-28.02220388504223</v>
       </c>
       <c r="AZ23" t="b">
         <v>0</v>
@@ -16230,7 +16173,7 @@
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>sem sinal (-21.2% do topo; Em Baixa)</t>
+          <t>sem sinal (-22.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -16251,13 +16194,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.86</v>
+        <v>62.94</v>
       </c>
       <c r="E24" t="n">
         <v>78.42</v>
       </c>
       <c r="F24" t="n">
-        <v>38.18</v>
+        <v>38.47</v>
       </c>
       <c r="G24" t="n">
         <v>90.23</v>
@@ -16655,7 +16598,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2087424256</v>
+        <v>2084035712</v>
       </c>
       <c r="W26" t="n">
         <v>13.46</v>
@@ -16728,7 +16671,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>A análise fundamentalista da FESA4 revela um cenário de baixa rentabilidade e contração operacional, evidenciado pelo RO</t>
+          <t>A Ferbasa (FESA4) apresenta-se atualmente como um caso de estudo intrigante, onde a baixa valorização de mercado contrasta com desafios operacionais recentes no setor de materiais básicos. A qualidade atual da companhia, refletida em um ROE de 4,9% e um ROIC de 4,4% — ambos situando-se abaixo dos pares do setor, que registram 10,6% e 7,5% respectivamente —, convive com múltiplos de preço descontados, visto que o P/L de 13,46 e o P/VP de 0,66 sugerem que o mercado já precifica essa rentabilidade mais tímida. Essa compressão de margens e retornos é acompanhada por uma estrutura de capital extremamente robusta, evidenciada pela relação dívida/patrimônio de apenas 0,12 e uma folgada liquidez corrente de 3,27, indicando que a saúde financeira da empresa permanece blindada contra intempéries. O generoso dividend yield de 11,4% mostra-se surpreendentemente elevado frente ao lucro e à rentabilidade atuais, mas encontra sustentabilidade na ausência de alavancagem financeira sufocante, embora o investidor deva monitorar a perenidade desse fluxo caso a contração operacional persista. No quesito expansão, o crescimento da empresa passa por um momento de forte pressão, com o CAGR de receita de cinco anos negativo em 7,9%, bem abaixo da média setorial de 17,4%, o que justifica o fato de a companhia ter atendido a apenas um dos sete critérios do checklist fundamentalista aplicado. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 4,64 pelo fluxo de caixa descontado até os otimistas R$ 11,7 pelo método de Bazin, estabelecendo uma mediana de R$ 8,46 que projeta um upside de 37,4% sobre a cotação atual de R$ 6,16. Em um balanço final, os principais pontos positivos residem na sólida segurança financeira, no robusto retorno via proventos e no desconto patrimonial atrativo, enquanto os pontos negativos concentram-se na perda de eficiência operacional frente aos concorrentes, no encolhimento histórico das receitas e no fraco desempenho no checklist de qualidade.</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -16782,13 +16725,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62.02</v>
+        <v>62.11</v>
       </c>
       <c r="E27" t="n">
         <v>67.77</v>
       </c>
       <c r="F27" t="n">
-        <v>45.2</v>
+        <v>45.49</v>
       </c>
       <c r="G27" t="n">
         <v>73.7</v>
@@ -16915,10 +16858,10 @@
         </is>
       </c>
       <c r="AW27" t="n">
-        <v>6.579999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="AX27" t="n">
-        <v>-3.49544105988292</v>
+        <v>-3.053439393562163</v>
       </c>
       <c r="AY27" t="n">
         <v>-39.52381043207078</v>
@@ -16934,7 +16877,7 @@
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.1% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16917,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -17084,26 +17027,18 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr">
-        <is>
-          <t>Yes, Net Debt/EBITDA &lt; 3 and &lt;= sector: n/d, market cap &gt;= 300</t>
-        </is>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
       <c r="AV28" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW28" t="n">
-        <v>32.34000015258789</v>
+        <v>32.47999954223633</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.4328985435618105</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
         <v>-10.30102081343549</v>
@@ -17112,14 +17047,14 @@
         <v>1</v>
       </c>
       <c r="BA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17339,7 @@
         <v>-2.713682693188602</v>
       </c>
       <c r="AY30" t="n">
-        <v>-39.51924817380552</v>
+        <v>-39.51925640744687</v>
       </c>
       <c r="AZ30" t="b">
         <v>1</v>
@@ -17559,12 +17494,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>4. Correlate indicators (not just list them)? Yes.
-        5. Position each indicator vs. sector average</t>
-        </is>
-      </c>
+      <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -17582,7 +17512,7 @@
         <v>0.5876255599746028</v>
       </c>
       <c r="AY31" t="n">
-        <v>-20.18449126434217</v>
+        <v>-20.18448271439143</v>
       </c>
       <c r="AZ31" t="b">
         <v>1</v>
@@ -17812,7 +17742,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -17922,27 +17852,18 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>0m: Yes, no insider selling: No).
-    *   *Technical*: Breakout (Rompimento),</t>
-        </is>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
       <c r="AV33" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW33" t="n">
-        <v>12.21000003814697</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.146603954835057</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>-12.59730869465475</v>
@@ -17951,14 +17872,14 @@
         <v>1</v>
       </c>
       <c r="BA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -18110,7 +18031,7 @@
         <v>-3.517688651440576</v>
       </c>
       <c r="AY34" t="n">
-        <v>-12.46352623832258</v>
+        <v>-12.46350726988326</v>
       </c>
       <c r="AZ34" t="b">
         <v>1</v>
@@ -18269,7 +18190,7 @@
       <c r="AU35" t="inlineStr"/>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW35" t="n">
@@ -18292,7 +18213,7 @@
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>sem sinal (-2.2% do topo; Em Alta)</t>
+          <t>sem sinal (-2.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -18619,10 +18540,10 @@
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>29.75</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="AX37" t="n">
-        <v>-2.285715311515235</v>
+        <v>-2.252858377438904</v>
       </c>
       <c r="AY37" t="n">
         <v>-17.59775069846685</v>
@@ -18792,10 +18713,10 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.7537681217588132</v>
+        <v>-1.98511558212644</v>
       </c>
       <c r="AY38" t="n">
         <v>-47.92224740248528</v>
@@ -18811,7 +18732,7 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Lateral)</t>
+          <t>sem sinal (-2.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -18969,10 +18890,10 @@
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>2.339999914169312</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="AX39" t="n">
-        <v>-3.418800283779255</v>
+        <v>-3.004289078750577</v>
       </c>
       <c r="AY39" t="n">
         <v>-52.18694930098489</v>
@@ -18988,7 +18909,7 @@
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>sem sinal (-3.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -19028,7 +18949,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -19063,7 +18984,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2549322752</v>
+        <v>2570927104</v>
       </c>
       <c r="W40" t="n">
         <v>7.8</v>
@@ -19094,28 +19015,28 @@
         <v>0.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.539999961853027</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="AH40" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AJ40" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="AK40" t="n">
-        <v>6.94</v>
+        <v>7</v>
       </c>
       <c r="AL40" t="n">
-        <v>13.62</v>
+        <v>13.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>6.67</v>
+        <v>6.73</v>
       </c>
       <c r="AN40" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="AO40" t="n">
         <v>64.72</v>
@@ -19139,33 +19060,37 @@
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW40" t="n">
-        <v>3.630000114440918</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="AX40" t="n">
-        <v>-2.479342968333542</v>
+        <v>0.847456828052251</v>
       </c>
       <c r="AY40" t="n">
-        <v>-53.54330688952109</v>
+        <v>-53.14960647166905</v>
       </c>
       <c r="AZ40" t="b">
         <v>1</v>
       </c>
       <c r="BA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
+          <t>Rompimento</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19334,7 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>6174486528</v>
+        <v>6182217728</v>
       </c>
       <c r="W42" t="n">
         <v>6.2</v>
@@ -19436,28 +19361,28 @@
         <v>2.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>23.95999908447266</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="AH42" t="n">
-        <v>42.25</v>
+        <v>42.3</v>
       </c>
       <c r="AI42" t="n">
-        <v>21.3</v>
+        <v>21.33</v>
       </c>
       <c r="AJ42" t="n">
-        <v>32.47</v>
+        <v>32.52</v>
       </c>
       <c r="AK42" t="n">
-        <v>48.94</v>
+        <v>49</v>
       </c>
       <c r="AL42" t="n">
-        <v>49</v>
+        <v>49.06</v>
       </c>
       <c r="AM42" t="n">
-        <v>38.79</v>
+        <v>38.84</v>
       </c>
       <c r="AN42" t="n">
-        <v>42.25</v>
+        <v>42.3</v>
       </c>
       <c r="AO42" t="n">
         <v>76.33</v>
@@ -19491,10 +19416,10 @@
         <v>24.09000015258789</v>
       </c>
       <c r="AX42" t="n">
-        <v>-0.5396474358314585</v>
+        <v>-0.4151115850407505</v>
       </c>
       <c r="AY42" t="n">
-        <v>-12.32560412402255</v>
+        <v>-12.21582565248605</v>
       </c>
       <c r="AZ42" t="b">
         <v>1</v>
@@ -19507,7 +19432,7 @@
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>sem sinal (-0.5% do topo; Lateral)</t>
+          <t>sem sinal (-0.4% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -19582,7 +19507,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>2260919552</v>
+        <v>2290645504</v>
       </c>
       <c r="W43" t="n">
         <v>5.65</v>
@@ -20178,7 +20103,7 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>setor Não, Dív.Líq/EBITDA n/d, sem venda de insiders Não).</t>
+          <t>A análise do Banco BMG (BMGB4) sob a ótica fundamentalista revela um ativo que transita em uma tendência lateral de preços, com sinal gráfico de rompimento e uma clara assimetria entre múltiplos descontados e indicadores de eficiência. O retorno sobre o patrimônio líquido (ROE) de 14,0% e o retorno sobre o capital investido (ROIC) de 0,0% situam-se abaixo dos pares do setor de serviços financeiros, que registram médias de 20,1% e 7,9%, respectivamente, sugerindo que a instituição enfrenta desafios para rentabilizar seus recursos no mesmo patamar de seus concorrentes. Essa menor rentabilidade relativa, contudo, convive com múltiplos de preço bastante depreciados, visto que o preço sobre o lucro (P/L) de 5,97 e o preço sobre o valor patrimonial (P/VP) de 0,83 indicam um papel negociado com desconto em relação ao seu valor de livro. O dividend yield de 7,41% mostra-se atrativo e coerente com a forte margem líquida de 28,17%, sugerindo que a distribuição de proventos possui sustentabilidade lastreada na conversão de receitas em lucro líquido, mesmo diante de um crescimento histórico de receita nos últimos cinco anos de 8,6%, ligeiramente abaixo da média setorial de 8,9%. No que tange ao checklist de critérios de qualidade e segurança, o ativo atendeu a apenas um dos seis requisitos aplicáveis, penalizado principalmente pelo ROE inferior à taxa Selic e à média do setor, pelo ROIC abaixo dos pares e pela presença de vendas por parte de insiders, embora preserve a segurança de um valor de mercado robusto de aproximadamente 3,52 bilhões de reais. Sob a perspectiva de valuation, as projeções de preço-teto apresentam uma dispersão acentuada entre as metodologias, variando desde os conservadores 5,20 reais pelo modelo de Gordon e 6,74 reais por Bazin, até estimativas mais otimistas de 11,63 reais por Graham, 11,75 reais por fluxo de caixa descontado e 14,64 reais pelo modelo de Lynch. Essa disparidade resulta em uma média de 9,99 reais e uma mediana de 11,63 reais, o que projeta um expressivo potencial de valorização de 113,1% frente ao preço atual de 5,46 reais. Em balanço, os principais prós residem no valuation descontado, no carrego atraente de dividendos e no elevado potencial de valorização implícito nas métricas de preço-teto, enquanto os contras concentram-se na rentabilidade inferior à média do setor, no crescimento de receita abaixo dos pares e no fraco desempenho no checklist de critérios fundamentais.</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
@@ -20687,11 +20612,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT49" t="inlineStr">
-        <is>
-          <t>A análise fundamentalista do papel BBSE3 revela uma empresa de altíssima rentabilidade sobre o patrimônio líquido, com</t>
-        </is>
-      </c>
+      <c r="AT49" t="inlineStr"/>
       <c r="AU49" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -20876,10 +20797,10 @@
         </is>
       </c>
       <c r="AW50" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>-0.5291042223046771</v>
       </c>
       <c r="AY50" t="n">
         <v>-15.4147281673955</v>
@@ -20895,7 +20816,7 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Alta)</t>
+          <t>sem sinal (-0.5% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20891,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>4499459584</v>
+        <v>4531737088</v>
       </c>
       <c r="W51" t="n">
         <v>5.54</v>
@@ -21001,28 +20922,28 @@
         <v>0.08</v>
       </c>
       <c r="AG51" t="n">
-        <v>13.9399995803833</v>
+        <v>14.03999996185303</v>
       </c>
       <c r="AH51" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AJ51" t="n">
-        <v>32.33</v>
+        <v>32.56</v>
       </c>
       <c r="AK51" t="n">
-        <v>35.39</v>
+        <v>35.65</v>
       </c>
       <c r="AL51" t="n">
-        <v>75.48999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="AM51" t="n">
-        <v>29.92</v>
+        <v>30.13</v>
       </c>
       <c r="AN51" t="n">
-        <v>32.33</v>
+        <v>32.56</v>
       </c>
       <c r="AO51" t="n">
         <v>131.92</v>
@@ -21053,13 +20974,13 @@
         </is>
       </c>
       <c r="AW51" t="n">
-        <v>16.3700008392334</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="AX51" t="n">
-        <v>-14.84423417392992</v>
+        <v>-12.52336056544037</v>
       </c>
       <c r="AY51" t="n">
-        <v>-34.85117715011583</v>
+        <v>-34.38382368287039</v>
       </c>
       <c r="AZ51" t="b">
         <v>1</v>
@@ -21072,7 +20993,7 @@
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>sem sinal (-14.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -21222,14 +21143,14 @@
       <c r="AU52" t="inlineStr"/>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW52" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="AX52" t="n">
-        <v>-0.1856102533401627</v>
+        <v>-0.6925190193304398</v>
       </c>
       <c r="AY52" t="n">
         <v>-27.87197279000151</v>
@@ -21245,7 +21166,7 @@
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>sem sinal (-0.2% do topo; Lateral)</t>
+          <t>sem sinal (-0.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -21395,11 +21316,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT53" t="inlineStr">
-        <is>
-          <t>A CPFL Energia (CPFE3) apresenta-se como um ativo de alta qualidade operacional no setor de utilidade pública, com um retorno sobre o patrimônio líquido de 23,7% e um retorno sobre o capital investido de 15,3% que se posicionam significativamente acima das médias setoriais de 11,6% e 9,5%, respectivamente. Essa sólida rentabilidade convive com múltiplos de preço que sugerem um valuation misto, pois, embora o preço sobre valor patrimonial de 2,2 esteja acima dos pares, o preço sobre lucro de 9,27 e o indicador de crescimento PEG de 0,52 mostram-se atraentes frente à forte capacidade de geração de resultados da companhia. O robusto crescimento da empresa é evidenciado pela taxa de crescimento anual composta da receita nos últimos cinco anos de 18,0%, superando com folga a média negativa do setor de 10,1%, o que valida o cumprimento de seis dos sete critérios do checklist de investimento. No âmbito financeiro, a relação de dívida sobre o patrimônio de 1,43 reflete uma alavancagem que exige atenção, mas que é mitigada por uma liquidez corrente de 1,15 e pela alta eficiência operacional, sustentando um rendimento de dividendos de 8,05% que se mostra coerente com a forte geração de caixa e com o histórico de distribuição da empresa. Sob a ótica do valuation por múltiplos métodos de preço-teto, observa-se uma dispersão relevante entre as metodologias, variando desde os mais conservadores 47,94 reais pelo modelo de Gordon e 48,68 reais por Graham, passando por 62,19 reais por Bazin, até os mais otimistas 130,25 reais por Lynch. Essa disparidade resulta em uma média de 70,66 reais e uma mediana de 62,19 reais, o que confere ao papel um potencial de valorização de 34,2% em relação à mediana frente ao preço atual de 46,35 reais. Como principais prós, destacam-se a rentabilidade muito acima da média setorial, o forte crescimento histórico de receita e o atraente retorno em dividendos amparado por ótimos indicadores de qualidade. Em contrapartida, figuram como contras o nível de endividamento patrimonial relativamente elevado, uma margem líquida de 12,79% que não atinge o patamar ideal de 15% do checklist e a tendência gráfica lateralizada que reflete a atual indefinição do mercado no curto prazo.</t>
-        </is>
-      </c>
+      <c r="AT53" t="inlineStr"/>
       <c r="AU53" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -21767,7 +21684,7 @@
         <v>-4.576970169490013</v>
       </c>
       <c r="AY55" t="n">
-        <v>-23.4739172343906</v>
+        <v>-23.47392377028176</v>
       </c>
       <c r="AZ55" t="b">
         <v>1</v>
@@ -21855,7 +21772,7 @@
         <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>15677621248</v>
+        <v>15691892736</v>
       </c>
       <c r="W56" t="n">
         <v>9.75</v>
@@ -21884,26 +21801,26 @@
       </c>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="n">
-        <v>32.95999908447266</v>
+        <v>32.9900016784668</v>
       </c>
       <c r="AH56" t="n">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="AI56" t="n">
-        <v>10.97</v>
+        <v>10.98</v>
       </c>
       <c r="AJ56" t="n">
-        <v>34.3</v>
+        <v>34.33</v>
       </c>
       <c r="AK56" t="n">
-        <v>46.29</v>
+        <v>46.33</v>
       </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="n">
-        <v>27.39</v>
+        <v>27.42</v>
       </c>
       <c r="AN56" t="n">
-        <v>26.16</v>
+        <v>26.18</v>
       </c>
       <c r="AO56" t="n">
         <v>-20.63</v>
@@ -21926,11 +21843,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>Liq/EBITDA (n/d), market cap &gt;= 300mi (Yes), no insider selling</t>
-        </is>
-      </c>
+      <c r="AT56" t="inlineStr"/>
       <c r="AU56" t="inlineStr">
         <is>
           <t>Pivô de alta</t>
@@ -21942,13 +21855,13 @@
         </is>
       </c>
       <c r="AW56" t="n">
-        <v>34.11000061035156</v>
+        <v>33.75</v>
       </c>
       <c r="AX56" t="n">
-        <v>-3.371449737030807</v>
+        <v>-2.251846878616903</v>
       </c>
       <c r="AY56" t="n">
-        <v>-10.60545926870959</v>
+        <v>-10.52408584075593</v>
       </c>
       <c r="AZ56" t="b">
         <v>1</v>
@@ -22405,13 +22318,13 @@
         </is>
       </c>
       <c r="AW59" t="n">
-        <v>43.63000106811523</v>
+        <v>43.61150741577148</v>
       </c>
       <c r="AX59" t="n">
-        <v>-3.506767262291599</v>
+        <v>-3.465848880756128</v>
       </c>
       <c r="AY59" t="n">
-        <v>-13.58724744836764</v>
+        <v>-13.55060950604702</v>
       </c>
       <c r="AZ59" t="b">
         <v>1</v>
@@ -22574,7 +22487,7 @@
       <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW60" t="n">
@@ -22597,7 +22510,7 @@
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>sem sinal (-2.7% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.7% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -22968,13 +22881,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>51.4</v>
+        <v>51.48</v>
       </c>
       <c r="E63" t="n">
         <v>85.64</v>
       </c>
       <c r="F63" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="G63" t="n">
         <v>64.13</v>
@@ -23093,11 +23006,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT63" t="inlineStr">
-        <is>
-          <t>A WEG (WEGE3) se consolida como uma empresa de altíssima eficiência operacional, apresentando um ROE de 33,2% e um ROIC de 24,3% que se posicionam muito acima dos pares do setor de bens industriais, os quais registram médias de 7,0% e 10,1%, respectivamente. Essa qualidade excepcional, contudo, convive com múltiplos de preço bastante esticados, evidenciados pelo P/L de 33,0 e pelo P/VP de 10,94, indicando que o mercado cobra um prêmio elevado por essa rentabilidade diferenciada. No balanço entre rentabilidade e endividamento, a companhia demonstra extrema solidez financeira ao associar sua forte margem líquida de 15,58% a uma baixa relação de dívida sobre o patrimônio de 0,29 e a uma confortável liquidez corrente de 1,59. O retorno em dividendos de 4,08% mostra-se coerente e sustentável diante da robusta geração de lucro e da estrutura de capital desalavancada, embora o crescimento de longo prazo acenda um sinal de alerta, visto que o CAGR de receita de cinco anos contraiu 2,1%, situando-se abaixo da média setorial de expansão de 14,9%. No checklist de critérios fundamentalistas, a empresa atende a 5 de 7 requisitos, falhando justamente na expansão de receita frente aos pares e na ocorrência de vendas por parte de insiders, o que se reflete em uma nota de qualidade de 86,0 contra um score de valor de apenas 4,0. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão acentuada, variando desde os R$ 33,44 pelo modelo de Bazin até os R$ 12,28 pela fórmula de Graham, resultando em uma média de R$ 20,30 e uma mediana de R$ 17,74. Frente ao preço atual de R$ 49,17, a mediana projeta um upside negativo de 63,9%, sugerindo que a cotação de mercado atual embutiu expectativas excessivamente otimistas que descolam o papel de suas referências teóricas de valor. Em suma, os principais prós do investimento residem na rentabilidade formidável, na saúde financeira impecável e na resiliência operacional, enquanto os contras concentram-se no valuation severamente esticado, no crescimento recente de receita abaixo do setor e na expressiva distância para os preços-teto calculados.</t>
-        </is>
-      </c>
+      <c r="AT63" t="inlineStr"/>
       <c r="AU63" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -23399,12 +23308,7 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AT65" t="inlineStr">
-        <is>
-          <t>Selic, ROIC&gt;=sector, margin&gt;=15%, CAGR&gt;=sector).
-    *   *Technical/Trend*:</t>
-        </is>
-      </c>
+      <c r="AT65" t="inlineStr"/>
       <c r="AU65" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -23935,7 +23839,7 @@
         <v>-11.96971905794416</v>
       </c>
       <c r="AY68" t="n">
-        <v>-23.22975619580519</v>
+        <v>-23.22976334700939</v>
       </c>
       <c r="AZ68" t="b">
         <v>1</v>
@@ -23969,10 +23873,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>49.15</v>
+        <v>49.24</v>
       </c>
       <c r="E69" t="n">
-        <v>49.81</v>
+        <v>50.06</v>
       </c>
       <c r="F69" t="n">
         <v>33.07</v>
@@ -24142,13 +24046,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>49.13</v>
+        <v>49.21</v>
       </c>
       <c r="E70" t="n">
         <v>51.61</v>
       </c>
       <c r="F70" t="n">
-        <v>34.83</v>
+        <v>35.09</v>
       </c>
       <c r="G70" t="n">
         <v>50.26</v>
@@ -24275,10 +24179,10 @@
         </is>
       </c>
       <c r="AW70" t="n">
-        <v>76.08999633789062</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="AX70" t="n">
-        <v>0.2891329100952689</v>
+        <v>0.03932718901014098</v>
       </c>
       <c r="AY70" t="n">
         <v>-16.71033041805866</v>
@@ -24315,10 +24219,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>49</v>
+        <v>49.11</v>
       </c>
       <c r="E71" t="n">
-        <v>40.57</v>
+        <v>40.82</v>
       </c>
       <c r="F71" t="n">
         <v>66.67</v>
@@ -24436,10 +24340,10 @@
         </is>
       </c>
       <c r="AW71" t="n">
-        <v>21.27000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="AX71" t="n">
-        <v>-1.316411286410224</v>
+        <v>-1.686185498450943</v>
       </c>
       <c r="AY71" t="n">
         <v>-23.79046311986899</v>
@@ -24455,7 +24359,7 @@
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>sem sinal (-1.3% do topo; Em Alta)</t>
+          <t>sem sinal (-1.7% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -24609,10 +24513,10 @@
         </is>
       </c>
       <c r="AW72" t="n">
-        <v>30.3700008392334</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="AX72" t="n">
-        <v>-7.770828268476048</v>
+        <v>-7.679630560276429</v>
       </c>
       <c r="AY72" t="n">
         <v>-20.69199954808616</v>
@@ -24628,7 +24532,7 @@
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>sem sinal (-7.8% do topo; Em Baixa)</t>
+          <t>sem sinal (-7.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24649,10 +24553,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>48.8</v>
+        <v>48.89</v>
       </c>
       <c r="E73" t="n">
-        <v>11.15</v>
+        <v>11.4</v>
       </c>
       <c r="F73" t="n">
         <v>72.72</v>
@@ -24703,7 +24607,7 @@
         <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>2136550656</v>
+        <v>2153027840</v>
       </c>
       <c r="W73" t="n">
         <v>-10.11</v>
@@ -24734,22 +24638,22 @@
         <v>-0.21</v>
       </c>
       <c r="AG73" t="n">
-        <v>3.890000104904175</v>
+        <v>3.920000076293945</v>
       </c>
       <c r="AH73" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="AI73" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="AN73" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="AO73" t="n">
         <v>16.29</v>
@@ -24776,13 +24680,13 @@
         </is>
       </c>
       <c r="AW73" t="n">
-        <v>4.070000171661377</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="AX73" t="n">
-        <v>-4.422605876297203</v>
+        <v>-1.010100037063255</v>
       </c>
       <c r="AY73" t="n">
-        <v>-19.0219927402037</v>
+        <v>-18.39748429920602</v>
       </c>
       <c r="AZ73" t="b">
         <v>0</v>
@@ -24795,7 +24699,7 @@
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>sem sinal (-4.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24833,7 @@
       <c r="AU74" t="inlineStr"/>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW74" t="n">
@@ -24952,7 +24856,7 @@
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>sem sinal (-5.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.3% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -25444,7 +25348,7 @@
       <c r="AU77" t="inlineStr"/>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW77" t="n">
@@ -25467,7 +25371,7 @@
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>sem sinal (-10.4% do topo; Lateral)</t>
+          <t>sem sinal (-10.4% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25881,7 @@
         <v>0.1575335373968034</v>
       </c>
       <c r="AY80" t="n">
-        <v>-33.331611084974</v>
+        <v>-33.33160558679006</v>
       </c>
       <c r="AZ80" t="b">
         <v>0</v>
@@ -26199,7 +26103,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -26234,7 +26138,7 @@
         <v>1</v>
       </c>
       <c r="V82" t="n">
-        <v>1223084672</v>
+        <v>1226549504</v>
       </c>
       <c r="W82" t="n">
         <v>24.18</v>
@@ -26306,21 +26210,17 @@
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr"/>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU82" t="inlineStr"/>
       <c r="AV82" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AW82" t="n">
-        <v>3.519999980926514</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.2840906397000742</v>
+        <v>-0.8426958391001382</v>
       </c>
       <c r="AY82" t="n">
         <v>-43.96825611876666</v>
@@ -26329,14 +26229,14 @@
         <v>0</v>
       </c>
       <c r="BA82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="b">
         <v>0</v>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.8% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -26374,7 +26274,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -26475,21 +26375,17 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr"/>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW83" t="n">
-        <v>21.85000038146973</v>
+        <v>22</v>
       </c>
       <c r="AX83" t="n">
-        <v>0.09153527420819874</v>
+        <v>-0.5909052762118283</v>
       </c>
       <c r="AY83" t="n">
         <v>-14.67030216407054</v>
@@ -26498,14 +26394,14 @@
         <v>0</v>
       </c>
       <c r="BA83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB83" t="b">
         <v>0</v>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -26655,10 +26551,10 @@
         </is>
       </c>
       <c r="AW84" t="n">
-        <v>60.54000091552734</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="AX84" t="n">
-        <v>-3.452263166470892</v>
+        <v>-3.944121234780862</v>
       </c>
       <c r="AY84" t="n">
         <v>-19.90956690277227</v>
@@ -26674,7 +26570,7 @@
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>sem sinal (-3.5% do topo; Em Alta)</t>
+          <t>sem sinal (-3.9% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -26975,10 +26871,10 @@
         </is>
       </c>
       <c r="AW86" t="n">
-        <v>0.1599999964237213</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>-5.882356034843117</v>
       </c>
       <c r="AY86" t="n">
         <v>-99.17440658744904</v>
@@ -26994,7 +26890,7 @@
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.9% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -27979,10 +27875,10 @@
         </is>
       </c>
       <c r="AW92" t="n">
-        <v>66.26999664306641</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="AX92" t="n">
-        <v>-3.561184420100938</v>
+        <v>-3.313159874831761</v>
       </c>
       <c r="AY92" t="n">
         <v>-5.76526078591314</v>
@@ -27998,7 +27894,7 @@
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>sem sinal (-3.6% do topo; Em Alta)</t>
+          <t>sem sinal (-3.3% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -28073,7 +27969,7 @@
         <v>1</v>
       </c>
       <c r="V93" t="n">
-        <v>4413220352</v>
+        <v>4459920896</v>
       </c>
       <c r="W93" t="n">
         <v>-49.49</v>
@@ -28104,22 +28000,22 @@
         <v>-8.109999999999999</v>
       </c>
       <c r="AG93" t="n">
-        <v>7.559999942779541</v>
+        <v>7.639999866485596</v>
       </c>
       <c r="AH93" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="inlineStr"/>
       <c r="AL93" t="inlineStr"/>
       <c r="AM93" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AO93" t="n">
         <v>-75.5</v>
@@ -28146,13 +28042,13 @@
         </is>
       </c>
       <c r="AW93" t="n">
-        <v>8.060000419616699</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="AX93" t="n">
-        <v>-6.20347953853998</v>
+        <v>-3.045688381596556</v>
       </c>
       <c r="AY93" t="n">
-        <v>-48.25211410587148</v>
+        <v>-47.70451794782736</v>
       </c>
       <c r="AZ93" t="b">
         <v>0</v>
@@ -28165,7 +28061,7 @@
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>sem sinal (-6.2% do topo; Em Baixa)</t>
+          <t>sem sinal (-3.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -28186,13 +28082,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>42.25</v>
+        <v>42.42</v>
       </c>
       <c r="E94" t="n">
-        <v>38.67</v>
+        <v>38.92</v>
       </c>
       <c r="F94" t="n">
-        <v>32.84</v>
+        <v>33.13</v>
       </c>
       <c r="G94" t="n">
         <v>48.85</v>
@@ -28413,7 +28309,7 @@
         <v>1</v>
       </c>
       <c r="V95" t="n">
-        <v>1853859328</v>
+        <v>1856839808</v>
       </c>
       <c r="W95" t="n">
         <v>14.13</v>
@@ -28444,28 +28340,28 @@
         <v>0.48</v>
       </c>
       <c r="AG95" t="n">
-        <v>12.4399995803833</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="AH95" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="AI95" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="AJ95" t="n">
-        <v>11.31</v>
+        <v>11.33</v>
       </c>
       <c r="AK95" t="n">
-        <v>13.08</v>
+        <v>13.1</v>
       </c>
       <c r="AL95" t="n">
-        <v>26.41</v>
+        <v>26.45</v>
       </c>
       <c r="AM95" t="n">
-        <v>12.1</v>
+        <v>12.12</v>
       </c>
       <c r="AN95" t="n">
-        <v>11.31</v>
+        <v>11.33</v>
       </c>
       <c r="AO95" t="n">
         <v>-9.07</v>
@@ -28496,13 +28392,13 @@
         </is>
       </c>
       <c r="AW95" t="n">
-        <v>11.93000030517578</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="AX95" t="n">
-        <v>4.274930948545386</v>
+        <v>0.1607753893755115</v>
       </c>
       <c r="AY95" t="n">
-        <v>-23.65887805399658</v>
+        <v>-23.53613124192423</v>
       </c>
       <c r="AZ95" t="b">
         <v>0</v>
@@ -28590,7 +28486,7 @@
         <v>1</v>
       </c>
       <c r="V96" t="n">
-        <v>5618809344</v>
+        <v>5607715840</v>
       </c>
       <c r="W96" t="n">
         <v>22.42</v>
@@ -28619,26 +28515,26 @@
       </c>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="n">
-        <v>20.26000022888184</v>
+        <v>20.21999931335449</v>
       </c>
       <c r="AH96" t="n">
-        <v>10.23</v>
+        <v>10.21</v>
       </c>
       <c r="AI96" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="AJ96" t="n">
-        <v>9.17</v>
+        <v>9.15</v>
       </c>
       <c r="AK96" t="n">
-        <v>13.21</v>
+        <v>13.19</v>
       </c>
       <c r="AL96" t="inlineStr"/>
       <c r="AM96" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AN96" t="n">
-        <v>9.699999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="AO96" t="n">
         <v>-52.12</v>
@@ -28665,13 +28561,13 @@
         </is>
       </c>
       <c r="AW96" t="n">
-        <v>21.07999992370605</v>
+        <v>21.17000007629395</v>
       </c>
       <c r="AX96" t="n">
-        <v>-3.889941640379546</v>
+        <v>-4.487485873952634</v>
       </c>
       <c r="AY96" t="n">
-        <v>-19.35852192104358</v>
+        <v>-19.51773874810155</v>
       </c>
       <c r="AZ96" t="b">
         <v>0</v>
@@ -28684,7 +28580,7 @@
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>sem sinal (-3.9% do topo; Lateral)</t>
+          <t>sem sinal (-4.5% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -28932,7 +28828,7 @@
         <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1778307584</v>
+        <v>1785281408</v>
       </c>
       <c r="W98" t="n">
         <v>-6.14</v>
@@ -28961,7 +28857,7 @@
       </c>
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="n">
-        <v>5.099999904632568</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="AH98" t="inlineStr"/>
       <c r="AI98" t="inlineStr"/>
@@ -28994,10 +28890,10 @@
         <v>5.139999866485596</v>
       </c>
       <c r="AX98" t="n">
-        <v>-0.778209394786944</v>
+        <v>-0.389104697393472</v>
       </c>
       <c r="AY98" t="n">
-        <v>-30.13698943315821</v>
+        <v>-29.76680504319727</v>
       </c>
       <c r="AZ98" t="b">
         <v>0</v>
@@ -29010,7 +28906,7 @@
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>sem sinal (-0.8% do topo; Em Alta)</t>
+          <t>sem sinal (-0.4% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -29319,10 +29215,10 @@
         </is>
       </c>
       <c r="AW100" t="n">
-        <v>8.710000038146973</v>
+        <v>8.659999847412109</v>
       </c>
       <c r="AX100" t="n">
-        <v>-0.5740550001823053</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
         <v>-18.43808159694287</v>
@@ -29338,7 +29234,7 @@
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>sem sinal (-0.6% do topo; Em Baixa)</t>
+          <t>sem sinal (+0.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -29413,7 +29309,7 @@
         <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>449765664</v>
+        <v>452594400</v>
       </c>
       <c r="W101" t="n">
         <v>29.65</v>
@@ -29444,25 +29340,25 @@
         <v>0.93</v>
       </c>
       <c r="AG101" t="n">
-        <v>1.590000033378601</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="AH101" t="n">
         <v>0.15</v>
       </c>
       <c r="AI101" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AJ101" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="AK101" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AL101" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AM101" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AN101" t="n">
         <v>0.6899999999999999</v>
@@ -29495,10 +29391,10 @@
         <v>1.690000057220459</v>
       </c>
       <c r="AX101" t="n">
-        <v>-5.917160973729663</v>
+        <v>-5.325445581737076</v>
       </c>
       <c r="AY101" t="n">
-        <v>-43.33106396063281</v>
+        <v>-42.97465590524905</v>
       </c>
       <c r="AZ101" t="b">
         <v>0</v>
@@ -29511,7 +29407,7 @@
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>sem sinal (-5.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-5.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -29661,10 +29557,10 @@
         </is>
       </c>
       <c r="AW102" t="n">
-        <v>32.43999862670898</v>
+        <v>32.27000045776367</v>
       </c>
       <c r="AX102" t="n">
-        <v>-7.12083712617817</v>
+        <v>-6.631550252991147</v>
       </c>
       <c r="AY102" t="n">
         <v>-22.38033148894612</v>
@@ -29680,7 +29576,7 @@
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>sem sinal (-7.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-6.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -29755,7 +29651,7 @@
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>484647584</v>
+        <v>480493472</v>
       </c>
       <c r="W103" t="n">
         <v>50.48</v>
@@ -29786,28 +29682,28 @@
         <v>14.02</v>
       </c>
       <c r="AG103" t="n">
-        <v>3.5</v>
+        <v>3.470000028610229</v>
       </c>
       <c r="AH103" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AI103" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AJ103" t="n">
         <v>0.67</v>
       </c>
       <c r="AK103" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="AL103" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="AM103" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AN103" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AO103" t="n">
         <v>-50.1</v>
@@ -29834,13 +29730,13 @@
         </is>
       </c>
       <c r="AW103" t="n">
-        <v>3.990000009536743</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="AX103" t="n">
-        <v>-12.28070196404922</v>
+        <v>-12.15189907035467</v>
       </c>
       <c r="AY103" t="n">
-        <v>-27.08333623078123</v>
+        <v>-27.70833560989954</v>
       </c>
       <c r="AZ103" t="b">
         <v>0</v>
@@ -29853,7 +29749,7 @@
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>sem sinal (-12.3% do topo; Em Baixa)</t>
+          <t>sem sinal (-12.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -29874,10 +29770,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>39.97</v>
+        <v>40.06</v>
       </c>
       <c r="E104" t="n">
-        <v>22.01</v>
+        <v>22.26</v>
       </c>
       <c r="F104" t="n">
         <v>64.94</v>
@@ -30043,10 +29939,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>39.07</v>
+        <v>39.16</v>
       </c>
       <c r="E105" t="n">
-        <v>23.58</v>
+        <v>23.83</v>
       </c>
       <c r="F105" t="n">
         <v>44.78</v>
@@ -30097,7 +29993,7 @@
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>1620088320</v>
+        <v>1616677504</v>
       </c>
       <c r="W105" t="n">
         <v>15.08</v>
@@ -30126,26 +30022,26 @@
       </c>
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="n">
-        <v>4.75</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="AH105" t="n">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
       <c r="AI105" t="n">
         <v>2.97</v>
       </c>
       <c r="AJ105" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AK105" t="n">
-        <v>7.75</v>
+        <v>7.74</v>
       </c>
       <c r="AL105" t="inlineStr"/>
       <c r="AM105" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="AN105" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="AO105" t="n">
         <v>-14.94</v>
@@ -30172,13 +30068,13 @@
         </is>
       </c>
       <c r="AW105" t="n">
-        <v>5.389999866485596</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="AX105" t="n">
-        <v>-11.87383826231688</v>
+        <v>-1.455305041457566</v>
       </c>
       <c r="AY105" t="n">
-        <v>-34.97463200501271</v>
+        <v>-35.1115306498707</v>
       </c>
       <c r="AZ105" t="b">
         <v>0</v>
@@ -30191,7 +30087,7 @@
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>sem sinal (-11.9% do topo; Em Baixa)</t>
+          <t>sem sinal (-1.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -30439,7 +30335,7 @@
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>5755065344</v>
+        <v>5820122624</v>
       </c>
       <c r="W107" t="n">
         <v>8.08</v>
@@ -30468,26 +30364,26 @@
       </c>
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="n">
-        <v>11.5</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="AH107" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AJ107" t="n">
-        <v>14.44</v>
+        <v>14.6</v>
       </c>
       <c r="AK107" t="n">
-        <v>17.45</v>
+        <v>17.64</v>
       </c>
       <c r="AL107" t="inlineStr"/>
       <c r="AM107" t="n">
-        <v>9.19</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AN107" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="AO107" t="n">
         <v>-24.05</v>
@@ -30517,10 +30413,10 @@
         <v>15.56999969482422</v>
       </c>
       <c r="AX107" t="n">
-        <v>-26.14001139754144</v>
+        <v>-25.30507166093932</v>
       </c>
       <c r="AY107" t="n">
-        <v>-35.75418857498145</v>
+        <v>-35.0279309369291</v>
       </c>
       <c r="AZ107" t="b">
         <v>0</v>
@@ -30533,7 +30429,7 @@
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>sem sinal (-26.1% do topo; Em Baixa)</t>
+          <t>sem sinal (-25.3% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -30729,7 +30625,7 @@
         <v>1</v>
       </c>
       <c r="V109" t="n">
-        <v>1845874432</v>
+        <v>1838901248</v>
       </c>
       <c r="W109" t="n">
         <v>-128.68</v>
@@ -30758,22 +30654,22 @@
       </c>
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="n">
-        <v>18.53000068664551</v>
+        <v>18.45999908447266</v>
       </c>
       <c r="AH109" t="n">
-        <v>12.54</v>
+        <v>12.49</v>
       </c>
       <c r="AI109" t="n">
-        <v>7.63</v>
+        <v>7.6</v>
       </c>
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="inlineStr"/>
       <c r="AL109" t="inlineStr"/>
       <c r="AM109" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN109" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AO109" t="n">
         <v>-45.57</v>
@@ -30796,17 +30692,17 @@
       <c r="AU109" t="inlineStr"/>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW109" t="n">
         <v>19.6299991607666</v>
       </c>
       <c r="AX109" t="n">
-        <v>-5.603660321695781</v>
+        <v>-5.960265544138998</v>
       </c>
       <c r="AY109" t="n">
-        <v>-18.54944753122854</v>
+        <v>-18.85714688143887</v>
       </c>
       <c r="AZ109" t="b">
         <v>0</v>
@@ -30819,7 +30715,7 @@
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>sem sinal (-5.6% do topo; Em Alta)</t>
+          <t>sem sinal (-6.0% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -31180,10 +31076,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>36.47</v>
+        <v>36.55</v>
       </c>
       <c r="E112" t="n">
-        <v>34.6</v>
+        <v>34.85</v>
       </c>
       <c r="F112" t="n">
         <v>28.76</v>
@@ -31762,10 +31658,10 @@
         </is>
       </c>
       <c r="AW115" t="n">
-        <v>2.141556024551392</v>
+        <v>2.051909446716309</v>
       </c>
       <c r="AX115" t="n">
-        <v>-6.609961305170353</v>
+        <v>-2.529811771147106</v>
       </c>
       <c r="AY115" t="n">
         <v>-47.29958317919294</v>
@@ -31781,7 +31677,7 @@
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>sem sinal (-6.6% do topo; Em Baixa)</t>
+          <t>sem sinal (-2.5% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -31955,10 +31851,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>34.89</v>
+        <v>34.98</v>
       </c>
       <c r="E117" t="n">
-        <v>19.77</v>
+        <v>20.02</v>
       </c>
       <c r="F117" t="n">
         <v>85.13</v>
@@ -32223,10 +32119,10 @@
         </is>
       </c>
       <c r="AW118" t="n">
-        <v>6.940000057220459</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="AX118" t="n">
-        <v>-15.99423810320502</v>
+        <v>-14.64128859693144</v>
       </c>
       <c r="AY118" t="n">
         <v>-57.6923074261264</v>
@@ -32242,14 +32138,14 @@
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>sem sinal (-16.0% do topo; Em Baixa)</t>
+          <t>sem sinal (-14.6% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>CVCB3</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -32259,34 +32155,34 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>33.78</v>
+        <v>33.46</v>
       </c>
       <c r="E119" t="n">
-        <v>31.52</v>
+        <v>12.25</v>
       </c>
       <c r="F119" t="n">
-        <v>17.07</v>
+        <v>79.44</v>
       </c>
       <c r="G119" t="n">
-        <v>33.61</v>
+        <v>19.57</v>
       </c>
       <c r="H119" t="n">
-        <v>72.73</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I119" t="n">
         <v>118</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
         <v>7</v>
@@ -32307,7 +32203,7 @@
         <v>0</v>
       </c>
       <c r="R119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="b">
@@ -32317,66 +32213,48 @@
         <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>129685618688</v>
+        <v>718702080</v>
       </c>
       <c r="W119" t="n">
-        <v>30.5</v>
+        <v>-6.85</v>
       </c>
       <c r="X119" t="n">
-        <v>2.52</v>
+        <v>1.81</v>
       </c>
       <c r="Y119" t="n">
-        <v>7.72</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>8.26</v>
+        <v>-26.34</v>
       </c>
       <c r="AA119" t="n">
-        <v>6.28</v>
+        <v>5.79</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.27</v>
+        <v>-7.1</v>
       </c>
       <c r="AC119" t="inlineStr"/>
       <c r="AD119" t="n">
-        <v>1.78</v>
+        <v>0.73</v>
       </c>
       <c r="AE119" t="n">
-        <v>2.27</v>
+        <v>1.4</v>
       </c>
       <c r="AF119" t="n">
-        <v>16.94</v>
+        <v>-13.7</v>
       </c>
       <c r="AG119" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="AH119" t="n">
-        <v>23.48</v>
-      </c>
-      <c r="AI119" t="n">
-        <v>11.52</v>
-      </c>
-      <c r="AJ119" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AK119" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="AL119" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AM119" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="AN119" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="AO119" t="n">
-        <v>-45.89</v>
-      </c>
-      <c r="AP119" t="n">
-        <v>-39.22</v>
-      </c>
+        <v>1.379999995231628</v>
+      </c>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
+      <c r="AP119" t="inlineStr"/>
       <c r="AQ119" t="inlineStr">
         <is>
           <t>n/d</t>
@@ -32389,37 +32267,33 @@
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="inlineStr"/>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="AU119" t="inlineStr"/>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW119" t="n">
-        <v>18.23999977111816</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="AX119" t="n">
-        <v>0.05482581692610733</v>
+        <v>-4.166670805877947</v>
       </c>
       <c r="AY119" t="n">
-        <v>-14.11764705882353</v>
+        <v>-50.53763390322496</v>
       </c>
       <c r="AZ119" t="b">
         <v>0</v>
       </c>
       <c r="BA119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="b">
         <v>0</v>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>sem sinal (-4.2% do topo; Lateral)</t>
         </is>
       </c>
     </row>
@@ -32599,7 +32473,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CVCB3</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -32609,23 +32483,23 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>33.37</v>
+        <v>33.31</v>
       </c>
       <c r="E121" t="n">
-        <v>12</v>
+        <v>49.85</v>
       </c>
       <c r="F121" t="n">
-        <v>79.44</v>
+        <v>25.19</v>
       </c>
       <c r="G121" t="n">
-        <v>19.57</v>
+        <v>23.34</v>
       </c>
       <c r="H121" t="n">
-        <v>9.470000000000001</v>
+        <v>24.24</v>
       </c>
       <c r="I121" t="n">
         <v>120</v>
@@ -32636,7 +32510,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L121" t="n">
         <v>7</v>
@@ -32648,16 +32522,16 @@
         <v>0</v>
       </c>
       <c r="O121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
       <c r="R121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="b">
@@ -32667,48 +32541,66 @@
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>718702080</v>
+        <v>26202454016</v>
       </c>
       <c r="W121" t="n">
-        <v>-6.85</v>
+        <v>25.23</v>
       </c>
       <c r="X121" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="Z121" t="n">
-        <v>-26.34</v>
+        <v>7.49</v>
       </c>
       <c r="AA121" t="n">
-        <v>5.79</v>
+        <v>12.14</v>
       </c>
       <c r="AB121" t="n">
-        <v>-7.1</v>
+        <v>7.34</v>
       </c>
       <c r="AC121" t="inlineStr"/>
       <c r="AD121" t="n">
-        <v>0.73</v>
+        <v>1.37</v>
       </c>
       <c r="AE121" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>14.11999988555908</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI121" t="n">
         <v>1.4</v>
       </c>
-      <c r="AF121" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="AG121" t="n">
-        <v>1.379999995231628</v>
-      </c>
-      <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="inlineStr"/>
-      <c r="AJ121" t="inlineStr"/>
-      <c r="AK121" t="inlineStr"/>
-      <c r="AL121" t="inlineStr"/>
-      <c r="AM121" t="inlineStr"/>
-      <c r="AN121" t="inlineStr"/>
-      <c r="AO121" t="inlineStr"/>
-      <c r="AP121" t="inlineStr"/>
+      <c r="AJ121" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-54.93</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-62.52</v>
+      </c>
       <c r="AQ121" t="inlineStr">
         <is>
           <t>n/d</t>
@@ -32724,17 +32616,17 @@
       <c r="AU121" t="inlineStr"/>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW121" t="n">
-        <v>1.440000057220459</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="AX121" t="n">
-        <v>-4.166670805877947</v>
+        <v>-2.21606443298612</v>
       </c>
       <c r="AY121" t="n">
-        <v>-50.53763390322496</v>
+        <v>-18.51651739090506</v>
       </c>
       <c r="AZ121" t="b">
         <v>0</v>
@@ -32747,14 +32639,14 @@
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>sem sinal (-4.2% do topo; Lateral)</t>
+          <t>sem sinal (-2.2% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RAIL3</t>
+          <t>EQTL3</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -32764,23 +32656,23 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>33.22</v>
+        <v>32.55</v>
       </c>
       <c r="E122" t="n">
-        <v>49.6</v>
+        <v>40.42</v>
       </c>
       <c r="F122" t="n">
-        <v>25.19</v>
+        <v>19.48</v>
       </c>
       <c r="G122" t="n">
-        <v>23.34</v>
+        <v>27</v>
       </c>
       <c r="H122" t="n">
-        <v>24.24</v>
+        <v>47.73</v>
       </c>
       <c r="I122" t="n">
         <v>121</v>
@@ -32791,7 +32683,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L122" t="n">
         <v>7</v>
@@ -32803,7 +32695,7 @@
         <v>0</v>
       </c>
       <c r="O122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
@@ -32822,65 +32714,61 @@
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>26202454016</v>
+        <v>49205260288</v>
       </c>
       <c r="W122" t="n">
-        <v>25.23</v>
+        <v>31.93</v>
       </c>
       <c r="X122" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Y122" t="n">
-        <v>0.77</v>
+        <v>4.03</v>
       </c>
       <c r="Z122" t="n">
-        <v>7.49</v>
+        <v>6.02</v>
       </c>
       <c r="AA122" t="n">
-        <v>12.14</v>
+        <v>10.19</v>
       </c>
       <c r="AB122" t="n">
-        <v>7.34</v>
+        <v>2.89</v>
       </c>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AE122" t="n">
         <v>2.06</v>
       </c>
-      <c r="AF122" t="n">
-        <v>2.38</v>
-      </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="n">
-        <v>14.11999988555908</v>
+        <v>39.20999908447266</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.81</v>
+        <v>26.34</v>
       </c>
       <c r="AI122" t="n">
-        <v>1.4</v>
+        <v>16.03</v>
       </c>
       <c r="AJ122" t="n">
-        <v>7.19</v>
+        <v>12.46</v>
       </c>
       <c r="AK122" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AL122" t="n">
-        <v>6.36</v>
-      </c>
+        <v>23.75</v>
+      </c>
+      <c r="AL122" t="inlineStr"/>
       <c r="AM122" t="n">
-        <v>5.29</v>
+        <v>19.65</v>
       </c>
       <c r="AN122" t="n">
-        <v>6.36</v>
+        <v>19.89</v>
       </c>
       <c r="AO122" t="n">
-        <v>-54.93</v>
+        <v>-49.26</v>
       </c>
       <c r="AP122" t="n">
-        <v>-62.52</v>
+        <v>-49.9</v>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
@@ -32897,17 +32785,17 @@
       <c r="AU122" t="inlineStr"/>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AW122" t="n">
-        <v>14.27999973297119</v>
+        <v>40.95000076293945</v>
       </c>
       <c r="AX122" t="n">
-        <v>-1.120447131680857</v>
+        <v>-4.249088268739499</v>
       </c>
       <c r="AY122" t="n">
-        <v>-18.51651739090506</v>
+        <v>-15.34974235145781</v>
       </c>
       <c r="AZ122" t="b">
         <v>0</v>
@@ -32920,7 +32808,7 @@
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>sem sinal (-1.1% do topo; Em Alta)</t>
+          <t>sem sinal (-4.2% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -33080,7 +32968,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EQTL3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -33090,23 +32978,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>32.38</v>
+        <v>32.06</v>
       </c>
       <c r="E124" t="n">
-        <v>40.16</v>
+        <v>27.98</v>
       </c>
       <c r="F124" t="n">
-        <v>19.23</v>
+        <v>15.45</v>
       </c>
       <c r="G124" t="n">
-        <v>27</v>
+        <v>33.61</v>
       </c>
       <c r="H124" t="n">
-        <v>47.73</v>
+        <v>72.73</v>
       </c>
       <c r="I124" t="n">
         <v>123</v>
@@ -33117,7 +33005,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>7</v>
@@ -33132,7 +33020,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="b">
         <v>0</v>
@@ -33148,61 +33036,65 @@
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>49205260288</v>
+        <v>129685618688</v>
       </c>
       <c r="W124" t="n">
-        <v>31.93</v>
+        <v>40.58</v>
       </c>
       <c r="X124" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="Y124" t="n">
-        <v>4.03</v>
+        <v>7.72</v>
       </c>
       <c r="Z124" t="n">
-        <v>6.02</v>
+        <v>5.92</v>
       </c>
       <c r="AA124" t="n">
-        <v>10.19</v>
+        <v>5.45</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.89</v>
+        <v>2.27</v>
       </c>
       <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AE124" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF124" t="inlineStr"/>
+        <v>2.27</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>22.54</v>
+      </c>
       <c r="AG124" t="n">
-        <v>39.20999908447266</v>
+        <v>18.25</v>
       </c>
       <c r="AH124" t="n">
-        <v>26.34</v>
+        <v>23.48</v>
       </c>
       <c r="AI124" t="n">
-        <v>16.03</v>
+        <v>11.52</v>
       </c>
       <c r="AJ124" t="n">
-        <v>12.46</v>
+        <v>3.68</v>
       </c>
       <c r="AK124" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="AL124" t="inlineStr"/>
+        <v>8.77</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>4.28</v>
+      </c>
       <c r="AM124" t="n">
-        <v>19.65</v>
+        <v>10.35</v>
       </c>
       <c r="AN124" t="n">
-        <v>19.89</v>
+        <v>8.77</v>
       </c>
       <c r="AO124" t="n">
-        <v>-49.26</v>
+        <v>-51.93</v>
       </c>
       <c r="AP124" t="n">
-        <v>-49.9</v>
+        <v>-43.31</v>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
@@ -33219,17 +33111,17 @@
       <c r="AU124" t="inlineStr"/>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW124" t="n">
-        <v>40.95000076293945</v>
+        <v>18.25</v>
       </c>
       <c r="AX124" t="n">
-        <v>-4.249088268739499</v>
+        <v>0</v>
       </c>
       <c r="AY124" t="n">
-        <v>-15.34974235145781</v>
+        <v>-14.11764705882353</v>
       </c>
       <c r="AZ124" t="b">
         <v>0</v>
@@ -33242,7 +33134,7 @@
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>sem sinal (-4.2% do topo; Em Baixa)</t>
+          <t>sem sinal (+0.0% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -33416,13 +33308,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>30.6</v>
+        <v>30.66</v>
       </c>
       <c r="E126" t="n">
         <v>28.44</v>
       </c>
       <c r="F126" t="n">
-        <v>42.56</v>
+        <v>42.74</v>
       </c>
       <c r="G126" t="n">
         <v>21.79</v>
@@ -33821,10 +33713,10 @@
         </is>
       </c>
       <c r="AW128" t="n">
-        <v>0.3300000131130219</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="AX128" t="n">
-        <v>-15.15151816185063</v>
+        <v>-9.677419664956521</v>
       </c>
       <c r="AY128" t="n">
         <v>-80.5555562454241</v>
@@ -33840,7 +33732,7 @@
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>sem sinal (-15.2% do topo; Em Baixa)</t>
+          <t>sem sinal (-9.7% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -33986,7 +33878,7 @@
       <c r="AU129" t="inlineStr"/>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AW129" t="n">
@@ -34009,7 +33901,7 @@
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>sem sinal (-1.9% do topo; Lateral)</t>
+          <t>sem sinal (-1.9% do topo; Em Alta)</t>
         </is>
       </c>
     </row>
@@ -34084,7 +33976,7 @@
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>9784341504</v>
+        <v>9839271936</v>
       </c>
       <c r="W130" t="n">
         <v>114.78</v>
@@ -34115,24 +34007,24 @@
         <v>3.06</v>
       </c>
       <c r="AG130" t="n">
-        <v>71.25</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="AH130" t="inlineStr"/>
       <c r="AI130" t="inlineStr"/>
       <c r="AJ130" t="n">
-        <v>7.98</v>
+        <v>8.02</v>
       </c>
       <c r="AK130" t="n">
-        <v>12.19</v>
+        <v>12.26</v>
       </c>
       <c r="AL130" t="n">
-        <v>18.62</v>
+        <v>18.73</v>
       </c>
       <c r="AM130" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="AN130" t="n">
-        <v>12.19</v>
+        <v>12.26</v>
       </c>
       <c r="AO130" t="n">
         <v>-82.90000000000001</v>
@@ -34159,13 +34051,13 @@
         </is>
       </c>
       <c r="AW130" t="n">
-        <v>75.94000244140625</v>
+        <v>75.26999664306641</v>
       </c>
       <c r="AX130" t="n">
-        <v>-6.175931380862099</v>
+        <v>-4.809346723308194</v>
       </c>
       <c r="AY130" t="n">
-        <v>-16.07774002420738</v>
+        <v>-15.60659571479652</v>
       </c>
       <c r="AZ130" t="b">
         <v>0</v>
@@ -34178,7 +34070,7 @@
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>sem sinal (-6.2% do topo; Em Baixa)</t>
+          <t>sem sinal (-4.8% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>
@@ -34314,10 +34206,10 @@
         </is>
       </c>
       <c r="AW131" t="n">
-        <v>12.31999969482422</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="AX131" t="n">
-        <v>-8.441558341027754</v>
+        <v>-8.367186446266416</v>
       </c>
       <c r="AY131" t="n">
         <v>-23.05593553629934</v>
@@ -34509,10 +34401,10 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>25</v>
+        <v>25.17</v>
       </c>
       <c r="E133" t="n">
-        <v>34.52</v>
+        <v>35.03</v>
       </c>
       <c r="F133" t="n">
         <v>12.65</v>
@@ -34528,7 +34420,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -34563,7 +34455,7 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>51848818688</v>
+        <v>51957202944</v>
       </c>
       <c r="W133" t="n">
         <v>40.6</v>
@@ -34631,10 +34523,14 @@
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="inlineStr"/>
-      <c r="AU133" t="inlineStr"/>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AW133" t="n">
@@ -34650,14 +34546,14 @@
         <v>0</v>
       </c>
       <c r="BA133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB133" t="b">
         <v>0</v>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>sem sinal (-0.0% do topo; Em Baixa)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -34732,7 +34628,7 @@
         <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>696023296</v>
+        <v>729701824</v>
       </c>
       <c r="W134" t="n">
         <v>-0.18</v>
@@ -34761,7 +34657,7 @@
       </c>
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="n">
-        <v>0.6200000047683716</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="AH134" t="inlineStr"/>
       <c r="AI134" t="inlineStr"/>
@@ -34791,13 +34687,13 @@
         </is>
       </c>
       <c r="AW134" t="n">
-        <v>0.9599999785423279</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="AX134" t="n">
-        <v>-35.41666472641126</v>
+        <v>-26.96629363980926</v>
       </c>
       <c r="AY134" t="n">
-        <v>-89.31034509690564</v>
+        <v>-88.63636363636364</v>
       </c>
       <c r="AZ134" t="b">
         <v>0</v>
@@ -34810,7 +34706,7 @@
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>sem sinal (-35.4% do topo; Em Baixa)</t>
+          <t>sem sinal (-27.0% do topo; Em Baixa)</t>
         </is>
       </c>
     </row>

--- a/reports/screener_2026-08-05.xlsx
+++ b/reports/screener_2026-08-05.xlsx
@@ -984,7 +984,7 @@
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         <v>15.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="AA4" t="n">
         <v>23.93</v>
@@ -1119,10 +1119,10 @@
         <v>25.09000015258789</v>
       </c>
       <c r="AI4" t="n">
-        <v>16.49</v>
+        <v>16.48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30.58</v>
+        <v>30.57</v>
       </c>
       <c r="AK4" t="n">
         <v>64.8</v>
@@ -1134,7 +1134,7 @@
         <v>146.73</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.59</v>
+        <v>47.58</v>
       </c>
       <c r="AO4" t="n">
         <v>47.38</v>
@@ -1149,7 +1149,7 @@
         <v>69.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>89.67</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26.68000030517578</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="BA4" t="n">
-        <v>-5.959520743631474</v>
+        <v>-6.380593780420607</v>
       </c>
       <c r="BB4" t="n">
         <v>-26.80863172101163</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
         <v>15.44</v>
       </c>
       <c r="AS5" t="n">
-        <v>30.39</v>
+        <v>30.38</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
         <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>55.43</v>
+        <v>55.42</v>
       </c>
       <c r="AS7" t="n">
-        <v>77.54000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="BA7" t="n">
-        <v>-13.00000190734863</v>
+        <v>-16.34615261173808</v>
       </c>
       <c r="BB7" t="n">
         <v>-35.46839081107605</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-13.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-16.3%))</t>
         </is>
       </c>
     </row>
@@ -2096,13 +2096,13 @@
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>5.429999828338623</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="BA9" t="n">
-        <v>-14.1804789183963</v>
+        <v>-17.08185156041993</v>
       </c>
       <c r="BB9" t="n">
-        <v>-41.3906633420233</v>
+        <v>-41.39066698170934</v>
       </c>
       <c r="BC9" t="b">
         <v>1</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-14.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-17.1%))</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v>24.74</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.99</v>
+        <v>13.98</v>
       </c>
       <c r="AA10" t="n">
         <v>29.03</v>
@@ -2250,10 +2250,10 @@
         <v>4</v>
       </c>
       <c r="AR10" t="n">
-        <v>42.73</v>
+        <v>42.72</v>
       </c>
       <c r="AS10" t="n">
-        <v>55.05</v>
+        <v>55.04</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11.06999969482422</v>
+        <v>11.28999996185303</v>
       </c>
       <c r="BA10" t="n">
-        <v>-4.516711958300911</v>
+        <v>-6.377327453158244</v>
       </c>
       <c r="BB10" t="n">
         <v>-44.3098000539846</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
         <v>258</v>
       </c>
       <c r="AS11" t="n">
-        <v>312.55</v>
+        <v>312.54</v>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8.489999771118164</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="BA11" t="n">
-        <v>-8.480563128411301</v>
+        <v>-12.59842878676004</v>
       </c>
       <c r="BB11" t="n">
         <v>-28.27777682361776</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-12.6%))</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>14.95</v>
       </c>
       <c r="AO12" t="n">
-        <v>14.47</v>
+        <v>14.46</v>
       </c>
       <c r="AP12" t="n">
         <v>13.02</v>
@@ -2621,7 +2621,7 @@
         <v>28.77</v>
       </c>
       <c r="AS12" t="n">
-        <v>47.86</v>
+        <v>47.85</v>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>-19.84</v>
       </c>
       <c r="AS13" t="n">
-        <v>-10.93</v>
+        <v>-10.94</v>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>14.44999980926514</v>
+        <v>14.47000026702881</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.4844269601950835</v>
+        <v>-0.6219775461439592</v>
       </c>
       <c r="BB13" t="n">
         <v>-22.78768022987632</v>
@@ -2982,7 +2982,7 @@
         <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>81.31999999999999</v>
+        <v>81.31</v>
       </c>
       <c r="AS14" t="n">
         <v>86.58</v>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3.869999885559082</v>
+        <v>3.900000095367432</v>
       </c>
       <c r="BA14" t="n">
-        <v>-7.235141593533156</v>
+        <v>-7.948722400451991</v>
       </c>
       <c r="BB14" t="n">
         <v>-27.79886012258027</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.9%))</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-1.9%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-1.9%))</t>
         </is>
       </c>
     </row>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5.400000095367432</v>
+        <v>5.75</v>
       </c>
       <c r="BA16" t="n">
-        <v>-12.77777861175222</v>
+        <v>-18.08695585831351</v>
       </c>
       <c r="BB16" t="n">
         <v>-44.78994625697538</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-12.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-18.1%))</t>
         </is>
       </c>
     </row>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>18.65999984741211</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="BA17" t="n">
-        <v>-14.46945247236746</v>
+        <v>-15.33156649781151</v>
       </c>
       <c r="BB17" t="n">
         <v>-54.36595303857709</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-14.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-15.3%))</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>6.72</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.73</v>
+        <v>5.74</v>
       </c>
       <c r="AA18" t="n">
         <v>24.19</v>
@@ -3694,7 +3694,7 @@
         <v>6.39</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
       <c r="AK18" t="n">
         <v>24.01</v>
@@ -3721,7 +3721,7 @@
         <v>0.88</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.99</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>6.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.91</v>
+        <v>7.77</v>
       </c>
       <c r="AA19" t="n">
         <v>27.12</v>
@@ -3877,10 +3877,10 @@
         <v>10.85000038146973</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.13</v>
+        <v>6.03</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10.26</v>
+        <v>10.08</v>
       </c>
       <c r="AK19" t="n">
         <v>33.26</v>
@@ -3889,25 +3889,25 @@
         <v>25.31</v>
       </c>
       <c r="AM19" t="n">
-        <v>36.47</v>
+        <v>36.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.33</v>
+        <v>31.56</v>
       </c>
       <c r="AO19" t="n">
-        <v>29.29</v>
+        <v>33.26</v>
       </c>
       <c r="AP19" t="n">
-        <v>26.36</v>
+        <v>29.93</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR19" t="n">
-        <v>142.92</v>
+        <v>175.87</v>
       </c>
       <c r="AS19" t="n">
-        <v>142.63</v>
+        <v>190.83</v>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>-4.3176944710975</v>
       </c>
       <c r="BB19" t="n">
-        <v>-23.34158416605098</v>
+        <v>-23.34158944412654</v>
       </c>
       <c r="BC19" t="b">
         <v>1</v>
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>32.72999954223633</v>
+        <v>33.59000015258789</v>
       </c>
       <c r="BA20" t="n">
-        <v>-2.138713023922101</v>
+        <v>-4.644243424246685</v>
       </c>
       <c r="BB20" t="n">
         <v>-21.96522472282059</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.6%))</t>
         </is>
       </c>
     </row>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>9.760000228881836</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="BA21" t="n">
-        <v>-8.811481456800019</v>
+        <v>-13.50826383358356</v>
       </c>
       <c r="BB21" t="n">
-        <v>-37.68844283346846</v>
+        <v>-37.6884471704558</v>
       </c>
       <c r="BC21" t="b">
         <v>1</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-13.5%))</t>
         </is>
       </c>
     </row>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>12.26000022888184</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="BA22" t="n">
-        <v>-8.319742567057853</v>
+        <v>-11.70463334405124</v>
       </c>
       <c r="BB22" t="n">
         <v>-32.25406537556344</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.7%))</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
         <v>117.14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>170.55</v>
+        <v>170.56</v>
       </c>
       <c r="AK23" t="n">
         <v>85.67</v>
@@ -4634,7 +4634,7 @@
         <v>101.41</v>
       </c>
       <c r="AP23" t="n">
-        <v>91.26000000000001</v>
+        <v>91.27</v>
       </c>
       <c r="AQ23" t="n">
         <v>4</v>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>43.41999816894531</v>
+        <v>43.04999923706055</v>
       </c>
       <c r="BA23" t="n">
-        <v>-3.431593566568136</v>
+        <v>-2.601623581262669</v>
       </c>
       <c r="BB23" t="n">
         <v>-14.7034868185516</v>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.4%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.6%))</t>
         </is>
       </c>
     </row>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>22.5</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="BA24" t="n">
-        <v>-3.911107381184897</v>
+        <v>-5.836229523830728</v>
       </c>
       <c r="BB24" t="n">
         <v>-39.96970182639408</v>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.8%))</t>
         </is>
       </c>
     </row>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>12.67000007629395</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="BA26" t="n">
-        <v>-6.787684700068297</v>
+        <v>-9.083905868305431</v>
       </c>
       <c r="BB26" t="n">
         <v>-31.56747126463702</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.1%))</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
         <v>4.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7.89</v>
+        <v>7.88</v>
       </c>
       <c r="AK27" t="n">
         <v>19.67</v>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>14.10000038146973</v>
+        <v>14.28999996185303</v>
       </c>
       <c r="BA27" t="n">
-        <v>-3.049647471931205</v>
+        <v>-4.338697601218778</v>
       </c>
       <c r="BB27" t="n">
         <v>-21.08023573257425</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>10.34000015258789</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="BA28" t="n">
-        <v>-9.671179741227764</v>
+        <v>-10.87785724659653</v>
       </c>
       <c r="BB28" t="n">
         <v>-48.32374123146461</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.9%))</t>
         </is>
       </c>
     </row>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>49.04000091552734</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="BA29" t="n">
-        <v>-3.853995420807621</v>
+        <v>-3.182749923568973</v>
       </c>
       <c r="BB29" t="n">
         <v>-13.66491732462657</v>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.9%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>28.53000068664551</v>
+        <v>29.25</v>
       </c>
       <c r="BA30" t="n">
-        <v>-6.379255374588089</v>
+        <v>-8.683763813768696</v>
       </c>
       <c r="BB30" t="n">
         <v>-16.64613360497911</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
         </is>
       </c>
     </row>
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>6.489999771118164</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.927574531340327</v>
+        <v>-3.816793781985395</v>
       </c>
       <c r="BB32" t="n">
         <v>-39.99999818347749</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
         </is>
       </c>
     </row>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>33.04000091552734</v>
+        <v>34.59999847412109</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.240919600639079</v>
+        <v>-3.323692953460033</v>
       </c>
       <c r="BB33" t="n">
         <v>-11.83447028542765</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (+1.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.3%))</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       <c r="AX34" t="inlineStr"/>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ34" t="n">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
         <v>-4.559090928004061</v>
       </c>
       <c r="BB37" t="n">
-        <v>-13.40836972085915</v>
+        <v>-13.40836033901044</v>
       </c>
       <c r="BC37" t="b">
         <v>1</v>
@@ -7943,7 +7943,7 @@
         <v>-12.73</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.49</v>
+        <v>12.48</v>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
@@ -8146,14 +8146,14 @@
       <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ42" t="n">
-        <v>4.03000020980835</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="BA42" t="n">
-        <v>-3.47394783165117</v>
+        <v>-2.261304365276429</v>
       </c>
       <c r="BB42" t="n">
         <v>-48.71330110836315</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.5%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.3%))</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
         <v>-3.496970464635651</v>
       </c>
       <c r="BB43" t="n">
-        <v>-18.64656395665553</v>
+        <v>-18.64655512043243</v>
       </c>
       <c r="BC43" t="b">
         <v>1</v>
@@ -8486,10 +8486,10 @@
         <v>3</v>
       </c>
       <c r="AR44" t="n">
-        <v>-36.41</v>
+        <v>-36.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>-17.41</v>
+        <v>-17.4</v>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
       <c r="AX44" t="inlineStr"/>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AZ44" t="n">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.6%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.6%))</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ47" t="n">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.7%))</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.1, +0.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.0, +0.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="AZ49" t="n">
-        <v>3.539999961853027</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="BA49" t="n">
-        <v>-0.5649712187015044</v>
+        <v>-3.030306612851064</v>
       </c>
       <c r="BB49" t="n">
         <v>-53.80577383475578</v>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-0.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.0%))</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       <c r="AX52" t="inlineStr"/>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ52" t="n">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-0.9%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-0.9%))</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
         <v>24.98999977111816</v>
       </c>
       <c r="AI53" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="AJ53" t="n">
         <v>8.119999999999999</v>
@@ -10160,7 +10160,7 @@
       <c r="AX53" t="inlineStr"/>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ53" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.8%))</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10275,7 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>98.33</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
@@ -10288,7 +10288,7 @@
         <v>33.1</v>
       </c>
       <c r="AJ54" t="n">
-        <v>48.19</v>
+        <v>48.2</v>
       </c>
       <c r="AK54" t="n">
         <v>48.75</v>
@@ -10301,19 +10301,19 @@
         <v>43.35</v>
       </c>
       <c r="AO54" t="n">
-        <v>48.19</v>
+        <v>48.2</v>
       </c>
       <c r="AP54" t="n">
-        <v>43.37</v>
+        <v>43.38</v>
       </c>
       <c r="AQ54" t="n">
         <v>3</v>
       </c>
       <c r="AR54" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="AZ55" t="n">
-        <v>15.01000022888184</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="BA55" t="n">
-        <v>-0.1332475513570408</v>
+        <v>-0.9253162079564725</v>
       </c>
       <c r="BB55" t="n">
         <v>-17.53704668810377</v>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-0.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-0.9%))</t>
         </is>
       </c>
     </row>
@@ -10702,10 +10702,10 @@
         </is>
       </c>
       <c r="AZ56" t="n">
-        <v>11.34000015258789</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="BA56" t="n">
-        <v>-0.7936521285438536</v>
+        <v>-0.2659550858277293</v>
       </c>
       <c r="BB56" t="n">
         <v>-15.63968699969552</v>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-0.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-0.3%))</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -10880,19 +10880,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>A BMOB3 apresenta um perfil de alta qualidade operacional no setor de serviços de comunicação, com um retorno sobre o patrimônio líquido de 16,4% e um retorno sobre o capital investido de 10,1% que se posicionam significativamente acima dos pares, cujas médias são de 3,0% e 4,4%, respectivamente. Essa sólida rentabilidade convive com múltiplos de preço que sugerem uma avaliação intermediária, onde o preço sobre o lucro de 12,72 e o preço sobre o valor patrimonial de 2,08 indicam que o mercado já precifica parte dessa eficiência, embora o indicador de crescimento de lucros de 1,5 aponte para um equilíbrio relativo entre preço e expansão. A saúde financeira da companhia é robusta, evidenciada por um endividamento sobre o patrimônio de apenas 0,05 e uma liquidez corrente de 1,78, garantindo que a alta rentabilidade não esteja alavancada em riscos financeiros excessivos. Esse balanço patrimonial desalancado confere sustentabilidade ao expressivo rendimento de dividendos de 9,0%, o qual se mostra coerente com a forte geração de lucro e com a capacidade de distribuição da empresa. No quesito expansão, a taxa de crescimento anual composta da receita nos últimos cinco anos foi de 8,5%, superando com folga a retração média de 0,7% do setor, o que corrobora o sucesso do modelo de negócios refletido no checklist de critérios da empresa, que atendeu a 6 de 7 requisitos estabelecidos. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão relevante entre si, variando desde a abordagem conservadora de Bazin a 10,21 reais até a projeção mais otimista de Lynch a 27,24 reais, resultando em uma média de 20,68 reais e uma mediana de 22,08 reais. Frente ao preço atual de 23,94 reais, o preço-teto ajustado com margem de segurança fica em 19,87 reais, o que aponta para um potencial de valorização negativo de 17,0% em relação a essa métrica de referência ajustada, em um momento em que a tendência do papel é lateral, apesar do sinal gráfico de pivô de alta. Como principais prós, destacam-se a excelente rentabilidade comparativa, o endividamento quase nulo, o forte histórico de crescimento frente aos pares e o atraente retorno em proventos; em contrapartida, pesam negativamente a margem líquida abaixo de 15% e a ausência de margem de segurança no preço atual perante a média dos modelos de valuation calculados.</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ57" t="n">
@@ -10908,14 +10900,14 @@
         <v>1</v>
       </c>
       <c r="BD57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-0.4%))</t>
         </is>
       </c>
     </row>
@@ -11078,10 +11070,10 @@
         </is>
       </c>
       <c r="AZ58" t="n">
-        <v>43.31999969482422</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="BA58" t="n">
-        <v>-1.108032192100128</v>
+        <v>-0.6032443868630666</v>
       </c>
       <c r="BB58" t="n">
         <v>-28.17376420728133</v>
@@ -11097,7 +11089,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-1.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-0.6%))</t>
         </is>
       </c>
     </row>
@@ -11264,10 +11256,10 @@
         </is>
       </c>
       <c r="AZ59" t="n">
-        <v>16.04999923706055</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="BA59" t="n">
-        <v>-10.90342136767718</v>
+        <v>-11.2903260157962</v>
       </c>
       <c r="BB59" t="n">
         <v>-33.16870823364264</v>
@@ -11283,7 +11275,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.3%))</t>
         </is>
       </c>
     </row>
@@ -11632,10 +11624,10 @@
         </is>
       </c>
       <c r="AZ61" t="n">
-        <v>36.0099983215332</v>
+        <v>36.04999923706055</v>
       </c>
       <c r="BA61" t="n">
-        <v>-4.332123386023334</v>
+        <v>-4.43827602769058</v>
       </c>
       <c r="BB61" t="n">
         <v>-23.36268916509432</v>
@@ -11651,7 +11643,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -11814,10 +11806,10 @@
         </is>
       </c>
       <c r="AZ62" t="n">
-        <v>33.75</v>
+        <v>34.11000061035156</v>
       </c>
       <c r="BA62" t="n">
-        <v>-2.962962962962967</v>
+        <v>-3.987102275040222</v>
       </c>
       <c r="BB62" t="n">
         <v>-11.17502153302618</v>
@@ -11833,7 +11825,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.0%))</t>
         </is>
       </c>
     </row>
@@ -12182,14 +12174,14 @@
       <c r="AX64" t="inlineStr"/>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ64" t="n">
-        <v>47.18999862670898</v>
+        <v>47.20000076293945</v>
       </c>
       <c r="BA64" t="n">
-        <v>-2.330999165358116</v>
+        <v>-2.351696170359208</v>
       </c>
       <c r="BB64" t="n">
         <v>-13.02433864601955</v>
@@ -12205,7 +12197,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.4%))</t>
         </is>
       </c>
     </row>
@@ -12368,10 +12360,10 @@
         </is>
       </c>
       <c r="AZ65" t="n">
-        <v>37.2599983215332</v>
+        <v>37.43000030517578</v>
       </c>
       <c r="BA65" t="n">
-        <v>-6.575408101471359</v>
+        <v>-6.999729923920073</v>
       </c>
       <c r="BB65" t="n">
         <v>-28.55090209131846</v>
@@ -12387,7 +12379,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.0%))</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12730,7 @@
         <v>-0.7524892122498517</v>
       </c>
       <c r="BB67" t="n">
-        <v>-10.10472871725758</v>
+        <v>-10.10473516918537</v>
       </c>
       <c r="BC67" t="b">
         <v>1</v>
@@ -12920,7 +12912,7 @@
         <v>-0.356291362225214</v>
       </c>
       <c r="BB68" t="n">
-        <v>-13.89556964471864</v>
+        <v>-13.89556104749984</v>
       </c>
       <c r="BC68" t="b">
         <v>1</v>
@@ -13037,10 +13029,10 @@
         <v>42.38000106811523</v>
       </c>
       <c r="AI69" t="n">
-        <v>21.66</v>
+        <v>21.65</v>
       </c>
       <c r="AJ69" t="n">
-        <v>40.17</v>
+        <v>40.16</v>
       </c>
       <c r="AK69" t="n">
         <v>56.38</v>
@@ -13049,25 +13041,25 @@
         <v>42.56</v>
       </c>
       <c r="AM69" t="n">
-        <v>78.95</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="AN69" t="n">
-        <v>39.4</v>
+        <v>39.39</v>
       </c>
       <c r="AO69" t="n">
-        <v>40.17</v>
+        <v>40.16</v>
       </c>
       <c r="AP69" t="n">
-        <v>36.15</v>
+        <v>36.14</v>
       </c>
       <c r="AQ69" t="n">
         <v>3</v>
       </c>
       <c r="AR69" t="n">
-        <v>-14.69</v>
+        <v>-14.72</v>
       </c>
       <c r="AS69" t="n">
-        <v>-7.03</v>
+        <v>-7.05</v>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
@@ -13088,17 +13080,17 @@
       <c r="AX69" t="inlineStr"/>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ69" t="n">
-        <v>43.16999816894531</v>
+        <v>43.63000106811523</v>
       </c>
       <c r="BA69" t="n">
-        <v>-1.829967881255012</v>
+        <v>-2.865001075861762</v>
       </c>
       <c r="BB69" t="n">
-        <v>-12.97564384179887</v>
+        <v>-13.01253231157464</v>
       </c>
       <c r="BC69" t="b">
         <v>1</v>
@@ -13111,7 +13103,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-1.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
         </is>
       </c>
     </row>
@@ -13250,10 +13242,10 @@
         <v>4</v>
       </c>
       <c r="AR70" t="n">
-        <v>116.2</v>
+        <v>116.19</v>
       </c>
       <c r="AS70" t="n">
-        <v>117.29</v>
+        <v>117.28</v>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
@@ -13278,10 +13270,10 @@
         </is>
       </c>
       <c r="AZ70" t="n">
-        <v>2.269999980926514</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="BA70" t="n">
-        <v>-5.286338615302688</v>
+        <v>-25.0871017038871</v>
       </c>
       <c r="BB70" t="n">
         <v>-59.34562708904367</v>
@@ -13297,7 +13289,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-25.1%))</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13701,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -13835,7 +13827,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -13844,10 +13836,10 @@
         </is>
       </c>
       <c r="AZ73" t="n">
-        <v>14.96000003814697</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="BA73" t="n">
-        <v>0.06684644957444252</v>
+        <v>-1.188114561278963</v>
       </c>
       <c r="BB73" t="n">
         <v>-15.64782318985707</v>
@@ -13863,7 +13855,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.2, +0.1% do topo, MM50&gt;MM200)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -14198,10 +14190,10 @@
         </is>
       </c>
       <c r="AZ75" t="n">
-        <v>21.35000038146973</v>
+        <v>21.27000045776367</v>
       </c>
       <c r="BA75" t="n">
-        <v>-1.405157559948145</v>
+        <v>-1.034326356221693</v>
       </c>
       <c r="BB75" t="n">
         <v>-23.57261978673966</v>
@@ -14217,7 +14209,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-1.4%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-1.0%))</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14336,7 @@
         <v>24.18</v>
       </c>
       <c r="AN76" t="n">
-        <v>21.21</v>
+        <v>21.2</v>
       </c>
       <c r="AO76" t="n">
         <v>20.56</v>
@@ -14384,10 +14376,10 @@
         </is>
       </c>
       <c r="AZ76" t="n">
-        <v>10.03999996185303</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="BA76" t="n">
-        <v>-6.772911431866946</v>
+        <v>-9.126218608259585</v>
       </c>
       <c r="BB76" t="n">
         <v>-38.76167698563921</v>
@@ -14403,7 +14395,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.1%))</t>
         </is>
       </c>
     </row>
@@ -14570,10 +14562,10 @@
         </is>
       </c>
       <c r="AZ77" t="n">
-        <v>29.97999954223633</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="BA77" t="n">
-        <v>-7.571716118826677</v>
+        <v>-8.668427998972517</v>
       </c>
       <c r="BB77" t="n">
         <v>-21.54142799156917</v>
@@ -14589,7 +14581,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
         </is>
       </c>
     </row>
@@ -15174,7 +15166,7 @@
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -15197,7 +15189,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15276,7 @@
         <v>15.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="AA4" t="n">
         <v>23.93</v>
@@ -15309,10 +15301,10 @@
         <v>25.09000015258789</v>
       </c>
       <c r="AI4" t="n">
-        <v>16.49</v>
+        <v>16.48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30.58</v>
+        <v>30.57</v>
       </c>
       <c r="AK4" t="n">
         <v>64.8</v>
@@ -15324,7 +15316,7 @@
         <v>146.73</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.59</v>
+        <v>47.58</v>
       </c>
       <c r="AO4" t="n">
         <v>47.38</v>
@@ -15339,7 +15331,7 @@
         <v>69.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>89.67</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -15364,10 +15356,10 @@
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26.68000030517578</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="BA4" t="n">
-        <v>-5.959520743631474</v>
+        <v>-6.380593780420607</v>
       </c>
       <c r="BB4" t="n">
         <v>-26.80863172101163</v>
@@ -15383,7 +15375,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -15521,7 +15513,7 @@
         <v>15.44</v>
       </c>
       <c r="AS5" t="n">
-        <v>30.39</v>
+        <v>30.38</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -15886,10 +15878,10 @@
         <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>55.43</v>
+        <v>55.42</v>
       </c>
       <c r="AS7" t="n">
-        <v>77.54000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -15914,10 +15906,10 @@
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="BA7" t="n">
-        <v>-13.00000190734863</v>
+        <v>-16.34615261173808</v>
       </c>
       <c r="BB7" t="n">
         <v>-35.46839081107605</v>
@@ -15933,7 +15925,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-13.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-16.3%))</t>
         </is>
       </c>
     </row>
@@ -16286,13 +16278,13 @@
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>5.429999828338623</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="BA9" t="n">
-        <v>-14.1804789183963</v>
+        <v>-17.08185156041993</v>
       </c>
       <c r="BB9" t="n">
-        <v>-41.3906633420233</v>
+        <v>-41.39066698170934</v>
       </c>
       <c r="BC9" t="b">
         <v>1</v>
@@ -16305,7 +16297,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-14.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-17.1%))</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16384,7 @@
         <v>24.74</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.99</v>
+        <v>13.98</v>
       </c>
       <c r="AA10" t="n">
         <v>29.03</v>
@@ -16440,10 +16432,10 @@
         <v>4</v>
       </c>
       <c r="AR10" t="n">
-        <v>42.73</v>
+        <v>42.72</v>
       </c>
       <c r="AS10" t="n">
-        <v>55.05</v>
+        <v>55.04</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -16468,10 +16460,10 @@
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11.06999969482422</v>
+        <v>11.28999996185303</v>
       </c>
       <c r="BA10" t="n">
-        <v>-4.516711958300911</v>
+        <v>-6.377327453158244</v>
       </c>
       <c r="BB10" t="n">
         <v>-44.3098000539846</v>
@@ -16487,7 +16479,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16621,7 @@
         <v>258</v>
       </c>
       <c r="AS11" t="n">
-        <v>312.55</v>
+        <v>312.54</v>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
@@ -16654,10 +16646,10 @@
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8.489999771118164</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="BA11" t="n">
-        <v>-8.480563128411301</v>
+        <v>-12.59842878676004</v>
       </c>
       <c r="BB11" t="n">
         <v>-28.27777682361776</v>
@@ -16673,7 +16665,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-12.6%))</t>
         </is>
       </c>
     </row>
@@ -16799,7 +16791,7 @@
         <v>14.95</v>
       </c>
       <c r="AO12" t="n">
-        <v>14.47</v>
+        <v>14.46</v>
       </c>
       <c r="AP12" t="n">
         <v>13.02</v>
@@ -16811,7 +16803,7 @@
         <v>28.77</v>
       </c>
       <c r="AS12" t="n">
-        <v>47.86</v>
+        <v>47.85</v>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
@@ -16985,7 +16977,7 @@
         <v>-19.84</v>
       </c>
       <c r="AS13" t="n">
-        <v>-10.93</v>
+        <v>-10.94</v>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
@@ -17018,10 +17010,10 @@
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>14.44999980926514</v>
+        <v>14.47000026702881</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.4844269601950835</v>
+        <v>-0.6219775461439592</v>
       </c>
       <c r="BB13" t="n">
         <v>-22.78768022987632</v>
@@ -17172,7 +17164,7 @@
         <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>81.31999999999999</v>
+        <v>81.31</v>
       </c>
       <c r="AS14" t="n">
         <v>86.58</v>
@@ -17200,10 +17192,10 @@
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3.869999885559082</v>
+        <v>3.900000095367432</v>
       </c>
       <c r="BA14" t="n">
-        <v>-7.235141593533156</v>
+        <v>-7.948722400451991</v>
       </c>
       <c r="BB14" t="n">
         <v>-27.79886012258027</v>
@@ -17219,7 +17211,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.9%))</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17374,7 @@
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -17405,7 +17397,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-1.9%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-1.9%))</t>
         </is>
       </c>
     </row>
@@ -17568,10 +17560,10 @@
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5.400000095367432</v>
+        <v>5.75</v>
       </c>
       <c r="BA16" t="n">
-        <v>-12.77777861175222</v>
+        <v>-18.08695585831351</v>
       </c>
       <c r="BB16" t="n">
         <v>-44.78994625697538</v>
@@ -17587,7 +17579,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-12.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-18.1%))</t>
         </is>
       </c>
     </row>
@@ -17750,10 +17742,10 @@
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>18.65999984741211</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="BA17" t="n">
-        <v>-14.46945247236746</v>
+        <v>-15.33156649781151</v>
       </c>
       <c r="BB17" t="n">
         <v>-54.36595303857709</v>
@@ -17769,7 +17761,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-14.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-15.3%))</t>
         </is>
       </c>
     </row>
@@ -17856,7 +17848,7 @@
         <v>6.72</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.73</v>
+        <v>5.74</v>
       </c>
       <c r="AA18" t="n">
         <v>24.19</v>
@@ -17884,7 +17876,7 @@
         <v>6.39</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
       <c r="AK18" t="n">
         <v>24.01</v>
@@ -17911,7 +17903,7 @@
         <v>0.88</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.99</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
@@ -18042,7 +18034,7 @@
         <v>6.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.91</v>
+        <v>7.77</v>
       </c>
       <c r="AA19" t="n">
         <v>27.12</v>
@@ -18067,10 +18059,10 @@
         <v>10.85000038146973</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.13</v>
+        <v>6.03</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10.26</v>
+        <v>10.08</v>
       </c>
       <c r="AK19" t="n">
         <v>33.26</v>
@@ -18079,25 +18071,25 @@
         <v>25.31</v>
       </c>
       <c r="AM19" t="n">
-        <v>36.47</v>
+        <v>36.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.33</v>
+        <v>31.56</v>
       </c>
       <c r="AO19" t="n">
-        <v>29.29</v>
+        <v>33.26</v>
       </c>
       <c r="AP19" t="n">
-        <v>26.36</v>
+        <v>29.93</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR19" t="n">
-        <v>142.92</v>
+        <v>175.87</v>
       </c>
       <c r="AS19" t="n">
-        <v>142.63</v>
+        <v>190.83</v>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
@@ -18128,7 +18120,7 @@
         <v>-4.3176944710975</v>
       </c>
       <c r="BB19" t="n">
-        <v>-23.34158416605098</v>
+        <v>-23.34158944412654</v>
       </c>
       <c r="BC19" t="b">
         <v>1</v>
@@ -18308,10 +18300,10 @@
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>32.72999954223633</v>
+        <v>33.59000015258789</v>
       </c>
       <c r="BA20" t="n">
-        <v>-2.138713023922101</v>
+        <v>-4.644243424246685</v>
       </c>
       <c r="BB20" t="n">
         <v>-21.96522472282059</v>
@@ -18327,7 +18319,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.6%))</t>
         </is>
       </c>
     </row>
@@ -18490,13 +18482,13 @@
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>9.760000228881836</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="BA21" t="n">
-        <v>-8.811481456800019</v>
+        <v>-13.50826383358356</v>
       </c>
       <c r="BB21" t="n">
-        <v>-37.68844283346846</v>
+        <v>-37.6884471704558</v>
       </c>
       <c r="BC21" t="b">
         <v>1</v>
@@ -18509,7 +18501,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-13.5%))</t>
         </is>
       </c>
     </row>
@@ -18676,10 +18668,10 @@
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>12.26000022888184</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="BA22" t="n">
-        <v>-8.319742567057853</v>
+        <v>-11.70463334405124</v>
       </c>
       <c r="BB22" t="n">
         <v>-32.25406537556344</v>
@@ -18695,7 +18687,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.7%))</t>
         </is>
       </c>
     </row>
@@ -18808,7 +18800,7 @@
         <v>117.14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>170.55</v>
+        <v>170.56</v>
       </c>
       <c r="AK23" t="n">
         <v>85.67</v>
@@ -18824,7 +18816,7 @@
         <v>101.41</v>
       </c>
       <c r="AP23" t="n">
-        <v>91.26000000000001</v>
+        <v>91.27</v>
       </c>
       <c r="AQ23" t="n">
         <v>4</v>
@@ -18858,10 +18850,10 @@
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>43.41999816894531</v>
+        <v>43.04999923706055</v>
       </c>
       <c r="BA23" t="n">
-        <v>-3.431593566568136</v>
+        <v>-2.601623581262669</v>
       </c>
       <c r="BB23" t="n">
         <v>-14.7034868185516</v>
@@ -18877,7 +18869,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.4%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.6%))</t>
         </is>
       </c>
     </row>
@@ -19040,10 +19032,10 @@
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>22.5</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="BA24" t="n">
-        <v>-3.911107381184897</v>
+        <v>-5.836229523830728</v>
       </c>
       <c r="BB24" t="n">
         <v>-39.96970182639408</v>
@@ -19059,7 +19051,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.8%))</t>
         </is>
       </c>
     </row>
@@ -19412,10 +19404,10 @@
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>12.67000007629395</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="BA26" t="n">
-        <v>-6.787684700068297</v>
+        <v>-9.083905868305431</v>
       </c>
       <c r="BB26" t="n">
         <v>-31.56747126463702</v>
@@ -19431,7 +19423,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.1%))</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19538,7 @@
         <v>4.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7.89</v>
+        <v>7.88</v>
       </c>
       <c r="AK27" t="n">
         <v>19.67</v>
@@ -19598,10 +19590,10 @@
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>14.10000038146973</v>
+        <v>14.28999996185303</v>
       </c>
       <c r="BA27" t="n">
-        <v>-3.049647471931205</v>
+        <v>-4.338697601218778</v>
       </c>
       <c r="BB27" t="n">
         <v>-21.08023573257425</v>
@@ -19617,7 +19609,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -19780,10 +19772,10 @@
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>10.34000015258789</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="BA28" t="n">
-        <v>-9.671179741227764</v>
+        <v>-10.87785724659653</v>
       </c>
       <c r="BB28" t="n">
         <v>-48.32374123146461</v>
@@ -19799,7 +19791,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.9%))</t>
         </is>
       </c>
     </row>
@@ -19962,10 +19954,10 @@
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>49.04000091552734</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="BA29" t="n">
-        <v>-3.853995420807621</v>
+        <v>-3.182749923568973</v>
       </c>
       <c r="BB29" t="n">
         <v>-13.66491732462657</v>
@@ -19981,7 +19973,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.9%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -20144,10 +20136,10 @@
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>28.53000068664551</v>
+        <v>29.25</v>
       </c>
       <c r="BA30" t="n">
-        <v>-6.379255374588089</v>
+        <v>-8.683763813768696</v>
       </c>
       <c r="BB30" t="n">
         <v>-16.64613360497911</v>
@@ -20163,7 +20155,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
         </is>
       </c>
     </row>
@@ -20508,10 +20500,10 @@
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>6.489999771118164</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.927574531340327</v>
+        <v>-3.816793781985395</v>
       </c>
       <c r="BB32" t="n">
         <v>-39.99999818347749</v>
@@ -20527,7 +20519,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
         </is>
       </c>
     </row>
@@ -20694,10 +20686,10 @@
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>33.04000091552734</v>
+        <v>34.59999847412109</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.240919600639079</v>
+        <v>-3.323692953460033</v>
       </c>
       <c r="BB33" t="n">
         <v>-11.83447028542765</v>
@@ -20713,7 +20705,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (+1.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.3%))</t>
         </is>
       </c>
     </row>
@@ -20872,7 +20864,7 @@
       <c r="AX34" t="inlineStr"/>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ34" t="n">
@@ -20895,7 +20887,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -21428,7 +21420,7 @@
         <v>-4.559090928004061</v>
       </c>
       <c r="BB37" t="n">
-        <v>-13.40836972085915</v>
+        <v>-13.40836033901044</v>
       </c>
       <c r="BC37" t="b">
         <v>1</v>
@@ -22133,7 +22125,7 @@
         <v>-12.73</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.49</v>
+        <v>12.48</v>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
@@ -22336,14 +22328,14 @@
       <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ42" t="n">
-        <v>4.03000020980835</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="BA42" t="n">
-        <v>-3.47394783165117</v>
+        <v>-2.261304365276429</v>
       </c>
       <c r="BB42" t="n">
         <v>-48.71330110836315</v>
@@ -22359,7 +22351,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.5%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.3%))</t>
         </is>
       </c>
     </row>
@@ -22532,7 +22524,7 @@
         <v>-3.496970464635651</v>
       </c>
       <c r="BB43" t="n">
-        <v>-18.64656395665553</v>
+        <v>-18.64655512043243</v>
       </c>
       <c r="BC43" t="b">
         <v>1</v>
@@ -22676,10 +22668,10 @@
         <v>3</v>
       </c>
       <c r="AR44" t="n">
-        <v>-36.41</v>
+        <v>-36.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>-17.41</v>
+        <v>-17.4</v>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
@@ -22700,7 +22692,7 @@
       <c r="AX44" t="inlineStr"/>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AZ44" t="n">
@@ -22723,7 +22715,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.6%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.6%))</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23234,7 @@
       <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ47" t="n">
@@ -23265,7 +23257,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.7%))</t>
         </is>
       </c>
     </row>
@@ -23451,7 +23443,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.1, +0.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.0, +0.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -23618,10 +23610,10 @@
         </is>
       </c>
       <c r="AZ49" t="n">
-        <v>3.539999961853027</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="BA49" t="n">
-        <v>-0.5649712187015044</v>
+        <v>-3.030306612851064</v>
       </c>
       <c r="BB49" t="n">
         <v>-53.80577383475578</v>
@@ -23637,7 +23629,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-0.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.0%))</t>
         </is>
       </c>
     </row>
@@ -24168,7 +24160,7 @@
       <c r="AX52" t="inlineStr"/>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ52" t="n">
@@ -24191,7 +24183,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-0.9%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-0.9%))</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24291,7 @@
         <v>24.98999977111816</v>
       </c>
       <c r="AI53" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="AJ53" t="n">
         <v>8.119999999999999</v>
@@ -24350,7 +24342,7 @@
       <c r="AX53" t="inlineStr"/>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ53" t="n">
@@ -24373,7 +24365,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.8%))</t>
         </is>
       </c>
     </row>
@@ -24465,7 +24457,7 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>98.33</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
@@ -24478,7 +24470,7 @@
         <v>33.1</v>
       </c>
       <c r="AJ54" t="n">
-        <v>48.19</v>
+        <v>48.2</v>
       </c>
       <c r="AK54" t="n">
         <v>48.75</v>
@@ -24491,19 +24483,19 @@
         <v>43.35</v>
       </c>
       <c r="AO54" t="n">
-        <v>48.19</v>
+        <v>48.2</v>
       </c>
       <c r="AP54" t="n">
-        <v>43.37</v>
+        <v>43.38</v>
       </c>
       <c r="AQ54" t="n">
         <v>3</v>
       </c>
       <c r="AR54" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
@@ -24710,10 +24702,10 @@
         </is>
       </c>
       <c r="AZ55" t="n">
-        <v>15.01000022888184</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="BA55" t="n">
-        <v>-0.1332475513570408</v>
+        <v>-0.9253162079564725</v>
       </c>
       <c r="BB55" t="n">
         <v>-17.53704668810377</v>
@@ -24729,7 +24721,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-0.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-0.9%))</t>
         </is>
       </c>
     </row>
@@ -24892,10 +24884,10 @@
         </is>
       </c>
       <c r="AZ56" t="n">
-        <v>11.34000015258789</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="BA56" t="n">
-        <v>-0.7936521285438536</v>
+        <v>-0.2659550858277293</v>
       </c>
       <c r="BB56" t="n">
         <v>-15.63968699969552</v>
@@ -24911,7 +24903,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-0.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-0.3%))</t>
         </is>
       </c>
     </row>
@@ -24951,7 +24943,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -25070,19 +25062,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>A BMOB3 apresenta um perfil de alta qualidade operacional no setor de serviços de comunicação, com um retorno sobre o patrimônio líquido de 16,4% e um retorno sobre o capital investido de 10,1% que se posicionam significativamente acima dos pares, cujas médias são de 3,0% e 4,4%, respectivamente. Essa sólida rentabilidade convive com múltiplos de preço que sugerem uma avaliação intermediária, onde o preço sobre o lucro de 12,72 e o preço sobre o valor patrimonial de 2,08 indicam que o mercado já precifica parte dessa eficiência, embora o indicador de crescimento de lucros de 1,5 aponte para um equilíbrio relativo entre preço e expansão. A saúde financeira da companhia é robusta, evidenciada por um endividamento sobre o patrimônio de apenas 0,05 e uma liquidez corrente de 1,78, garantindo que a alta rentabilidade não esteja alavancada em riscos financeiros excessivos. Esse balanço patrimonial desalancado confere sustentabilidade ao expressivo rendimento de dividendos de 9,0%, o qual se mostra coerente com a forte geração de lucro e com a capacidade de distribuição da empresa. No quesito expansão, a taxa de crescimento anual composta da receita nos últimos cinco anos foi de 8,5%, superando com folga a retração média de 0,7% do setor, o que corrobora o sucesso do modelo de negócios refletido no checklist de critérios da empresa, que atendeu a 6 de 7 requisitos estabelecidos. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão relevante entre si, variando desde a abordagem conservadora de Bazin a 10,21 reais até a projeção mais otimista de Lynch a 27,24 reais, resultando em uma média de 20,68 reais e uma mediana de 22,08 reais. Frente ao preço atual de 23,94 reais, o preço-teto ajustado com margem de segurança fica em 19,87 reais, o que aponta para um potencial de valorização negativo de 17,0% em relação a essa métrica de referência ajustada, em um momento em que a tendência do papel é lateral, apesar do sinal gráfico de pivô de alta. Como principais prós, destacam-se a excelente rentabilidade comparativa, o endividamento quase nulo, o forte histórico de crescimento frente aos pares e o atraente retorno em proventos; em contrapartida, pesam negativamente a margem líquida abaixo de 15% e a ausência de margem de segurança no preço atual perante a média dos modelos de valuation calculados.</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ57" t="n">
@@ -25098,14 +25082,14 @@
         <v>1</v>
       </c>
       <c r="BD57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-0.4%))</t>
         </is>
       </c>
     </row>
@@ -25268,10 +25252,10 @@
         </is>
       </c>
       <c r="AZ58" t="n">
-        <v>43.31999969482422</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="BA58" t="n">
-        <v>-1.108032192100128</v>
+        <v>-0.6032443868630666</v>
       </c>
       <c r="BB58" t="n">
         <v>-28.17376420728133</v>
@@ -25287,7 +25271,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-1.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-0.6%))</t>
         </is>
       </c>
     </row>
@@ -25454,10 +25438,10 @@
         </is>
       </c>
       <c r="AZ59" t="n">
-        <v>16.04999923706055</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="BA59" t="n">
-        <v>-10.90342136767718</v>
+        <v>-11.2903260157962</v>
       </c>
       <c r="BB59" t="n">
         <v>-33.16870823364264</v>
@@ -25473,7 +25457,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.3%))</t>
         </is>
       </c>
     </row>
@@ -25822,10 +25806,10 @@
         </is>
       </c>
       <c r="AZ61" t="n">
-        <v>36.0099983215332</v>
+        <v>36.04999923706055</v>
       </c>
       <c r="BA61" t="n">
-        <v>-4.332123386023334</v>
+        <v>-4.43827602769058</v>
       </c>
       <c r="BB61" t="n">
         <v>-23.36268916509432</v>
@@ -25841,7 +25825,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -26004,10 +25988,10 @@
         </is>
       </c>
       <c r="AZ62" t="n">
-        <v>33.75</v>
+        <v>34.11000061035156</v>
       </c>
       <c r="BA62" t="n">
-        <v>-2.962962962962967</v>
+        <v>-3.987102275040222</v>
       </c>
       <c r="BB62" t="n">
         <v>-11.17502153302618</v>
@@ -26023,7 +26007,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.0%))</t>
         </is>
       </c>
     </row>
@@ -26372,14 +26356,14 @@
       <c r="AX64" t="inlineStr"/>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ64" t="n">
-        <v>47.18999862670898</v>
+        <v>47.20000076293945</v>
       </c>
       <c r="BA64" t="n">
-        <v>-2.330999165358116</v>
+        <v>-2.351696170359208</v>
       </c>
       <c r="BB64" t="n">
         <v>-13.02433864601955</v>
@@ -26395,7 +26379,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.4%))</t>
         </is>
       </c>
     </row>
@@ -26558,10 +26542,10 @@
         </is>
       </c>
       <c r="AZ65" t="n">
-        <v>37.2599983215332</v>
+        <v>37.43000030517578</v>
       </c>
       <c r="BA65" t="n">
-        <v>-6.575408101471359</v>
+        <v>-6.999729923920073</v>
       </c>
       <c r="BB65" t="n">
         <v>-28.55090209131846</v>
@@ -26577,7 +26561,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.0%))</t>
         </is>
       </c>
     </row>
@@ -26928,7 +26912,7 @@
         <v>-0.7524892122498517</v>
       </c>
       <c r="BB67" t="n">
-        <v>-10.10472871725758</v>
+        <v>-10.10473516918537</v>
       </c>
       <c r="BC67" t="b">
         <v>1</v>
@@ -27110,7 +27094,7 @@
         <v>-0.356291362225214</v>
       </c>
       <c r="BB68" t="n">
-        <v>-13.89556964471864</v>
+        <v>-13.89556104749984</v>
       </c>
       <c r="BC68" t="b">
         <v>1</v>
@@ -27227,10 +27211,10 @@
         <v>42.38000106811523</v>
       </c>
       <c r="AI69" t="n">
-        <v>21.66</v>
+        <v>21.65</v>
       </c>
       <c r="AJ69" t="n">
-        <v>40.17</v>
+        <v>40.16</v>
       </c>
       <c r="AK69" t="n">
         <v>56.38</v>
@@ -27239,25 +27223,25 @@
         <v>42.56</v>
       </c>
       <c r="AM69" t="n">
-        <v>78.95</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="AN69" t="n">
-        <v>39.4</v>
+        <v>39.39</v>
       </c>
       <c r="AO69" t="n">
-        <v>40.17</v>
+        <v>40.16</v>
       </c>
       <c r="AP69" t="n">
-        <v>36.15</v>
+        <v>36.14</v>
       </c>
       <c r="AQ69" t="n">
         <v>3</v>
       </c>
       <c r="AR69" t="n">
-        <v>-14.69</v>
+        <v>-14.72</v>
       </c>
       <c r="AS69" t="n">
-        <v>-7.03</v>
+        <v>-7.05</v>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
@@ -27278,17 +27262,17 @@
       <c r="AX69" t="inlineStr"/>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ69" t="n">
-        <v>43.16999816894531</v>
+        <v>43.63000106811523</v>
       </c>
       <c r="BA69" t="n">
-        <v>-1.829967881255012</v>
+        <v>-2.865001075861762</v>
       </c>
       <c r="BB69" t="n">
-        <v>-12.97564384179887</v>
+        <v>-13.01253231157464</v>
       </c>
       <c r="BC69" t="b">
         <v>1</v>
@@ -27301,7 +27285,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-1.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
         </is>
       </c>
     </row>
@@ -27440,10 +27424,10 @@
         <v>4</v>
       </c>
       <c r="AR70" t="n">
-        <v>116.2</v>
+        <v>116.19</v>
       </c>
       <c r="AS70" t="n">
-        <v>117.29</v>
+        <v>117.28</v>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
@@ -27468,10 +27452,10 @@
         </is>
       </c>
       <c r="AZ70" t="n">
-        <v>2.269999980926514</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="BA70" t="n">
-        <v>-5.286338615302688</v>
+        <v>-25.0871017038871</v>
       </c>
       <c r="BB70" t="n">
         <v>-59.34562708904367</v>
@@ -27487,7 +27471,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-25.1%))</t>
         </is>
       </c>
     </row>
@@ -27899,7 +27883,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -28025,7 +28009,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -28034,10 +28018,10 @@
         </is>
       </c>
       <c r="AZ73" t="n">
-        <v>14.96000003814697</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="BA73" t="n">
-        <v>0.06684644957444252</v>
+        <v>-1.188114561278963</v>
       </c>
       <c r="BB73" t="n">
         <v>-15.64782318985707</v>
@@ -28053,7 +28037,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.2, +0.1% do topo, MM50&gt;MM200)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -28388,10 +28372,10 @@
         </is>
       </c>
       <c r="AZ75" t="n">
-        <v>21.35000038146973</v>
+        <v>21.27000045776367</v>
       </c>
       <c r="BA75" t="n">
-        <v>-1.405157559948145</v>
+        <v>-1.034326356221693</v>
       </c>
       <c r="BB75" t="n">
         <v>-23.57261978673966</v>
@@ -28407,7 +28391,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-1.4%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-1.0%))</t>
         </is>
       </c>
     </row>
@@ -28534,7 +28518,7 @@
         <v>24.18</v>
       </c>
       <c r="AN76" t="n">
-        <v>21.21</v>
+        <v>21.2</v>
       </c>
       <c r="AO76" t="n">
         <v>20.56</v>
@@ -28574,10 +28558,10 @@
         </is>
       </c>
       <c r="AZ76" t="n">
-        <v>10.03999996185303</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="BA76" t="n">
-        <v>-6.772911431866946</v>
+        <v>-9.126218608259585</v>
       </c>
       <c r="BB76" t="n">
         <v>-38.76167698563921</v>
@@ -28593,7 +28577,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.1%))</t>
         </is>
       </c>
     </row>
@@ -28760,10 +28744,10 @@
         </is>
       </c>
       <c r="AZ77" t="n">
-        <v>29.97999954223633</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="BA77" t="n">
-        <v>-7.571716118826677</v>
+        <v>-8.668427998972517</v>
       </c>
       <c r="BB77" t="n">
         <v>-21.54142799156917</v>
@@ -28779,7 +28763,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28945,7 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x0.9, +0.5% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -29124,13 +29108,13 @@
         </is>
       </c>
       <c r="AZ79" t="n">
-        <v>27.92396545410156</v>
+        <v>27.93385887145996</v>
       </c>
       <c r="BA79" t="n">
-        <v>-1.55409762161719</v>
+        <v>-1.588964497831291</v>
       </c>
       <c r="BB79" t="n">
-        <v>-16.17377809361959</v>
+        <v>-16.17376823596846</v>
       </c>
       <c r="BC79" t="b">
         <v>0</v>
@@ -29488,7 +29472,7 @@
         <v>-13.19352225208604</v>
       </c>
       <c r="BB81" t="n">
-        <v>-24.29703566053902</v>
+        <v>-24.29702860875267</v>
       </c>
       <c r="BC81" t="b">
         <v>0</v>
@@ -29793,7 +29777,7 @@
         <v>-75.77</v>
       </c>
       <c r="AS83" t="n">
-        <v>-73.06999999999999</v>
+        <v>-73.08</v>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
@@ -29814,10 +29798,10 @@
         </is>
       </c>
       <c r="AZ83" t="n">
-        <v>3.960000038146973</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="BA83" t="n">
-        <v>-1.010100037063255</v>
+        <v>-1.754384287606181</v>
       </c>
       <c r="BB83" t="n">
         <v>-18.39748429920602</v>
@@ -29833,7 +29817,7 @@
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
         </is>
       </c>
     </row>
@@ -29938,7 +29922,7 @@
         <v>11.32</v>
       </c>
       <c r="AJ84" t="n">
-        <v>16.48</v>
+        <v>16.49</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -29956,7 +29940,7 @@
         <v>2</v>
       </c>
       <c r="AR84" t="n">
-        <v>-76.92</v>
+        <v>-76.91</v>
       </c>
       <c r="AS84" t="n">
         <v>-74.34999999999999</v>
@@ -30103,7 +30087,7 @@
         <v>19.45000076293945</v>
       </c>
       <c r="AI85" t="n">
-        <v>13.37</v>
+        <v>13.38</v>
       </c>
       <c r="AJ85" t="n">
         <v>24.81</v>
@@ -30133,7 +30117,7 @@
         <v>-11.6</v>
       </c>
       <c r="AS85" t="n">
-        <v>-1.82</v>
+        <v>-1.81</v>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
@@ -30719,7 +30703,7 @@
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.8, +1.7% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.7, +1.7% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -30866,10 +30850,10 @@
         </is>
       </c>
       <c r="AZ89" t="n">
-        <v>15.03999996185303</v>
+        <v>15.0600004196167</v>
       </c>
       <c r="BA89" t="n">
-        <v>-4.255321442460303</v>
+        <v>-4.382475316711998</v>
       </c>
       <c r="BB89" t="n">
         <v>-33.0105584754462</v>
@@ -30885,7 +30869,7 @@
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -31202,7 +31186,7 @@
         <v>5</v>
       </c>
       <c r="AR91" t="n">
-        <v>-46.86</v>
+        <v>-46.85</v>
       </c>
       <c r="AS91" t="n">
         <v>-32.34</v>
@@ -31289,7 +31273,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -31385,17 +31369,21 @@
       </c>
       <c r="AV92" t="inlineStr"/>
       <c r="AW92" t="inlineStr"/>
-      <c r="AX92" t="inlineStr"/>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="AZ92" t="n">
-        <v>4.599999904632568</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="BA92" t="n">
-        <v>-0.2173859185215843</v>
+        <v>-6.326529321348828</v>
       </c>
       <c r="BB92" t="n">
         <v>-25.96773719688345</v>
@@ -31404,14 +31392,14 @@
         <v>0</v>
       </c>
       <c r="BD92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE92" t="b">
         <v>0</v>
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-0.2%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -31584,7 +31572,7 @@
         <v>2.26485493951083</v>
       </c>
       <c r="BB93" t="n">
-        <v>-31.82166878553975</v>
+        <v>-31.82166316282991</v>
       </c>
       <c r="BC93" t="b">
         <v>0</v>
@@ -31938,10 +31926,10 @@
         </is>
       </c>
       <c r="AZ95" t="n">
-        <v>12.8100004196167</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="BA95" t="n">
-        <v>-8.82123401581223</v>
+        <v>-9.876541120398075</v>
       </c>
       <c r="BB95" t="n">
         <v>-40.55979373067596</v>
@@ -31957,7 +31945,7 @@
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.9%))</t>
         </is>
       </c>
     </row>
@@ -32116,10 +32104,10 @@
         </is>
       </c>
       <c r="AZ96" t="n">
-        <v>8.840000152587891</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="BA96" t="n">
-        <v>-6.221721507254186</v>
+        <v>-7.477679391087467</v>
       </c>
       <c r="BB96" t="n">
         <v>-45.78155668714374</v>
@@ -32135,7 +32123,7 @@
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.5%))</t>
         </is>
       </c>
     </row>
@@ -32175,7 +32163,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -32274,10 +32262,10 @@
         <v>4</v>
       </c>
       <c r="AR97" t="n">
-        <v>-68.13</v>
+        <v>-68.14</v>
       </c>
       <c r="AS97" t="n">
-        <v>-64.2</v>
+        <v>-64.20999999999999</v>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
@@ -32291,17 +32279,21 @@
       </c>
       <c r="AV97" t="inlineStr"/>
       <c r="AW97" t="inlineStr"/>
-      <c r="AX97" t="inlineStr"/>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AZ97" t="n">
-        <v>3.559999942779541</v>
+        <v>3.529999971389771</v>
       </c>
       <c r="BA97" t="n">
-        <v>-0.5617972260667625</v>
+        <v>0.2832858511134795</v>
       </c>
       <c r="BB97" t="n">
         <v>-43.80952611621899</v>
@@ -32310,14 +32302,14 @@
         <v>0</v>
       </c>
       <c r="BD97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE97" t="b">
         <v>0</v>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-0.6%))</t>
+          <t>Rompimento (vol x0.6, +0.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -32357,7 +32349,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -32473,17 +32465,21 @@
       </c>
       <c r="AV98" t="inlineStr"/>
       <c r="AW98" t="inlineStr"/>
-      <c r="AX98" t="inlineStr"/>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>Em Alta</t>
         </is>
       </c>
       <c r="AZ98" t="n">
-        <v>60.84999847412109</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="BA98" t="n">
-        <v>-2.711582173470994</v>
+        <v>-2.213412838327533</v>
       </c>
       <c r="BB98" t="n">
         <v>-18.88188813392943</v>
@@ -32492,14 +32488,14 @@
         <v>0</v>
       </c>
       <c r="BD98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE98" t="b">
         <v>0</v>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -32537,7 +32533,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -32647,17 +32643,21 @@
       </c>
       <c r="AV99" t="inlineStr"/>
       <c r="AW99" t="inlineStr"/>
-      <c r="AX99" t="inlineStr"/>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ99" t="n">
-        <v>22</v>
+        <v>21.8700008392334</v>
       </c>
       <c r="BA99" t="n">
-        <v>0</v>
+        <v>0.5944177218932367</v>
       </c>
       <c r="BB99" t="n">
         <v>-14.16308731809582</v>
@@ -32666,14 +32666,14 @@
         <v>0</v>
       </c>
       <c r="BD99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE99" t="b">
         <v>0</v>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (+0.0%))</t>
+          <t>Rompimento (vol x0.7, +0.6% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -32828,10 +32828,10 @@
         </is>
       </c>
       <c r="AZ100" t="n">
-        <v>57.11999893188477</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="BA100" t="n">
-        <v>-0.5427128228125855</v>
+        <v>-1.967212035616572</v>
       </c>
       <c r="BB100" t="n">
         <v>-13.26717347589158</v>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-0.5%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.0%))</t>
         </is>
       </c>
     </row>
@@ -32959,7 +32959,7 @@
         <v>7.239999771118164</v>
       </c>
       <c r="AI101" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ101" t="n">
         <v>2.25</v>
@@ -33010,10 +33010,10 @@
         </is>
       </c>
       <c r="AZ101" t="n">
-        <v>7.570000171661377</v>
+        <v>7.820000171661377</v>
       </c>
       <c r="BA101" t="n">
-        <v>-4.359318270276713</v>
+        <v>-7.416884754620034</v>
       </c>
       <c r="BB101" t="n">
         <v>-39.32614564611788</v>
@@ -33029,7 +33029,7 @@
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.4%))</t>
         </is>
       </c>
     </row>
@@ -33166,7 +33166,7 @@
       <c r="AX102" t="inlineStr"/>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="AZ102" t="n">
@@ -33189,7 +33189,7 @@
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.7%))</t>
         </is>
       </c>
     </row>
@@ -33512,7 +33512,7 @@
       <c r="AX104" t="inlineStr"/>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ104" t="n">
@@ -33535,7 +33535,7 @@
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.7%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-6.7%))</t>
         </is>
       </c>
     </row>
@@ -33650,7 +33650,7 @@
         <v>15.21</v>
       </c>
       <c r="AJ105" t="n">
-        <v>28.21</v>
+        <v>28.22</v>
       </c>
       <c r="AK105" t="n">
         <v>32.9</v>
@@ -33851,7 +33851,7 @@
         <v>-92.73</v>
       </c>
       <c r="AS106" t="n">
-        <v>-91.93000000000001</v>
+        <v>-91.92</v>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
@@ -34054,10 +34054,10 @@
         </is>
       </c>
       <c r="AZ107" t="n">
-        <v>20.96999931335449</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="BA107" t="n">
-        <v>-4.911773071165204</v>
+        <v>-6.384970665335166</v>
       </c>
       <c r="BB107" t="n">
         <v>-24.48052562497421</v>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -34211,7 +34211,7 @@
         <v>-36.98</v>
       </c>
       <c r="AS108" t="n">
-        <v>-24.02</v>
+        <v>-24.01</v>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
@@ -34232,10 +34232,10 @@
         </is>
       </c>
       <c r="AZ108" t="n">
-        <v>65.36000061035156</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="BA108" t="n">
-        <v>-2.52448211516324</v>
+        <v>-3.615732896853474</v>
       </c>
       <c r="BB108" t="n">
         <v>-6.060160172287976</v>
@@ -34251,7 +34251,7 @@
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.5%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.6%))</t>
         </is>
       </c>
     </row>
@@ -34414,10 +34414,10 @@
         </is>
       </c>
       <c r="AZ109" t="n">
-        <v>6.039999961853027</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="BA109" t="n">
-        <v>-9.105963480273394</v>
+        <v>-10.87662488458373</v>
       </c>
       <c r="BB109" t="n">
         <v>-47.49312091788226</v>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.9%))</t>
         </is>
       </c>
     </row>
@@ -34744,10 +34744,10 @@
         <v>2</v>
       </c>
       <c r="AR111" t="n">
-        <v>-79.52</v>
+        <v>-79.53</v>
       </c>
       <c r="AS111" t="n">
-        <v>-77.25</v>
+        <v>-77.26000000000001</v>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
@@ -34768,10 +34768,10 @@
         </is>
       </c>
       <c r="AZ111" t="n">
-        <v>7.880000114440918</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="BA111" t="n">
-        <v>-2.79188152073292</v>
+        <v>-4.96278599726937</v>
       </c>
       <c r="BB111" t="n">
         <v>-47.56761890831631</v>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
         </is>
       </c>
     </row>
@@ -34946,10 +34946,10 @@
         </is>
       </c>
       <c r="AZ112" t="n">
-        <v>21.17000007629395</v>
+        <v>21.07999992370605</v>
       </c>
       <c r="BA112" t="n">
-        <v>-7.038260584546041</v>
+        <v>-6.641364438317043</v>
       </c>
       <c r="BB112" t="n">
         <v>-21.66711277025107</v>
@@ -34965,7 +34965,7 @@
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-7.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-6.6%))</t>
         </is>
       </c>
     </row>
@@ -35308,7 +35308,7 @@
         <v>-1.36186180238328</v>
       </c>
       <c r="BB114" t="n">
-        <v>-30.45267217844202</v>
+        <v>-30.54794466860145</v>
       </c>
       <c r="BC114" t="b">
         <v>0</v>
@@ -35484,10 +35484,10 @@
         </is>
       </c>
       <c r="AZ115" t="n">
-        <v>40.34999847412109</v>
+        <v>40.54000091552734</v>
       </c>
       <c r="BA115" t="n">
-        <v>-2.850056393234324</v>
+        <v>-3.305377706774182</v>
       </c>
       <c r="BB115" t="n">
         <v>-25.59920016687365</v>
@@ -35503,7 +35503,7 @@
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.3%))</t>
         </is>
       </c>
     </row>
@@ -35666,10 +35666,10 @@
         </is>
       </c>
       <c r="AZ116" t="n">
-        <v>15.02000045776367</v>
+        <v>15.21000003814697</v>
       </c>
       <c r="BA116" t="n">
-        <v>-1.065251639214981</v>
+        <v>-2.301120187981054</v>
       </c>
       <c r="BB116" t="n">
         <v>-11.92402588591038</v>
@@ -35685,7 +35685,7 @@
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.3%))</t>
         </is>
       </c>
     </row>
@@ -36020,10 +36020,10 @@
         </is>
       </c>
       <c r="AZ118" t="n">
-        <v>2.079999923706055</v>
+        <v>2.109999895095825</v>
       </c>
       <c r="BA118" t="n">
-        <v>-3.846150319251662</v>
+        <v>-5.213265429609393</v>
       </c>
       <c r="BB118" t="n">
         <v>-52.9902135681372</v>
@@ -36039,7 +36039,7 @@
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.2%))</t>
         </is>
       </c>
     </row>
@@ -36177,7 +36177,7 @@
         <v>-43.44</v>
       </c>
       <c r="AS119" t="n">
-        <v>-41.32</v>
+        <v>-41.33</v>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
@@ -36198,10 +36198,10 @@
         </is>
       </c>
       <c r="AZ119" t="n">
-        <v>30.6200008392334</v>
+        <v>32.27000045776367</v>
       </c>
       <c r="BA119" t="n">
-        <v>-2.580015982609363</v>
+        <v>-7.561203902835989</v>
       </c>
       <c r="BB119" t="n">
         <v>-23.15317722352317</v>
@@ -36217,7 +36217,7 @@
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.6%))</t>
         </is>
       </c>
     </row>
@@ -36727,7 +36727,7 @@
         <v>-55.76</v>
       </c>
       <c r="AS122" t="n">
-        <v>-44.75</v>
+        <v>-44.76</v>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
@@ -36748,10 +36748,10 @@
         </is>
       </c>
       <c r="AZ122" t="n">
-        <v>3.950000047683716</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="BA122" t="n">
-        <v>-12.405063382824</v>
+        <v>-13.28320727125276</v>
       </c>
       <c r="BB122" t="n">
         <v>-27.91666873627231</v>
@@ -36767,7 +36767,7 @@
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-12.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-13.3%))</t>
         </is>
       </c>
     </row>
@@ -36902,10 +36902,10 @@
         <v>3</v>
       </c>
       <c r="AR123" t="n">
-        <v>-78.26000000000001</v>
+        <v>-78.27</v>
       </c>
       <c r="AS123" t="n">
-        <v>-74.01000000000001</v>
+        <v>-74.02</v>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         </is>
       </c>
       <c r="AZ124" t="n">
-        <v>50.90999984741211</v>
+        <v>51.63999938964844</v>
       </c>
       <c r="BA124" t="n">
-        <v>-1.316044335009692</v>
+        <v>-2.711072284525007</v>
       </c>
       <c r="BB124" t="n">
         <v>-15.20674822199697</v>
@@ -37123,7 +37123,7 @@
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-1.3%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
         </is>
       </c>
     </row>
@@ -37614,7 +37614,7 @@
         <v>3</v>
       </c>
       <c r="AR127" t="n">
-        <v>-59.4</v>
+        <v>-59.41</v>
       </c>
       <c r="AS127" t="n">
         <v>-51.65</v>
@@ -37638,10 +37638,10 @@
         </is>
       </c>
       <c r="AZ127" t="n">
-        <v>4.809999942779541</v>
+        <v>5.389999866485596</v>
       </c>
       <c r="BA127" t="n">
-        <v>-2.494800145251941</v>
+        <v>-12.9870097700309</v>
       </c>
       <c r="BB127" t="n">
         <v>-35.79600429110067</v>
@@ -37657,7 +37657,7 @@
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-13.0%))</t>
         </is>
       </c>
     </row>
@@ -37800,10 +37800,10 @@
         </is>
       </c>
       <c r="AZ128" t="n">
-        <v>1.070000052452087</v>
+        <v>1.080000042915344</v>
       </c>
       <c r="BA128" t="n">
-        <v>-23.36449040649363</v>
+        <v>-24.07407775337299</v>
       </c>
       <c r="BB128" t="n">
         <v>-85.0364965329675</v>
@@ -37819,7 +37819,7 @@
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-23.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-24.1%))</t>
         </is>
       </c>
     </row>
@@ -37960,10 +37960,10 @@
         </is>
       </c>
       <c r="AZ129" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.5600000023841858</v>
       </c>
       <c r="BA129" t="n">
-        <v>-48.97959282973168</v>
+        <v>-55.35714304720869</v>
       </c>
       <c r="BB129" t="n">
         <v>-98.60801774641438</v>
@@ -37979,7 +37979,7 @@
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-49.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-55.4%))</t>
         </is>
       </c>
     </row>
@@ -39362,10 +39362,10 @@
         </is>
       </c>
       <c r="AZ137" t="n">
-        <v>6.409999847412109</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="BA137" t="n">
-        <v>-8.42433657890086</v>
+        <v>-14.05563761157501</v>
       </c>
       <c r="BB137" t="n">
         <v>-57.40203193535611</v>
@@ -39381,7 +39381,7 @@
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-14.1%))</t>
         </is>
       </c>
     </row>
@@ -39722,10 +39722,10 @@
         </is>
       </c>
       <c r="AZ139" t="n">
-        <v>14.4399995803833</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="BA139" t="n">
-        <v>-3.116342259984972</v>
+        <v>-2.030812095769474</v>
       </c>
       <c r="BB139" t="n">
         <v>-19.26672009275214</v>
@@ -39741,7 +39741,7 @@
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.0%))</t>
         </is>
       </c>
     </row>
@@ -40066,10 +40066,10 @@
         </is>
       </c>
       <c r="AZ141" t="n">
-        <v>19.73999977111816</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="BA141" t="n">
-        <v>-4.002021364430652</v>
+        <v>-3.807106451543563</v>
       </c>
       <c r="BB141" t="n">
         <v>-14.21457387034277</v>
@@ -40085,7 +40085,7 @@
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-4.0%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.8%))</t>
         </is>
       </c>
     </row>
@@ -40248,10 +40248,10 @@
         </is>
       </c>
       <c r="AZ142" t="n">
-        <v>22.71999931335449</v>
+        <v>23.09000015258789</v>
       </c>
       <c r="BA142" t="n">
-        <v>-17.69365612635446</v>
+        <v>-19.01255678058718</v>
       </c>
       <c r="BB142" t="n">
         <v>-34.03794200003011</v>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-17.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-19.0%))</t>
         </is>
       </c>
     </row>
@@ -40426,10 +40426,10 @@
         </is>
       </c>
       <c r="AZ143" t="n">
-        <v>40.33000183105469</v>
+        <v>40.95000076293945</v>
       </c>
       <c r="BA143" t="n">
-        <v>-2.851478982560796</v>
+        <v>-4.322345359674706</v>
       </c>
       <c r="BB143" t="n">
         <v>-15.4145065558933</v>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -40596,7 +40596,7 @@
       <c r="AX144" t="inlineStr"/>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="AZ144" t="n">
@@ -40619,7 +40619,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -41508,10 +41508,10 @@
         </is>
       </c>
       <c r="AZ149" t="n">
-        <v>11.98999977111816</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="BA149" t="n">
-        <v>-6.922434858634285</v>
+        <v>-9.342002705150176</v>
       </c>
       <c r="BB149" t="n">
         <v>-23.87448865231636</v>
@@ -41527,7 +41527,7 @@
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.3%))</t>
         </is>
       </c>
     </row>
@@ -41868,10 +41868,10 @@
         </is>
       </c>
       <c r="AZ151" t="n">
-        <v>75.26999664306641</v>
+        <v>75.94000244140625</v>
       </c>
       <c r="BA151" t="n">
-        <v>-4.982064789749707</v>
+        <v>-5.820391962391924</v>
       </c>
       <c r="BB151" t="n">
         <v>-15.75972278249496</v>
@@ -41887,7 +41887,7 @@
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.8%))</t>
         </is>
       </c>
     </row>
@@ -41962,7 +41962,7 @@
         <v>0</v>
       </c>
       <c r="V152" t="n">
-        <v>51612860416</v>
+        <v>51505192960</v>
       </c>
       <c r="W152" t="n">
         <v>40.6</v>
@@ -42046,10 +42046,10 @@
         </is>
       </c>
       <c r="AZ152" t="n">
-        <v>27.15999984741211</v>
+        <v>27.17000007629395</v>
       </c>
       <c r="BA152" t="n">
-        <v>-0.6627404498786515</v>
+        <v>-0.6993026629521171</v>
       </c>
       <c r="BB152" t="n">
         <v>-4.054058545426942</v>
